--- a/Financial Analysis/ZM.xlsx
+++ b/Financial Analysis/ZM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292C73F4-8335-48E3-A81E-18E6462B5A33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CD4F6D-17AF-4E5D-B0D6-351CC4AB620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{961327DF-2131-4088-BB64-D1A8B8DD32EB}"/>
   </bookViews>
@@ -363,14 +363,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
@@ -387,7 +387,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22120860" y="0"/>
+          <a:off x="23561040" y="0"/>
           <a:ext cx="0" cy="6316980"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -786,17 +786,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>73.25</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="E3" s="5">
-        <v>45751</v>
+        <v>45898</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45751</v>
+        <v>45898</v>
       </c>
       <c r="G3" s="5">
-        <v>45803</v>
+        <v>45985</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -804,11 +804,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>306.6</f>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>22458.45</v>
+        <v>24123.579999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,11 +825,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>1349.4+6442.3+591.5</f>
-        <v>8383.2000000000007</v>
+        <f>1198.6+6580.1+647.9</f>
+        <v>8426.6</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +849,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>8383.2000000000007</v>
+        <v>8426.6</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>14075.25</v>
+        <v>15696.979999999998</v>
       </c>
     </row>
   </sheetData>
@@ -1266,20 +1266,18 @@
         <v>1184.0999999999999</v>
       </c>
       <c r="AE3" s="7">
-        <f>AA3*1.03</f>
-        <v>1175.4360000000001</v>
+        <v>1174.7</v>
       </c>
       <c r="AF3" s="7">
-        <f>AB3*1.03</f>
-        <v>1197.375</v>
+        <v>1217.2</v>
       </c>
       <c r="AG3" s="7">
-        <f>AC3*1.02</f>
-        <v>1201.05</v>
+        <f>AC3*1.06</f>
+        <v>1248.1500000000001</v>
       </c>
       <c r="AH3" s="7">
-        <f>AD3*1.02</f>
-        <v>1207.7819999999999</v>
+        <f>AD3*1.06</f>
+        <v>1255.146</v>
       </c>
       <c r="AJ3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1311,43 +1309,43 @@
       </c>
       <c r="AQ3" s="7">
         <f>SUM(AE3:AH3)</f>
-        <v>4781.643</v>
+        <v>4895.1959999999999</v>
       </c>
       <c r="AR3" s="7">
-        <f>AQ3*1.02</f>
-        <v>4877.2758599999997</v>
+        <f>AQ3*1.03</f>
+        <v>5042.05188</v>
       </c>
       <c r="AS3" s="7">
         <f>AR3*1.01</f>
-        <v>4926.0486185999998</v>
+        <v>5092.4723987999996</v>
       </c>
       <c r="AT3" s="7">
         <f t="shared" ref="AT3:AZ3" si="0">AS3*1.01</f>
-        <v>4975.3091047859998</v>
+        <v>5143.3971227879993</v>
       </c>
       <c r="AU3" s="7">
         <f t="shared" si="0"/>
-        <v>5025.0621958338597</v>
+        <v>5194.831094015879</v>
       </c>
       <c r="AV3" s="7">
         <f t="shared" si="0"/>
-        <v>5075.3128177921981</v>
+        <v>5246.779404956038</v>
       </c>
       <c r="AW3" s="7">
         <f t="shared" si="0"/>
-        <v>5126.0659459701201</v>
+        <v>5299.2471990055983</v>
       </c>
       <c r="AX3" s="7">
         <f t="shared" si="0"/>
-        <v>5177.326605429821</v>
+        <v>5352.2396709956547</v>
       </c>
       <c r="AY3" s="7">
         <f t="shared" si="0"/>
-        <v>5229.0998714841189</v>
+        <v>5405.7620677056111</v>
       </c>
       <c r="AZ3" s="7">
         <f t="shared" si="0"/>
-        <v>5281.3908701989603</v>
+        <v>5459.8196883826677</v>
       </c>
     </row>
     <row r="4" spans="2:160" x14ac:dyDescent="0.3">
@@ -1439,20 +1437,18 @@
         <v>287.39999999999998</v>
       </c>
       <c r="AE4" s="3">
-        <f>AE3-AE5</f>
-        <v>282.10464000000002</v>
+        <v>278.39999999999998</v>
       </c>
       <c r="AF4" s="3">
-        <f t="shared" ref="AF4:AH4" si="1">AF3-AF5</f>
-        <v>287.37</v>
+        <v>273.2</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" si="1"/>
-        <v>288.25199999999995</v>
+        <f t="shared" ref="AF4:AH4" si="1">AG3-AG5</f>
+        <v>299.55600000000004</v>
       </c>
       <c r="AH4" s="3">
         <f t="shared" si="1"/>
-        <v>289.86767999999995</v>
+        <v>301.23504000000003</v>
       </c>
       <c r="AJ4" s="3">
         <f>SUM(C4:F4)</f>
@@ -1484,43 +1480,43 @@
       </c>
       <c r="AQ4" s="3">
         <f>SUM(AE4:AH4)</f>
-        <v>1147.5943199999999</v>
+        <v>1152.39104</v>
       </c>
       <c r="AR4" s="3">
         <f t="shared" ref="AR4:AW4" si="2">AR3-AR5</f>
-        <v>1170.5462063999998</v>
+        <v>1210.0924512000001</v>
       </c>
       <c r="AS4" s="3">
         <f t="shared" si="2"/>
-        <v>1182.251668464</v>
+        <v>1222.193375712</v>
       </c>
       <c r="AT4" s="3">
         <f t="shared" si="2"/>
-        <v>1194.07418514864</v>
+        <v>1234.4153094691196</v>
       </c>
       <c r="AU4" s="3">
         <f t="shared" si="2"/>
-        <v>1206.0149270001261</v>
+        <v>1246.7594625638108</v>
       </c>
       <c r="AV4" s="3">
         <f t="shared" si="2"/>
-        <v>1218.0750762701273</v>
+        <v>1259.2270571894492</v>
       </c>
       <c r="AW4" s="3">
         <f t="shared" si="2"/>
-        <v>1230.2558270328286</v>
+        <v>1271.8193277613436</v>
       </c>
       <c r="AX4" s="3">
         <f t="shared" ref="AX4:AZ4" si="3">AX3-AX5</f>
-        <v>1242.5583853031571</v>
+        <v>1284.537521038957</v>
       </c>
       <c r="AY4" s="3">
         <f t="shared" si="3"/>
-        <v>1254.9839691561883</v>
+        <v>1297.3828962493462</v>
       </c>
       <c r="AZ4" s="3">
         <f t="shared" si="3"/>
-        <v>1267.5338088477506</v>
+        <v>1310.3567252118401</v>
       </c>
     </row>
     <row r="5" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1624,7 +1620,7 @@
         <v>870.2</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" ref="AA5:AD5" si="12">AA3-AA4</f>
+        <f t="shared" ref="AA5:AF5" si="12">AA3-AA4</f>
         <v>867.90000000000009</v>
       </c>
       <c r="AB5" s="7">
@@ -1640,20 +1636,20 @@
         <v>896.69999999999993</v>
       </c>
       <c r="AE5" s="7">
-        <f>AE3*0.76</f>
-        <v>893.33136000000013</v>
+        <f t="shared" si="12"/>
+        <v>896.30000000000007</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" ref="AF5:AH5" si="13">AF3*0.76</f>
-        <v>910.005</v>
+        <f t="shared" si="12"/>
+        <v>944</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="13"/>
-        <v>912.798</v>
+        <f t="shared" ref="AF5:AH5" si="13">AG3*0.76</f>
+        <v>948.59400000000005</v>
       </c>
       <c r="AH5" s="7">
         <f t="shared" si="13"/>
-        <v>917.91431999999998</v>
+        <v>953.91095999999993</v>
       </c>
       <c r="AJ5" s="7">
         <f t="shared" ref="AJ5:AQ5" si="14">AJ3-AJ4</f>
@@ -1685,43 +1681,43 @@
       </c>
       <c r="AQ5" s="7">
         <f t="shared" si="14"/>
-        <v>3634.0486799999999</v>
+        <v>3742.8049599999999</v>
       </c>
       <c r="AR5" s="7">
         <f>AR3*0.76</f>
-        <v>3706.7296535999999</v>
+        <v>3831.9594287999998</v>
       </c>
       <c r="AS5" s="7">
         <f t="shared" ref="AS5:AZ5" si="15">AS3*0.76</f>
-        <v>3743.7969501359999</v>
+        <v>3870.2790230879996</v>
       </c>
       <c r="AT5" s="7">
         <f t="shared" si="15"/>
-        <v>3781.2349196373598</v>
+        <v>3908.9818133188796</v>
       </c>
       <c r="AU5" s="7">
         <f t="shared" si="15"/>
-        <v>3819.0472688337336</v>
+        <v>3948.0716314520682</v>
       </c>
       <c r="AV5" s="7">
         <f t="shared" si="15"/>
-        <v>3857.2377415220708</v>
+        <v>3987.5523477665888</v>
       </c>
       <c r="AW5" s="7">
         <f t="shared" si="15"/>
-        <v>3895.8101189372915</v>
+        <v>4027.4278712442547</v>
       </c>
       <c r="AX5" s="7">
         <f t="shared" si="15"/>
-        <v>3934.7682201266639</v>
+        <v>4067.7021499566977</v>
       </c>
       <c r="AY5" s="7">
         <f t="shared" si="15"/>
-        <v>3974.1159023279306</v>
+        <v>4108.3791714562649</v>
       </c>
       <c r="AZ5" s="7">
         <f t="shared" si="15"/>
-        <v>4013.8570613512097</v>
+        <v>4149.4629631708276</v>
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.3">
@@ -1813,16 +1809,14 @@
         <v>217.1</v>
       </c>
       <c r="AE6" s="3">
-        <f>AA6*1.09</f>
-        <v>224.10400000000001</v>
+        <v>205.4</v>
       </c>
       <c r="AF6" s="3">
-        <f>AB6*1.05</f>
-        <v>217.14000000000001</v>
+        <v>206.4</v>
       </c>
       <c r="AG6" s="3">
-        <f>AC6*1.04</f>
-        <v>231.92000000000002</v>
+        <f>AC6*0.98</f>
+        <v>218.54</v>
       </c>
       <c r="AH6" s="3">
         <f>AD6*1.03</f>
@@ -1858,43 +1852,43 @@
       </c>
       <c r="AQ6" s="3">
         <f>SUM(AE6:AH6)</f>
-        <v>896.77700000000004</v>
+        <v>853.95299999999997</v>
       </c>
       <c r="AR6" s="3">
         <f>AQ6*1.04</f>
-        <v>932.64808000000005</v>
+        <v>888.11112000000003</v>
       </c>
       <c r="AS6" s="3">
         <f>AR6*1.03</f>
-        <v>960.62752240000009</v>
+        <v>914.75445360000003</v>
       </c>
       <c r="AT6" s="3">
         <f>AS6*1.02</f>
-        <v>979.84007284800009</v>
+        <v>933.04954267200003</v>
       </c>
       <c r="AU6" s="3">
         <f t="shared" ref="AU6:AW8" si="16">AT6*1.01</f>
-        <v>989.63847357648012</v>
+        <v>942.38003809872009</v>
       </c>
       <c r="AV6" s="3">
         <f t="shared" si="16"/>
-        <v>999.53485831224498</v>
+        <v>951.80383847970734</v>
       </c>
       <c r="AW6" s="3">
         <f t="shared" si="16"/>
-        <v>1009.5302068953674</v>
+        <v>961.32187686450447</v>
       </c>
       <c r="AX6" s="3">
         <f t="shared" ref="AX6" si="17">AW6*1.01</f>
-        <v>1019.6255089643211</v>
+        <v>970.93509563314956</v>
       </c>
       <c r="AY6" s="3">
         <f t="shared" ref="AY6" si="18">AX6*1.01</f>
-        <v>1029.8217640539642</v>
+        <v>980.64444658948105</v>
       </c>
       <c r="AZ6" s="3">
         <f t="shared" ref="AZ6" si="19">AY6*1.01</f>
-        <v>1040.1199816945038</v>
+        <v>990.45089105537591</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.3">
@@ -1986,20 +1980,18 @@
         <v>358.9</v>
       </c>
       <c r="AE7" s="3">
-        <f>AE3*0.3</f>
-        <v>352.63080000000002</v>
+        <v>347</v>
       </c>
       <c r="AF7" s="3">
-        <f t="shared" ref="AF7:AH7" si="20">AF3*0.3</f>
-        <v>359.21249999999998</v>
+        <v>339</v>
       </c>
       <c r="AG7" s="3">
-        <f t="shared" si="20"/>
-        <v>360.315</v>
+        <f>AG3*0.28</f>
+        <v>349.48200000000008</v>
       </c>
       <c r="AH7" s="3">
-        <f t="shared" si="20"/>
-        <v>362.33459999999997</v>
+        <f>AH3*0.28</f>
+        <v>351.44088000000005</v>
       </c>
       <c r="AJ7" s="3">
         <f>SUM(C7:F7)</f>
@@ -2031,43 +2023,43 @@
       </c>
       <c r="AQ7" s="3">
         <f>SUM(AE7:AH7)</f>
-        <v>1434.4929</v>
+        <v>1386.9228800000001</v>
       </c>
       <c r="AR7" s="3">
-        <f>AR3*0.29</f>
-        <v>1414.4099993999998</v>
+        <f>AR3*0.28</f>
+        <v>1411.7745264000002</v>
       </c>
       <c r="AS7" s="3">
-        <f t="shared" ref="AS7:AZ7" si="21">AS3*0.29</f>
-        <v>1428.5540993939999</v>
+        <f t="shared" ref="AS7:AZ7" si="20">AS3*0.28</f>
+        <v>1425.892271664</v>
       </c>
       <c r="AT7" s="3">
-        <f t="shared" si="21"/>
-        <v>1442.8396403879399</v>
+        <f t="shared" si="20"/>
+        <v>1440.1511943806399</v>
       </c>
       <c r="AU7" s="3">
-        <f t="shared" si="21"/>
-        <v>1457.2680367918192</v>
+        <f t="shared" si="20"/>
+        <v>1454.5527063244463</v>
       </c>
       <c r="AV7" s="3">
-        <f t="shared" si="21"/>
-        <v>1471.8407171597373</v>
+        <f t="shared" si="20"/>
+        <v>1469.0982333876907</v>
       </c>
       <c r="AW7" s="3">
-        <f t="shared" si="21"/>
-        <v>1486.5591243313347</v>
+        <f t="shared" si="20"/>
+        <v>1483.7892157215676</v>
       </c>
       <c r="AX7" s="3">
-        <f t="shared" si="21"/>
-        <v>1501.424715574648</v>
+        <f t="shared" si="20"/>
+        <v>1498.6271078787834</v>
       </c>
       <c r="AY7" s="3">
-        <f t="shared" si="21"/>
-        <v>1516.4389627303945</v>
+        <f t="shared" si="20"/>
+        <v>1513.6133789575713</v>
       </c>
       <c r="AZ7" s="3">
-        <f t="shared" si="21"/>
-        <v>1531.6033523576984</v>
+        <f t="shared" si="20"/>
+        <v>1528.749512747147</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.3">
@@ -2159,15 +2151,13 @@
         <v>95.7</v>
       </c>
       <c r="AE8" s="3">
-        <f>AA8*0.9</f>
-        <v>100.17</v>
+        <v>102.3</v>
       </c>
       <c r="AF8" s="3">
-        <f t="shared" ref="AF8:AG8" si="22">AB8*0.9</f>
-        <v>98.55</v>
+        <v>76.900000000000006</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="AF8:AG8" si="21">AC8*0.9</f>
         <v>113.49</v>
       </c>
       <c r="AH8" s="3">
@@ -2204,43 +2194,43 @@
       </c>
       <c r="AQ8" s="3">
         <f>SUM(AE8:AH8)</f>
-        <v>412.69499999999999</v>
+        <v>393.17500000000001</v>
       </c>
       <c r="AR8" s="3">
         <f>AQ8*1.02</f>
-        <v>420.94889999999998</v>
+        <v>401.0385</v>
       </c>
       <c r="AS8" s="3">
         <f>AR8*1.02</f>
-        <v>429.36787799999996</v>
+        <v>409.05927000000003</v>
       </c>
       <c r="AT8" s="3">
         <f>AS8*1.02</f>
-        <v>437.95523555999995</v>
+        <v>417.24045540000003</v>
       </c>
       <c r="AU8" s="3">
         <f t="shared" si="16"/>
-        <v>442.33478791559997</v>
+        <v>421.41285995400006</v>
       </c>
       <c r="AV8" s="3">
         <f t="shared" si="16"/>
-        <v>446.75813579475596</v>
+        <v>425.62698855354006</v>
       </c>
       <c r="AW8" s="3">
         <f t="shared" si="16"/>
-        <v>451.22571715270351</v>
+        <v>429.88325843907546</v>
       </c>
       <c r="AX8" s="3">
-        <f t="shared" ref="AX8" si="23">AW8*1.01</f>
-        <v>455.73797432423055</v>
+        <f t="shared" ref="AX8" si="22">AW8*1.01</f>
+        <v>434.18209102346623</v>
       </c>
       <c r="AY8" s="3">
-        <f t="shared" ref="AY8" si="24">AX8*1.01</f>
-        <v>460.29535406747289</v>
+        <f t="shared" ref="AY8" si="23">AX8*1.01</f>
+        <v>438.5239119337009</v>
       </c>
       <c r="AZ8" s="3">
-        <f t="shared" ref="AZ8" si="25">AY8*1.01</f>
-        <v>464.8983076081476</v>
+        <f t="shared" ref="AZ8" si="24">AY8*1.01</f>
+        <v>442.90915105303793</v>
       </c>
     </row>
     <row r="9" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2248,132 +2238,132 @@
         <v>33</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:P9" si="26">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:P9" si="25">C5-C6-C7-C8</f>
         <v>-1.7999999999999883</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>3.5</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-1.1000000000000085</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>5.4999999999999982</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>1.6000000000000085</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>2.2000000000000028</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-1.6000000000000121</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>10.600000000000016</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>23.4</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>188.10000000000002</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>192.29999999999998</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>256.10000000000008</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>226.20000000000002</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>294.60000000000014</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" ref="Q9" si="27">Q5-Q6-Q7-Q8</f>
+        <f t="shared" ref="Q9" si="26">Q5-Q6-Q7-Q8</f>
         <v>290.89999999999998</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" ref="R9" si="28">R5-R6-R7-R8</f>
+        <f t="shared" ref="R9" si="27">R5-R6-R7-R8</f>
         <v>251.90000000000015</v>
       </c>
       <c r="S9" s="7">
-        <f t="shared" ref="S9:T9" si="29">S5-S6-S7-S8</f>
+        <f t="shared" ref="S9:T9" si="28">S5-S6-S7-S8</f>
         <v>187.10000000000002</v>
       </c>
       <c r="T9" s="7">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>121.69999999999996</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" ref="U9" si="30">U5-U6-U7-U8</f>
+        <f t="shared" ref="U9" si="29">U5-U6-U7-U8</f>
         <v>66.60000000000008</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" ref="V9" si="31">V5-V6-V7-V8</f>
+        <f t="shared" ref="V9" si="30">V5-V6-V7-V8</f>
         <v>-130.00000000000011</v>
       </c>
       <c r="W9" s="7">
-        <f t="shared" ref="W9:X9" si="32">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9:X9" si="31">W5-W6-W7-W8</f>
         <v>9.8000000000000398</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>177.59999999999997</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" ref="Y9" si="33">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="32">Y5-Y6-Y7-Y8</f>
         <v>169.40000000000012</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" ref="Z9" si="34">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="33">Z5-Z6-Z7-Z8</f>
         <v>168.50000000000006</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9:AH9" si="35">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AH9" si="34">AA5-AA6-AA7-AA8</f>
         <v>203.00000000000006</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>202.2999999999999</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>182.80000000000004</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>224.99999999999994</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="35"/>
-        <v>216.42656000000005</v>
+        <f t="shared" si="34"/>
+        <v>241.60000000000008</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="35"/>
-        <v>235.10250000000002</v>
+        <f t="shared" si="34"/>
+        <v>321.70000000000005</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="35"/>
-        <v>207.07299999999992</v>
+        <f t="shared" si="34"/>
+        <v>267.08199999999999</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="35"/>
-        <v>231.48172000000005</v>
+        <f t="shared" si="34"/>
+        <v>278.37207999999981</v>
       </c>
       <c r="AJ9" s="7">
         <f>AJ5-AJ6-AJ7-AJ8</f>
@@ -2392,56 +2382,56 @@
         <v>1063.5999999999997</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" ref="AN9:AW9" si="36">AN5-AN6-AN7-AN8</f>
+        <f t="shared" ref="AN9:AW9" si="35">AN5-AN6-AN7-AN8</f>
         <v>245.4000000000002</v>
       </c>
       <c r="AO9" s="7">
+        <f t="shared" si="35"/>
+        <v>525.30000000000007</v>
+      </c>
+      <c r="AP9" s="7">
+        <f t="shared" si="35"/>
+        <v>813.09999999999945</v>
+      </c>
+      <c r="AQ9" s="7">
+        <f t="shared" si="35"/>
+        <v>1108.7540799999999</v>
+      </c>
+      <c r="AR9" s="7">
+        <f t="shared" si="35"/>
+        <v>1131.0352823999997</v>
+      </c>
+      <c r="AS9" s="7">
+        <f t="shared" si="35"/>
+        <v>1120.5730278239996</v>
+      </c>
+      <c r="AT9" s="7">
+        <f t="shared" si="35"/>
+        <v>1118.5406208662398</v>
+      </c>
+      <c r="AU9" s="7">
+        <f t="shared" si="35"/>
+        <v>1129.726027074902</v>
+      </c>
+      <c r="AV9" s="7">
+        <f t="shared" si="35"/>
+        <v>1141.0232873456507</v>
+      </c>
+      <c r="AW9" s="7">
+        <f t="shared" si="35"/>
+        <v>1152.4335202191069</v>
+      </c>
+      <c r="AX9" s="7">
+        <f t="shared" ref="AX9:AZ9" si="36">AX5-AX6-AX7-AX8</f>
+        <v>1163.9578554212985</v>
+      </c>
+      <c r="AY9" s="7">
         <f t="shared" si="36"/>
-        <v>525.30000000000007</v>
-      </c>
-      <c r="AP9" s="7">
+        <v>1175.5974339755116</v>
+      </c>
+      <c r="AZ9" s="7">
         <f t="shared" si="36"/>
-        <v>813.09999999999945</v>
-      </c>
-      <c r="AQ9" s="7">
-        <f t="shared" si="36"/>
-        <v>890.08377999999993</v>
-      </c>
-      <c r="AR9" s="7">
-        <f t="shared" si="36"/>
-        <v>938.72267420000014</v>
-      </c>
-      <c r="AS9" s="7">
-        <f t="shared" si="36"/>
-        <v>925.24745034199987</v>
-      </c>
-      <c r="AT9" s="7">
-        <f t="shared" si="36"/>
-        <v>920.59997084141992</v>
-      </c>
-      <c r="AU9" s="7">
-        <f t="shared" si="36"/>
-        <v>929.80597054983446</v>
-      </c>
-      <c r="AV9" s="7">
-        <f t="shared" si="36"/>
-        <v>939.10403025533253</v>
-      </c>
-      <c r="AW9" s="7">
-        <f t="shared" si="36"/>
-        <v>948.49507055788581</v>
-      </c>
-      <c r="AX9" s="7">
-        <f t="shared" ref="AX9:AZ9" si="37">AX5-AX6-AX7-AX8</f>
-        <v>957.98002126346444</v>
-      </c>
-      <c r="AY9" s="7">
-        <f t="shared" si="37"/>
-        <v>967.55982147609905</v>
-      </c>
-      <c r="AZ9" s="7">
-        <f t="shared" si="37"/>
-        <v>977.23541969085954</v>
+        <v>1187.3534083152667</v>
       </c>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.3">
@@ -2548,10 +2538,12 @@
         <v>-225.3</v>
       </c>
       <c r="AE10" s="3">
-        <v>-100</v>
+        <f>13.6-87.8</f>
+        <v>-74.2</v>
       </c>
       <c r="AF10" s="3">
-        <v>-100</v>
+        <f>-45-81.7</f>
+        <v>-126.7</v>
       </c>
       <c r="AG10" s="3">
         <v>-100</v>
@@ -2589,43 +2581,43 @@
       </c>
       <c r="AQ10" s="3">
         <f>SUM(AE10:AH10)</f>
-        <v>-400</v>
+        <v>-400.9</v>
       </c>
       <c r="AR10" s="3">
-        <f>AQ10*1.01</f>
-        <v>-404</v>
+        <f>AQ10*1.03</f>
+        <v>-412.92699999999996</v>
       </c>
       <c r="AS10" s="3">
-        <f t="shared" ref="AS10:AZ10" si="38">AR10*1.01</f>
-        <v>-408.04</v>
+        <f t="shared" ref="AS10:AZ10" si="37">AR10*1.03</f>
+        <v>-425.31480999999997</v>
       </c>
       <c r="AT10" s="3">
-        <f t="shared" si="38"/>
-        <v>-412.12040000000002</v>
+        <f t="shared" si="37"/>
+        <v>-438.07425429999995</v>
       </c>
       <c r="AU10" s="3">
-        <f t="shared" si="38"/>
-        <v>-416.241604</v>
+        <f t="shared" si="37"/>
+        <v>-451.21648192899994</v>
       </c>
       <c r="AV10" s="3">
-        <f t="shared" si="38"/>
-        <v>-420.40402003999998</v>
+        <f t="shared" si="37"/>
+        <v>-464.75297638686993</v>
       </c>
       <c r="AW10" s="3">
-        <f t="shared" si="38"/>
-        <v>-424.60806024039999</v>
+        <f t="shared" si="37"/>
+        <v>-478.69556567847604</v>
       </c>
       <c r="AX10" s="3">
-        <f t="shared" si="38"/>
-        <v>-428.85414084280399</v>
+        <f t="shared" si="37"/>
+        <v>-493.05643264883031</v>
       </c>
       <c r="AY10" s="3">
-        <f t="shared" si="38"/>
-        <v>-433.14268225123203</v>
+        <f t="shared" si="37"/>
+        <v>-507.84812562829524</v>
       </c>
       <c r="AZ10" s="3">
-        <f t="shared" si="38"/>
-        <v>-437.47410907374433</v>
+        <f t="shared" si="37"/>
+        <v>-523.08356939714406</v>
       </c>
     </row>
     <row r="11" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2633,132 +2625,132 @@
         <v>35</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:P11" si="39">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="38">C9-C10</f>
         <v>-1.3999999999999884</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>-0.50000000000000855</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="G11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>2.6000000000000085</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>6.7000000000000028</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>2.5999999999999881</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>14.600000000000016</v>
       </c>
       <c r="K11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>29.2</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>190.20000000000002</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>194.1</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>264.60000000000008</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>228.8</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>323.90000000000015</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" ref="Q11" si="40">Q9-Q10</f>
+        <f t="shared" ref="Q11" si="39">Q9-Q10</f>
         <v>410.29999999999995</v>
       </c>
       <c r="R11" s="7">
-        <f t="shared" ref="R11" si="41">R9-R10</f>
+        <f t="shared" ref="R11" si="40">R9-R10</f>
         <v>138.70000000000016</v>
       </c>
       <c r="S11" s="7">
-        <f t="shared" ref="S11:T11" si="42">S9-S10</f>
+        <f t="shared" ref="S11:T11" si="41">S9-S10</f>
         <v>143.70000000000002</v>
       </c>
       <c r="T11" s="7">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>90.399999999999949</v>
       </c>
       <c r="U11" s="7">
-        <f t="shared" ref="U11" si="43">U9-U10</f>
+        <f t="shared" ref="U11" si="42">U9-U10</f>
         <v>54.800000000000082</v>
       </c>
       <c r="V11" s="7">
-        <f t="shared" ref="V11" si="44">V9-V10</f>
+        <f t="shared" ref="V11" si="43">V9-V10</f>
         <v>-39.700000000000117</v>
       </c>
       <c r="W11" s="7">
-        <f t="shared" ref="W11:X11" si="45">W9-W10</f>
+        <f t="shared" ref="W11:X11" si="44">W9-W10</f>
         <v>43.30000000000004</v>
       </c>
       <c r="X11" s="7">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>250.39999999999998</v>
       </c>
       <c r="Y11" s="7">
-        <f t="shared" ref="Y11" si="46">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="45">Y9-Y10</f>
         <v>185.80000000000013</v>
       </c>
       <c r="Z11" s="7">
-        <f t="shared" ref="Z11" si="47">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="46">Z9-Z10</f>
         <v>352.90000000000003</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AH11" si="48">AA9-AA10</f>
+        <f t="shared" ref="AA11:AH11" si="47">AA9-AA10</f>
         <v>292.00000000000006</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>292.7999999999999</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>280.30000000000007</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>450.29999999999995</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="48"/>
-        <v>316.42656000000005</v>
+        <f t="shared" si="47"/>
+        <v>315.80000000000007</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="48"/>
-        <v>335.10250000000002</v>
+        <f t="shared" si="47"/>
+        <v>448.40000000000003</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="48"/>
-        <v>307.07299999999992</v>
+        <f t="shared" si="47"/>
+        <v>367.08199999999999</v>
       </c>
       <c r="AH11" s="7">
-        <f t="shared" si="48"/>
-        <v>331.48172000000005</v>
+        <f t="shared" si="47"/>
+        <v>378.37207999999981</v>
       </c>
       <c r="AJ11" s="7">
         <f>AJ9-AJ10</f>
@@ -2777,56 +2769,56 @@
         <v>1101.6999999999996</v>
       </c>
       <c r="AN11" s="7">
-        <f t="shared" ref="AN11:AW11" si="49">AN9-AN10</f>
+        <f t="shared" ref="AN11:AW11" si="48">AN9-AN10</f>
         <v>249.20000000000022</v>
       </c>
       <c r="AO11" s="7">
+        <f t="shared" si="48"/>
+        <v>832.40000000000009</v>
+      </c>
+      <c r="AP11" s="7">
+        <f t="shared" si="48"/>
+        <v>1315.3999999999994</v>
+      </c>
+      <c r="AQ11" s="7">
+        <f t="shared" si="48"/>
+        <v>1509.6540799999998</v>
+      </c>
+      <c r="AR11" s="7">
+        <f t="shared" si="48"/>
+        <v>1543.9622823999996</v>
+      </c>
+      <c r="AS11" s="7">
+        <f t="shared" si="48"/>
+        <v>1545.8878378239997</v>
+      </c>
+      <c r="AT11" s="7">
+        <f t="shared" si="48"/>
+        <v>1556.6148751662397</v>
+      </c>
+      <c r="AU11" s="7">
+        <f t="shared" si="48"/>
+        <v>1580.9425090039019</v>
+      </c>
+      <c r="AV11" s="7">
+        <f t="shared" si="48"/>
+        <v>1605.7762637325206</v>
+      </c>
+      <c r="AW11" s="7">
+        <f t="shared" si="48"/>
+        <v>1631.1290858975829</v>
+      </c>
+      <c r="AX11" s="7">
+        <f t="shared" ref="AX11:AZ11" si="49">AX9-AX10</f>
+        <v>1657.0142880701287</v>
+      </c>
+      <c r="AY11" s="7">
         <f t="shared" si="49"/>
-        <v>832.40000000000009</v>
-      </c>
-      <c r="AP11" s="7">
+        <v>1683.4455596038069</v>
+      </c>
+      <c r="AZ11" s="7">
         <f t="shared" si="49"/>
-        <v>1315.3999999999994</v>
-      </c>
-      <c r="AQ11" s="7">
-        <f t="shared" si="49"/>
-        <v>1290.0837799999999</v>
-      </c>
-      <c r="AR11" s="7">
-        <f t="shared" si="49"/>
-        <v>1342.7226742000003</v>
-      </c>
-      <c r="AS11" s="7">
-        <f t="shared" si="49"/>
-        <v>1333.2874503419998</v>
-      </c>
-      <c r="AT11" s="7">
-        <f t="shared" si="49"/>
-        <v>1332.7203708414199</v>
-      </c>
-      <c r="AU11" s="7">
-        <f t="shared" si="49"/>
-        <v>1346.0475745498345</v>
-      </c>
-      <c r="AV11" s="7">
-        <f t="shared" si="49"/>
-        <v>1359.5080502953324</v>
-      </c>
-      <c r="AW11" s="7">
-        <f t="shared" si="49"/>
-        <v>1373.1031307982857</v>
-      </c>
-      <c r="AX11" s="7">
-        <f t="shared" ref="AX11:AZ11" si="50">AX9-AX10</f>
-        <v>1386.8341621062684</v>
-      </c>
-      <c r="AY11" s="7">
-        <f t="shared" si="50"/>
-        <v>1400.7025037273311</v>
-      </c>
-      <c r="AZ11" s="7">
-        <f t="shared" si="50"/>
-        <v>1414.7095287646039</v>
+        <v>1710.4369777124107</v>
       </c>
     </row>
     <row r="12" spans="2:160" x14ac:dyDescent="0.3">
@@ -2918,20 +2910,18 @@
         <v>82.5</v>
       </c>
       <c r="AE12" s="3">
-        <f>AE11*0.25</f>
-        <v>79.106640000000013</v>
+        <v>61.2</v>
       </c>
       <c r="AF12" s="3">
-        <f t="shared" ref="AF12:AG12" si="51">AF11*0.25</f>
-        <v>83.775625000000005</v>
+        <v>89.6</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" si="51"/>
-        <v>76.768249999999981</v>
+        <f t="shared" ref="AF12:AG12" si="50">AG11*0.25</f>
+        <v>91.770499999999998</v>
       </c>
       <c r="AH12" s="3">
         <f>AH11*0.2</f>
-        <v>66.296344000000019</v>
+        <v>75.674415999999965</v>
       </c>
       <c r="AJ12" s="3">
         <f>SUM(C12:F12)</f>
@@ -2963,43 +2953,43 @@
       </c>
       <c r="AQ12" s="3">
         <f>SUM(AE12:AH12)</f>
-        <v>305.94685900000002</v>
+        <v>318.24491599999999</v>
       </c>
       <c r="AR12" s="3">
-        <f>AR11*0.24</f>
-        <v>322.25344180800005</v>
+        <f>AR11*0.22</f>
+        <v>339.67170212799994</v>
       </c>
       <c r="AS12" s="3">
-        <f t="shared" ref="AS12:AZ12" si="52">AS11*0.24</f>
-        <v>319.98898808207997</v>
+        <f t="shared" ref="AS12:AZ12" si="51">AS11*0.22</f>
+        <v>340.09532432127992</v>
       </c>
       <c r="AT12" s="3">
-        <f t="shared" si="52"/>
-        <v>319.85288900194075</v>
+        <f t="shared" si="51"/>
+        <v>342.45527253657275</v>
       </c>
       <c r="AU12" s="3">
-        <f t="shared" si="52"/>
-        <v>323.05141789196028</v>
+        <f t="shared" si="51"/>
+        <v>347.80735198085841</v>
       </c>
       <c r="AV12" s="3">
-        <f t="shared" si="52"/>
-        <v>326.28193207087975</v>
+        <f t="shared" si="51"/>
+        <v>353.27077802115457</v>
       </c>
       <c r="AW12" s="3">
-        <f t="shared" si="52"/>
-        <v>329.54475139158859</v>
+        <f t="shared" si="51"/>
+        <v>358.84839889746826</v>
       </c>
       <c r="AX12" s="3">
-        <f t="shared" si="52"/>
-        <v>332.84019890550439</v>
+        <f t="shared" si="51"/>
+        <v>364.54314337542831</v>
       </c>
       <c r="AY12" s="3">
-        <f t="shared" si="52"/>
-        <v>336.16860089455946</v>
+        <f t="shared" si="51"/>
+        <v>370.35802311283754</v>
       </c>
       <c r="AZ12" s="3">
-        <f t="shared" si="52"/>
-        <v>339.53028690350493</v>
+        <f t="shared" si="51"/>
+        <v>376.29613509673032</v>
       </c>
     </row>
     <row r="13" spans="2:160" x14ac:dyDescent="0.3">
@@ -3167,132 +3157,132 @@
         <v>37</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" ref="C14:P14" si="53">C11-C12-C13</f>
+        <f t="shared" ref="C14:P14" si="52">C11-C12-C13</f>
         <v>-1.4999999999999885</v>
       </c>
       <c r="D14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0.69999999999999973</v>
       </c>
       <c r="E14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-0.60000000000000853</v>
       </c>
       <c r="F14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>1.9999999999999982</v>
       </c>
       <c r="G14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>0.3000000000000087</v>
       </c>
       <c r="H14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>5.5000000000000027</v>
       </c>
       <c r="I14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>2.2999999999999883</v>
       </c>
       <c r="J14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>15.400000000000016</v>
       </c>
       <c r="K14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>27.099999999999998</v>
       </c>
       <c r="L14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>185.80000000000004</v>
       </c>
       <c r="M14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>198.5</v>
       </c>
       <c r="N14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>260.40000000000009</v>
       </c>
       <c r="O14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>227.4</v>
       </c>
       <c r="P14" s="7">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>316.90000000000015</v>
       </c>
       <c r="Q14" s="7">
-        <f t="shared" ref="Q14" si="54">Q11-Q12-Q13</f>
+        <f t="shared" ref="Q14" si="53">Q11-Q12-Q13</f>
         <v>340.29999999999995</v>
       </c>
       <c r="R14" s="7">
-        <f t="shared" ref="R14" si="55">R11-R12-R13</f>
+        <f t="shared" ref="R14" si="54">R11-R12-R13</f>
         <v>490.70000000000016</v>
       </c>
       <c r="S14" s="7">
-        <f t="shared" ref="S14:T14" si="56">S11-S12-S13</f>
+        <f t="shared" ref="S14:T14" si="55">S11-S12-S13</f>
         <v>113.70000000000002</v>
       </c>
       <c r="T14" s="7">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>45.799999999999947</v>
       </c>
       <c r="U14" s="7">
-        <f t="shared" ref="U14" si="57">U11-U12-U13</f>
+        <f t="shared" ref="U14" si="56">U11-U12-U13</f>
         <v>48.400000000000084</v>
       </c>
       <c r="V14" s="7">
-        <f t="shared" ref="V14" si="58">V11-V12-V13</f>
+        <f t="shared" ref="V14" si="57">V11-V12-V13</f>
         <v>-104.20000000000012</v>
       </c>
       <c r="W14" s="7">
-        <f t="shared" ref="W14:X14" si="59">W11-W12-W13</f>
+        <f t="shared" ref="W14:X14" si="58">W11-W12-W13</f>
         <v>15.500000000000039</v>
       </c>
       <c r="X14" s="7">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>181.99999999999997</v>
       </c>
       <c r="Y14" s="7">
-        <f t="shared" ref="Y14" si="60">Y11-Y12-Y13</f>
+        <f t="shared" ref="Y14" si="59">Y11-Y12-Y13</f>
         <v>141.20000000000013</v>
       </c>
       <c r="Z14" s="7">
-        <f t="shared" ref="Z14" si="61">Z11-Z12-Z13</f>
+        <f t="shared" ref="Z14" si="60">Z11-Z12-Z13</f>
         <v>298.8</v>
       </c>
       <c r="AA14" s="7">
-        <f t="shared" ref="AA14:AD14" si="62">AA11-AA12-AA13</f>
+        <f t="shared" ref="AA14:AD14" si="61">AA11-AA12-AA13</f>
         <v>216.30000000000007</v>
       </c>
       <c r="AB14" s="7">
+        <f t="shared" si="61"/>
+        <v>218.89999999999989</v>
+      </c>
+      <c r="AC14" s="7">
+        <f t="shared" si="61"/>
+        <v>206.90000000000006</v>
+      </c>
+      <c r="AD14" s="7">
+        <f t="shared" si="61"/>
+        <v>367.79999999999995</v>
+      </c>
+      <c r="AE14" s="7">
+        <f t="shared" ref="AE14:AH14" si="62">AE11-AE12-AE13</f>
+        <v>254.60000000000008</v>
+      </c>
+      <c r="AF14" s="7">
         <f t="shared" si="62"/>
-        <v>218.89999999999989</v>
-      </c>
-      <c r="AC14" s="7">
+        <v>358.80000000000007</v>
+      </c>
+      <c r="AG14" s="7">
         <f t="shared" si="62"/>
-        <v>206.90000000000006</v>
-      </c>
-      <c r="AD14" s="7">
+        <v>275.31150000000002</v>
+      </c>
+      <c r="AH14" s="7">
         <f t="shared" si="62"/>
-        <v>367.79999999999995</v>
-      </c>
-      <c r="AE14" s="7">
-        <f t="shared" ref="AE14:AH14" si="63">AE11-AE12-AE13</f>
-        <v>237.31992000000002</v>
-      </c>
-      <c r="AF14" s="7">
-        <f t="shared" si="63"/>
-        <v>251.32687500000003</v>
-      </c>
-      <c r="AG14" s="7">
-        <f t="shared" si="63"/>
-        <v>230.30474999999996</v>
-      </c>
-      <c r="AH14" s="7">
-        <f t="shared" si="63"/>
-        <v>265.18537600000002</v>
+        <v>302.69766399999986</v>
       </c>
       <c r="AJ14" s="7">
         <f>AJ11-AJ12-AJ13</f>
@@ -3315,484 +3305,484 @@
         <v>103.70000000000022</v>
       </c>
       <c r="AO14" s="7">
-        <f t="shared" ref="AO14:AW14" si="64">AO11-AO12-AO13</f>
+        <f t="shared" ref="AO14:AW14" si="63">AO11-AO12-AO13</f>
         <v>637.50000000000011</v>
       </c>
       <c r="AP14" s="7">
+        <f t="shared" si="63"/>
+        <v>1009.8999999999994</v>
+      </c>
+      <c r="AQ14" s="7">
+        <f t="shared" si="63"/>
+        <v>1191.4091639999997</v>
+      </c>
+      <c r="AR14" s="7">
+        <f t="shared" si="63"/>
+        <v>1204.2905802719997</v>
+      </c>
+      <c r="AS14" s="7">
+        <f t="shared" si="63"/>
+        <v>1205.7925135027199</v>
+      </c>
+      <c r="AT14" s="7">
+        <f t="shared" si="63"/>
+        <v>1214.159602629667</v>
+      </c>
+      <c r="AU14" s="7">
+        <f t="shared" si="63"/>
+        <v>1233.1351570230436</v>
+      </c>
+      <c r="AV14" s="7">
+        <f t="shared" si="63"/>
+        <v>1252.505485711366</v>
+      </c>
+      <c r="AW14" s="7">
+        <f t="shared" si="63"/>
+        <v>1272.2806870001145</v>
+      </c>
+      <c r="AX14" s="7">
+        <f t="shared" ref="AX14:AZ14" si="64">AX11-AX12-AX13</f>
+        <v>1292.4711446947003</v>
+      </c>
+      <c r="AY14" s="7">
         <f t="shared" si="64"/>
-        <v>1009.8999999999994</v>
-      </c>
-      <c r="AQ14" s="7">
+        <v>1313.0875364909693</v>
+      </c>
+      <c r="AZ14" s="7">
         <f t="shared" si="64"/>
-        <v>984.13692099999992</v>
-      </c>
-      <c r="AR14" s="7">
-        <f t="shared" si="64"/>
-        <v>1020.4692323920002</v>
-      </c>
-      <c r="AS14" s="7">
-        <f t="shared" si="64"/>
-        <v>1013.2984622599199</v>
-      </c>
-      <c r="AT14" s="7">
-        <f t="shared" si="64"/>
-        <v>1012.8674818394792</v>
-      </c>
-      <c r="AU14" s="7">
-        <f t="shared" si="64"/>
-        <v>1022.9961566578743</v>
-      </c>
-      <c r="AV14" s="7">
-        <f t="shared" si="64"/>
-        <v>1033.2261182244526</v>
-      </c>
-      <c r="AW14" s="7">
-        <f t="shared" si="64"/>
-        <v>1043.5583794066972</v>
-      </c>
-      <c r="AX14" s="7">
-        <f t="shared" ref="AX14:AZ14" si="65">AX11-AX12-AX13</f>
-        <v>1053.993963200764</v>
-      </c>
-      <c r="AY14" s="7">
-        <f t="shared" si="65"/>
-        <v>1064.5339028327717</v>
-      </c>
-      <c r="AZ14" s="7">
-        <f t="shared" si="65"/>
-        <v>1075.1792418610989</v>
+        <v>1334.1408426156804</v>
       </c>
       <c r="BA14" s="1">
         <f>AZ14*(1+$BC$20)</f>
-        <v>1064.4274494424878</v>
+        <v>1320.7994341895237</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" ref="BB14:DM14" si="66">BA14*(1+$BC$20)</f>
-        <v>1053.7831749480629</v>
+        <f t="shared" ref="BB14:DM14" si="65">BA14*(1+$BC$20)</f>
+        <v>1307.5914398476284</v>
       </c>
       <c r="BC14" s="1">
+        <f t="shared" si="65"/>
+        <v>1294.5155254491522</v>
+      </c>
+      <c r="BD14" s="1">
+        <f t="shared" si="65"/>
+        <v>1281.5703701946607</v>
+      </c>
+      <c r="BE14" s="1">
+        <f t="shared" si="65"/>
+        <v>1268.754666492714</v>
+      </c>
+      <c r="BF14" s="1">
+        <f t="shared" si="65"/>
+        <v>1256.0671198277869</v>
+      </c>
+      <c r="BG14" s="1">
+        <f t="shared" si="65"/>
+        <v>1243.5064486295089</v>
+      </c>
+      <c r="BH14" s="1">
+        <f t="shared" si="65"/>
+        <v>1231.0713841432139</v>
+      </c>
+      <c r="BI14" s="1">
+        <f t="shared" si="65"/>
+        <v>1218.7606703017818</v>
+      </c>
+      <c r="BJ14" s="1">
+        <f t="shared" si="65"/>
+        <v>1206.5730635987641</v>
+      </c>
+      <c r="BK14" s="1">
+        <f t="shared" si="65"/>
+        <v>1194.5073329627764</v>
+      </c>
+      <c r="BL14" s="1">
+        <f t="shared" si="65"/>
+        <v>1182.5622596331486</v>
+      </c>
+      <c r="BM14" s="1">
+        <f t="shared" si="65"/>
+        <v>1170.7366370368172</v>
+      </c>
+      <c r="BN14" s="1">
+        <f t="shared" si="65"/>
+        <v>1159.0292706664491</v>
+      </c>
+      <c r="BO14" s="1">
+        <f t="shared" si="65"/>
+        <v>1147.4389779597846</v>
+      </c>
+      <c r="BP14" s="1">
+        <f t="shared" si="65"/>
+        <v>1135.9645881801866</v>
+      </c>
+      <c r="BQ14" s="1">
+        <f t="shared" si="65"/>
+        <v>1124.6049422983847</v>
+      </c>
+      <c r="BR14" s="1">
+        <f t="shared" si="65"/>
+        <v>1113.3588928754009</v>
+      </c>
+      <c r="BS14" s="1">
+        <f t="shared" si="65"/>
+        <v>1102.2253039466468</v>
+      </c>
+      <c r="BT14" s="1">
+        <f t="shared" si="65"/>
+        <v>1091.2030509071803</v>
+      </c>
+      <c r="BU14" s="1">
+        <f t="shared" si="65"/>
+        <v>1080.2910203981085</v>
+      </c>
+      <c r="BV14" s="1">
+        <f t="shared" si="65"/>
+        <v>1069.4881101941273</v>
+      </c>
+      <c r="BW14" s="1">
+        <f t="shared" si="65"/>
+        <v>1058.793229092186</v>
+      </c>
+      <c r="BX14" s="1">
+        <f t="shared" si="65"/>
+        <v>1048.2052968012642</v>
+      </c>
+      <c r="BY14" s="1">
+        <f t="shared" si="65"/>
+        <v>1037.7232438332517</v>
+      </c>
+      <c r="BZ14" s="1">
+        <f t="shared" si="65"/>
+        <v>1027.3460113949191</v>
+      </c>
+      <c r="CA14" s="1">
+        <f t="shared" si="65"/>
+        <v>1017.0725512809698</v>
+      </c>
+      <c r="CB14" s="1">
+        <f t="shared" si="65"/>
+        <v>1006.9018257681602</v>
+      </c>
+      <c r="CC14" s="1">
+        <f t="shared" si="65"/>
+        <v>996.83280751047857</v>
+      </c>
+      <c r="CD14" s="1">
+        <f t="shared" si="65"/>
+        <v>986.86447943537382</v>
+      </c>
+      <c r="CE14" s="1">
+        <f t="shared" si="65"/>
+        <v>976.99583464102011</v>
+      </c>
+      <c r="CF14" s="1">
+        <f t="shared" si="65"/>
+        <v>967.22587629460986</v>
+      </c>
+      <c r="CG14" s="1">
+        <f t="shared" si="65"/>
+        <v>957.5536175316638</v>
+      </c>
+      <c r="CH14" s="1">
+        <f t="shared" si="65"/>
+        <v>947.97808135634716</v>
+      </c>
+      <c r="CI14" s="1">
+        <f t="shared" si="65"/>
+        <v>938.49830054278368</v>
+      </c>
+      <c r="CJ14" s="1">
+        <f t="shared" si="65"/>
+        <v>929.11331753735578</v>
+      </c>
+      <c r="CK14" s="1">
+        <f t="shared" si="65"/>
+        <v>919.82218436198218</v>
+      </c>
+      <c r="CL14" s="1">
+        <f t="shared" si="65"/>
+        <v>910.6239625183623</v>
+      </c>
+      <c r="CM14" s="1">
+        <f t="shared" si="65"/>
+        <v>901.51772289317864</v>
+      </c>
+      <c r="CN14" s="1">
+        <f t="shared" si="65"/>
+        <v>892.5025456642469</v>
+      </c>
+      <c r="CO14" s="1">
+        <f t="shared" si="65"/>
+        <v>883.57752020760438</v>
+      </c>
+      <c r="CP14" s="1">
+        <f t="shared" si="65"/>
+        <v>874.74174500552829</v>
+      </c>
+      <c r="CQ14" s="1">
+        <f t="shared" si="65"/>
+        <v>865.99432755547298</v>
+      </c>
+      <c r="CR14" s="1">
+        <f t="shared" si="65"/>
+        <v>857.33438427991825</v>
+      </c>
+      <c r="CS14" s="1">
+        <f t="shared" si="65"/>
+        <v>848.76104043711905</v>
+      </c>
+      <c r="CT14" s="1">
+        <f t="shared" si="65"/>
+        <v>840.2734300327478</v>
+      </c>
+      <c r="CU14" s="1">
+        <f t="shared" si="65"/>
+        <v>831.87069573242036</v>
+      </c>
+      <c r="CV14" s="1">
+        <f t="shared" si="65"/>
+        <v>823.55198877509611</v>
+      </c>
+      <c r="CW14" s="1">
+        <f t="shared" si="65"/>
+        <v>815.31646888734508</v>
+      </c>
+      <c r="CX14" s="1">
+        <f t="shared" si="65"/>
+        <v>807.16330419847168</v>
+      </c>
+      <c r="CY14" s="1">
+        <f t="shared" si="65"/>
+        <v>799.091671156487</v>
+      </c>
+      <c r="CZ14" s="1">
+        <f t="shared" si="65"/>
+        <v>791.10075444492213</v>
+      </c>
+      <c r="DA14" s="1">
+        <f t="shared" si="65"/>
+        <v>783.18974690047287</v>
+      </c>
+      <c r="DB14" s="1">
+        <f t="shared" si="65"/>
+        <v>775.35784943146814</v>
+      </c>
+      <c r="DC14" s="1">
+        <f t="shared" si="65"/>
+        <v>767.6042709371535</v>
+      </c>
+      <c r="DD14" s="1">
+        <f t="shared" si="65"/>
+        <v>759.92822822778191</v>
+      </c>
+      <c r="DE14" s="1">
+        <f t="shared" si="65"/>
+        <v>752.32894594550407</v>
+      </c>
+      <c r="DF14" s="1">
+        <f t="shared" si="65"/>
+        <v>744.80565648604897</v>
+      </c>
+      <c r="DG14" s="1">
+        <f t="shared" si="65"/>
+        <v>737.35759992118847</v>
+      </c>
+      <c r="DH14" s="1">
+        <f t="shared" si="65"/>
+        <v>729.98402392197659</v>
+      </c>
+      <c r="DI14" s="1">
+        <f t="shared" si="65"/>
+        <v>722.68418368275684</v>
+      </c>
+      <c r="DJ14" s="1">
+        <f t="shared" si="65"/>
+        <v>715.45734184592925</v>
+      </c>
+      <c r="DK14" s="1">
+        <f t="shared" si="65"/>
+        <v>708.30276842746991</v>
+      </c>
+      <c r="DL14" s="1">
+        <f t="shared" si="65"/>
+        <v>701.21974074319519</v>
+      </c>
+      <c r="DM14" s="1">
+        <f t="shared" si="65"/>
+        <v>694.20754333576326</v>
+      </c>
+      <c r="DN14" s="1">
+        <f t="shared" ref="DN14:FD14" si="66">DM14*(1+$BC$20)</f>
+        <v>687.26546790240559</v>
+      </c>
+      <c r="DO14" s="1">
         <f t="shared" si="66"/>
-        <v>1043.2453431985823</v>
-      </c>
-      <c r="BD14" s="1">
+        <v>680.39281322338149</v>
+      </c>
+      <c r="DP14" s="1">
         <f t="shared" si="66"/>
-        <v>1032.8128897665965</v>
-      </c>
-      <c r="BE14" s="1">
+        <v>673.58888509114763</v>
+      </c>
+      <c r="DQ14" s="1">
         <f t="shared" si="66"/>
-        <v>1022.4847608689306</v>
-      </c>
-      <c r="BF14" s="1">
+        <v>666.85299624023617</v>
+      </c>
+      <c r="DR14" s="1">
         <f t="shared" si="66"/>
-        <v>1012.2599132602413</v>
-      </c>
-      <c r="BG14" s="1">
+        <v>660.18446627783385</v>
+      </c>
+      <c r="DS14" s="1">
         <f t="shared" si="66"/>
-        <v>1002.1373141276389</v>
-      </c>
-      <c r="BH14" s="1">
+        <v>653.58262161505547</v>
+      </c>
+      <c r="DT14" s="1">
         <f t="shared" si="66"/>
-        <v>992.11594098636249</v>
-      </c>
-      <c r="BI14" s="1">
+        <v>647.04679539890492</v>
+      </c>
+      <c r="DU14" s="1">
         <f t="shared" si="66"/>
-        <v>982.19478157649883</v>
-      </c>
-      <c r="BJ14" s="1">
+        <v>640.57632744491582</v>
+      </c>
+      <c r="DV14" s="1">
         <f t="shared" si="66"/>
-        <v>972.37283376073378</v>
-      </c>
-      <c r="BK14" s="1">
+        <v>634.1705641704666</v>
+      </c>
+      <c r="DW14" s="1">
         <f t="shared" si="66"/>
-        <v>962.64910542312646</v>
-      </c>
-      <c r="BL14" s="1">
+        <v>627.82885852876188</v>
+      </c>
+      <c r="DX14" s="1">
         <f t="shared" si="66"/>
-        <v>953.02261436889523</v>
-      </c>
-      <c r="BM14" s="1">
+        <v>621.55056994347422</v>
+      </c>
+      <c r="DY14" s="1">
         <f t="shared" si="66"/>
-        <v>943.49238822520624</v>
-      </c>
-      <c r="BN14" s="1">
+        <v>615.33506424403947</v>
+      </c>
+      <c r="DZ14" s="1">
         <f t="shared" si="66"/>
-        <v>934.05746434295418</v>
-      </c>
-      <c r="BO14" s="1">
+        <v>609.18171360159909</v>
+      </c>
+      <c r="EA14" s="1">
         <f t="shared" si="66"/>
-        <v>924.71688969952459</v>
-      </c>
-      <c r="BP14" s="1">
+        <v>603.08989646558314</v>
+      </c>
+      <c r="EB14" s="1">
         <f t="shared" si="66"/>
-        <v>915.46972080252931</v>
-      </c>
-      <c r="BQ14" s="1">
+        <v>597.05899750092726</v>
+      </c>
+      <c r="EC14" s="1">
         <f t="shared" si="66"/>
-        <v>906.31502359450405</v>
-      </c>
-      <c r="BR14" s="1">
+        <v>591.088407525918</v>
+      </c>
+      <c r="ED14" s="1">
         <f t="shared" si="66"/>
-        <v>897.25187335855901</v>
-      </c>
-      <c r="BS14" s="1">
+        <v>585.17752345065878</v>
+      </c>
+      <c r="EE14" s="1">
         <f t="shared" si="66"/>
-        <v>888.27935462497339</v>
-      </c>
-      <c r="BT14" s="1">
+        <v>579.32574821615219</v>
+      </c>
+      <c r="EF14" s="1">
         <f t="shared" si="66"/>
-        <v>879.39656107872361</v>
-      </c>
-      <c r="BU14" s="1">
+        <v>573.5324907339907</v>
+      </c>
+      <c r="EG14" s="1">
         <f t="shared" si="66"/>
-        <v>870.60259546793634</v>
-      </c>
-      <c r="BV14" s="1">
+        <v>567.79716582665083</v>
+      </c>
+      <c r="EH14" s="1">
         <f t="shared" si="66"/>
-        <v>861.89656951325696</v>
-      </c>
-      <c r="BW14" s="1">
+        <v>562.1191941683843</v>
+      </c>
+      <c r="EI14" s="1">
         <f t="shared" si="66"/>
-        <v>853.27760381812436</v>
-      </c>
-      <c r="BX14" s="1">
+        <v>556.49800222670046</v>
+      </c>
+      <c r="EJ14" s="1">
         <f t="shared" si="66"/>
-        <v>844.74482777994308</v>
-      </c>
-      <c r="BY14" s="1">
+        <v>550.93302220443343</v>
+      </c>
+      <c r="EK14" s="1">
         <f t="shared" si="66"/>
-        <v>836.2973795021436</v>
-      </c>
-      <c r="BZ14" s="1">
+        <v>545.42369198238907</v>
+      </c>
+      <c r="EL14" s="1">
         <f t="shared" si="66"/>
-        <v>827.93440570712221</v>
-      </c>
-      <c r="CA14" s="1">
+        <v>539.9694550625652</v>
+      </c>
+      <c r="EM14" s="1">
         <f t="shared" si="66"/>
-        <v>819.65506165005092</v>
-      </c>
-      <c r="CB14" s="1">
+        <v>534.56976051193953</v>
+      </c>
+      <c r="EN14" s="1">
         <f t="shared" si="66"/>
-        <v>811.45851103355039</v>
-      </c>
-      <c r="CC14" s="1">
+        <v>529.22406290682011</v>
+      </c>
+      <c r="EO14" s="1">
         <f t="shared" si="66"/>
-        <v>803.3439259232149</v>
-      </c>
-      <c r="CD14" s="1">
+        <v>523.93182227775185</v>
+      </c>
+      <c r="EP14" s="1">
         <f t="shared" si="66"/>
-        <v>795.31048666398272</v>
-      </c>
-      <c r="CE14" s="1">
+        <v>518.69250405497428</v>
+      </c>
+      <c r="EQ14" s="1">
         <f t="shared" si="66"/>
-        <v>787.3573817973429</v>
-      </c>
-      <c r="CF14" s="1">
+        <v>513.50557901442448</v>
+      </c>
+      <c r="ER14" s="1">
         <f t="shared" si="66"/>
-        <v>779.48380797936943</v>
-      </c>
-      <c r="CG14" s="1">
+        <v>508.37052322428025</v>
+      </c>
+      <c r="ES14" s="1">
         <f t="shared" si="66"/>
-        <v>771.68896989957568</v>
-      </c>
-      <c r="CH14" s="1">
+        <v>503.28681799203741</v>
+      </c>
+      <c r="ET14" s="1">
         <f t="shared" si="66"/>
-        <v>763.97208020057997</v>
-      </c>
-      <c r="CI14" s="1">
+        <v>498.25394981211701</v>
+      </c>
+      <c r="EU14" s="1">
         <f t="shared" si="66"/>
-        <v>756.33235939857411</v>
-      </c>
-      <c r="CJ14" s="1">
+        <v>493.27141031399583</v>
+      </c>
+      <c r="EV14" s="1">
         <f t="shared" si="66"/>
-        <v>748.76903580458838</v>
-      </c>
-      <c r="CK14" s="1">
+        <v>488.33869621085586</v>
+      </c>
+      <c r="EW14" s="1">
         <f t="shared" si="66"/>
-        <v>741.28134544654245</v>
-      </c>
-      <c r="CL14" s="1">
+        <v>483.45530924874731</v>
+      </c>
+      <c r="EX14" s="1">
         <f t="shared" si="66"/>
-        <v>733.86853199207701</v>
-      </c>
-      <c r="CM14" s="1">
+        <v>478.62075615625986</v>
+      </c>
+      <c r="EY14" s="1">
         <f t="shared" si="66"/>
-        <v>726.52984667215628</v>
-      </c>
-      <c r="CN14" s="1">
+        <v>473.83454859469725</v>
+      </c>
+      <c r="EZ14" s="1">
         <f t="shared" si="66"/>
-        <v>719.26454820543472</v>
-      </c>
-      <c r="CO14" s="1">
+        <v>469.09620310875027</v>
+      </c>
+      <c r="FA14" s="1">
         <f t="shared" si="66"/>
-        <v>712.07190272338039</v>
-      </c>
-      <c r="CP14" s="1">
+        <v>464.40524107766277</v>
+      </c>
+      <c r="FB14" s="1">
         <f t="shared" si="66"/>
-        <v>704.95118369614659</v>
-      </c>
-      <c r="CQ14" s="1">
+        <v>459.76118866688614</v>
+      </c>
+      <c r="FC14" s="1">
         <f t="shared" si="66"/>
-        <v>697.90167185918506</v>
-      </c>
-      <c r="CR14" s="1">
+        <v>455.16357678021728</v>
+      </c>
+      <c r="FD14" s="1">
         <f t="shared" si="66"/>
-        <v>690.92265514059318</v>
-      </c>
-      <c r="CS14" s="1">
-        <f t="shared" si="66"/>
-        <v>684.01342858918724</v>
-      </c>
-      <c r="CT14" s="1">
-        <f t="shared" si="66"/>
-        <v>677.17329430329539</v>
-      </c>
-      <c r="CU14" s="1">
-        <f t="shared" si="66"/>
-        <v>670.40156136026246</v>
-      </c>
-      <c r="CV14" s="1">
-        <f t="shared" si="66"/>
-        <v>663.69754574665978</v>
-      </c>
-      <c r="CW14" s="1">
-        <f t="shared" si="66"/>
-        <v>657.06057028919315</v>
-      </c>
-      <c r="CX14" s="1">
-        <f t="shared" si="66"/>
-        <v>650.4899645863012</v>
-      </c>
-      <c r="CY14" s="1">
-        <f t="shared" si="66"/>
-        <v>643.98506494043818</v>
-      </c>
-      <c r="CZ14" s="1">
-        <f t="shared" si="66"/>
-        <v>637.54521429103374</v>
-      </c>
-      <c r="DA14" s="1">
-        <f t="shared" si="66"/>
-        <v>631.16976214812337</v>
-      </c>
-      <c r="DB14" s="1">
-        <f t="shared" si="66"/>
-        <v>624.85806452664212</v>
-      </c>
-      <c r="DC14" s="1">
-        <f t="shared" si="66"/>
-        <v>618.6094838813757</v>
-      </c>
-      <c r="DD14" s="1">
-        <f t="shared" si="66"/>
-        <v>612.42338904256189</v>
-      </c>
-      <c r="DE14" s="1">
-        <f t="shared" si="66"/>
-        <v>606.29915515213622</v>
-      </c>
-      <c r="DF14" s="1">
-        <f t="shared" si="66"/>
-        <v>600.23616360061487</v>
-      </c>
-      <c r="DG14" s="1">
-        <f t="shared" si="66"/>
-        <v>594.23380196460869</v>
-      </c>
-      <c r="DH14" s="1">
-        <f t="shared" si="66"/>
-        <v>588.29146394496263</v>
-      </c>
-      <c r="DI14" s="1">
-        <f t="shared" si="66"/>
-        <v>582.40854930551302</v>
-      </c>
-      <c r="DJ14" s="1">
-        <f t="shared" si="66"/>
-        <v>576.5844638124579</v>
-      </c>
-      <c r="DK14" s="1">
-        <f t="shared" si="66"/>
-        <v>570.81861917433332</v>
-      </c>
-      <c r="DL14" s="1">
-        <f t="shared" si="66"/>
-        <v>565.11043298258994</v>
-      </c>
-      <c r="DM14" s="1">
-        <f t="shared" si="66"/>
-        <v>559.45932865276404</v>
-      </c>
-      <c r="DN14" s="1">
-        <f t="shared" ref="DN14:FD14" si="67">DM14*(1+$BC$20)</f>
-        <v>553.86473536623635</v>
-      </c>
-      <c r="DO14" s="1">
-        <f t="shared" si="67"/>
-        <v>548.32608801257402</v>
-      </c>
-      <c r="DP14" s="1">
-        <f t="shared" si="67"/>
-        <v>542.84282713244829</v>
-      </c>
-      <c r="DQ14" s="1">
-        <f t="shared" si="67"/>
-        <v>537.4143988611238</v>
-      </c>
-      <c r="DR14" s="1">
-        <f t="shared" si="67"/>
-        <v>532.04025487251261</v>
-      </c>
-      <c r="DS14" s="1">
-        <f t="shared" si="67"/>
-        <v>526.71985232378745</v>
-      </c>
-      <c r="DT14" s="1">
-        <f t="shared" si="67"/>
-        <v>521.45265380054957</v>
-      </c>
-      <c r="DU14" s="1">
-        <f t="shared" si="67"/>
-        <v>516.23812726254403</v>
-      </c>
-      <c r="DV14" s="1">
-        <f t="shared" si="67"/>
-        <v>511.07574598991857</v>
-      </c>
-      <c r="DW14" s="1">
-        <f t="shared" si="67"/>
-        <v>505.96498853001935</v>
-      </c>
-      <c r="DX14" s="1">
-        <f t="shared" si="67"/>
-        <v>500.90533864471917</v>
-      </c>
-      <c r="DY14" s="1">
-        <f t="shared" si="67"/>
-        <v>495.89628525827197</v>
-      </c>
-      <c r="DZ14" s="1">
-        <f t="shared" si="67"/>
-        <v>490.93732240568926</v>
-      </c>
-      <c r="EA14" s="1">
-        <f t="shared" si="67"/>
-        <v>486.02794918163238</v>
-      </c>
-      <c r="EB14" s="1">
-        <f t="shared" si="67"/>
-        <v>481.16766968981608</v>
-      </c>
-      <c r="EC14" s="1">
-        <f t="shared" si="67"/>
-        <v>476.35599299291789</v>
-      </c>
-      <c r="ED14" s="1">
-        <f t="shared" si="67"/>
-        <v>471.59243306298873</v>
-      </c>
-      <c r="EE14" s="1">
-        <f t="shared" si="67"/>
-        <v>466.87650873235884</v>
-      </c>
-      <c r="EF14" s="1">
-        <f t="shared" si="67"/>
-        <v>462.20774364503524</v>
-      </c>
-      <c r="EG14" s="1">
-        <f t="shared" si="67"/>
-        <v>457.58566620858488</v>
-      </c>
-      <c r="EH14" s="1">
-        <f t="shared" si="67"/>
-        <v>453.00980954649901</v>
-      </c>
-      <c r="EI14" s="1">
-        <f t="shared" si="67"/>
-        <v>448.47971145103401</v>
-      </c>
-      <c r="EJ14" s="1">
-        <f t="shared" si="67"/>
-        <v>443.99491433652366</v>
-      </c>
-      <c r="EK14" s="1">
-        <f t="shared" si="67"/>
-        <v>439.55496519315841</v>
-      </c>
-      <c r="EL14" s="1">
-        <f t="shared" si="67"/>
-        <v>435.15941554122685</v>
-      </c>
-      <c r="EM14" s="1">
-        <f t="shared" si="67"/>
-        <v>430.80782138581458</v>
-      </c>
-      <c r="EN14" s="1">
-        <f t="shared" si="67"/>
-        <v>426.49974317195642</v>
-      </c>
-      <c r="EO14" s="1">
-        <f t="shared" si="67"/>
-        <v>422.23474574023686</v>
-      </c>
-      <c r="EP14" s="1">
-        <f t="shared" si="67"/>
-        <v>418.01239828283451</v>
-      </c>
-      <c r="EQ14" s="1">
-        <f t="shared" si="67"/>
-        <v>413.83227430000613</v>
-      </c>
-      <c r="ER14" s="1">
-        <f t="shared" si="67"/>
-        <v>409.69395155700607</v>
-      </c>
-      <c r="ES14" s="1">
-        <f t="shared" si="67"/>
-        <v>405.59701204143602</v>
-      </c>
-      <c r="ET14" s="1">
-        <f t="shared" si="67"/>
-        <v>401.54104192102164</v>
-      </c>
-      <c r="EU14" s="1">
-        <f t="shared" si="67"/>
-        <v>397.5256315018114</v>
-      </c>
-      <c r="EV14" s="1">
-        <f t="shared" si="67"/>
-        <v>393.5503751867933</v>
-      </c>
-      <c r="EW14" s="1">
-        <f t="shared" si="67"/>
-        <v>389.61487143492536</v>
-      </c>
-      <c r="EX14" s="1">
-        <f t="shared" si="67"/>
-        <v>385.71872272057612</v>
-      </c>
-      <c r="EY14" s="1">
-        <f t="shared" si="67"/>
-        <v>381.86153549337035</v>
-      </c>
-      <c r="EZ14" s="1">
-        <f t="shared" si="67"/>
-        <v>378.04292013843667</v>
-      </c>
-      <c r="FA14" s="1">
-        <f t="shared" si="67"/>
-        <v>374.26249093705229</v>
-      </c>
-      <c r="FB14" s="1">
-        <f t="shared" si="67"/>
-        <v>370.51986602768176</v>
-      </c>
-      <c r="FC14" s="1">
-        <f t="shared" si="67"/>
-        <v>366.81466736740492</v>
-      </c>
-      <c r="FD14" s="1">
-        <f t="shared" si="67"/>
-        <v>363.14652069373085</v>
+        <v>450.61194101241512</v>
       </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.3">
@@ -3836,55 +3826,55 @@
         <v>287.60000000000002</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" ref="O15:AA15" si="68">263.6+45.7</f>
+        <f t="shared" ref="O15:AA15" si="67">263.6+45.7</f>
         <v>309.3</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="V15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="Z15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" si="68"/>
+        <f t="shared" si="67"/>
         <v>309.3</v>
       </c>
       <c r="AB15" s="3">
@@ -3899,20 +3889,20 @@
         <v>306.60000000000002</v>
       </c>
       <c r="AE15" s="3">
-        <f t="shared" ref="AE15:AH15" si="69">306.6</f>
-        <v>306.60000000000002</v>
+        <f>260.3+42.3</f>
+        <v>302.60000000000002</v>
       </c>
       <c r="AF15" s="3">
-        <f t="shared" si="69"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AG15" s="3">
-        <f t="shared" si="69"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AH15" s="3">
-        <f t="shared" si="69"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AJ15" s="3">
         <v>287.60000000000002</v>
@@ -3930,7 +3920,7 @@
         <v>287.60000000000002</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" ref="AO15" si="70">263.6+45.7</f>
+        <f t="shared" ref="AO15" si="68">263.6+45.7</f>
         <v>309.3</v>
       </c>
       <c r="AP15" s="3">
@@ -3938,44 +3928,44 @@
         <v>306.60000000000002</v>
       </c>
       <c r="AQ15" s="3">
-        <f>306.6</f>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AR15" s="3">
-        <f t="shared" ref="AR15:AZ15" si="71">306.6</f>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AS15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AT15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AU15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AV15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AW15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AX15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AY15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
       <c r="AZ15" s="3">
-        <f t="shared" si="71"/>
-        <v>306.60000000000002</v>
+        <f>266.5+32.8</f>
+        <v>299.3</v>
       </c>
     </row>
     <row r="16" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3983,132 +3973,132 @@
         <v>39</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:P16" si="72">C14/C15</f>
+        <f t="shared" ref="C16:P16" si="69">C14/C15</f>
         <v>-5.2155771905423795E-3</v>
       </c>
       <c r="D16" s="8">
+        <f t="shared" si="69"/>
+        <v>2.4339360222531284E-3</v>
+      </c>
+      <c r="E16" s="8">
+        <f t="shared" si="69"/>
+        <v>-2.0862308762169975E-3</v>
+      </c>
+      <c r="F16" s="8">
+        <f t="shared" si="69"/>
+        <v>6.9541029207232201E-3</v>
+      </c>
+      <c r="G16" s="8">
+        <f t="shared" si="69"/>
+        <v>1.0431154381085142E-3</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="69"/>
+        <v>1.9123783031988882E-2</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="69"/>
+        <v>7.9972183588316696E-3</v>
+      </c>
+      <c r="J16" s="8">
+        <f t="shared" si="69"/>
+        <v>5.3546592489568896E-2</v>
+      </c>
+      <c r="K16" s="8">
+        <f t="shared" si="69"/>
+        <v>9.4228094575799712E-2</v>
+      </c>
+      <c r="L16" s="8">
+        <f t="shared" si="69"/>
+        <v>0.64603616133518782</v>
+      </c>
+      <c r="M16" s="8">
+        <f t="shared" si="69"/>
+        <v>0.69019471488178019</v>
+      </c>
+      <c r="N16" s="8">
+        <f t="shared" si="69"/>
+        <v>0.90542420027816439</v>
+      </c>
+      <c r="O16" s="8">
+        <f t="shared" si="69"/>
+        <v>0.73520853540252185</v>
+      </c>
+      <c r="P16" s="8">
+        <f t="shared" si="69"/>
+        <v>1.0245716133204013</v>
+      </c>
+      <c r="Q16" s="8">
+        <f t="shared" ref="Q16" si="70">Q14/Q15</f>
+        <v>1.1002263174911087</v>
+      </c>
+      <c r="R16" s="8">
+        <f t="shared" ref="R16" si="71">R14/R15</f>
+        <v>1.5864856126737799</v>
+      </c>
+      <c r="S16" s="8">
+        <f t="shared" ref="S16:T16" si="72">S14/S15</f>
+        <v>0.36760426770126098</v>
+      </c>
+      <c r="T16" s="8">
         <f t="shared" si="72"/>
-        <v>2.4339360222531284E-3</v>
-      </c>
-      <c r="E16" s="8">
-        <f t="shared" si="72"/>
-        <v>-2.0862308762169975E-3</v>
-      </c>
-      <c r="F16" s="8">
-        <f t="shared" si="72"/>
-        <v>6.9541029207232201E-3</v>
-      </c>
-      <c r="G16" s="8">
-        <f t="shared" si="72"/>
-        <v>1.0431154381085142E-3</v>
-      </c>
-      <c r="H16" s="8">
-        <f t="shared" si="72"/>
-        <v>1.9123783031988882E-2</v>
-      </c>
-      <c r="I16" s="8">
-        <f t="shared" si="72"/>
-        <v>7.9972183588316696E-3</v>
-      </c>
-      <c r="J16" s="8">
-        <f t="shared" si="72"/>
-        <v>5.3546592489568896E-2</v>
-      </c>
-      <c r="K16" s="8">
-        <f t="shared" si="72"/>
-        <v>9.4228094575799712E-2</v>
-      </c>
-      <c r="L16" s="8">
-        <f t="shared" si="72"/>
-        <v>0.64603616133518782</v>
-      </c>
-      <c r="M16" s="8">
-        <f t="shared" si="72"/>
-        <v>0.69019471488178019</v>
-      </c>
-      <c r="N16" s="8">
-        <f t="shared" si="72"/>
-        <v>0.90542420027816439</v>
-      </c>
-      <c r="O16" s="8">
-        <f t="shared" si="72"/>
-        <v>0.73520853540252185</v>
-      </c>
-      <c r="P16" s="8">
-        <f t="shared" si="72"/>
-        <v>1.0245716133204013</v>
-      </c>
-      <c r="Q16" s="8">
-        <f t="shared" ref="Q16" si="73">Q14/Q15</f>
-        <v>1.1002263174911087</v>
-      </c>
-      <c r="R16" s="8">
-        <f t="shared" ref="R16" si="74">R14/R15</f>
-        <v>1.5864856126737799</v>
-      </c>
-      <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="75">S14/S15</f>
-        <v>0.36760426770126098</v>
-      </c>
-      <c r="T16" s="8">
+        <v>0.1480763013255737</v>
+      </c>
+      <c r="U16" s="8">
+        <f t="shared" ref="U16" si="73">U14/U15</f>
+        <v>0.15648237956676392</v>
+      </c>
+      <c r="V16" s="8">
+        <f t="shared" ref="V16" si="74">V14/V15</f>
+        <v>-0.33688975105076013</v>
+      </c>
+      <c r="W16" s="8">
+        <f t="shared" ref="W16:X16" si="75">W14/W15</f>
+        <v>5.0113158745554602E-2</v>
+      </c>
+      <c r="X16" s="8">
         <f t="shared" si="75"/>
-        <v>0.1480763013255737</v>
-      </c>
-      <c r="U16" s="8">
-        <f t="shared" ref="U16" si="76">U14/U15</f>
-        <v>0.15648237956676392</v>
-      </c>
-      <c r="V16" s="8">
-        <f t="shared" ref="V16" si="77">V14/V15</f>
-        <v>-0.33688975105076013</v>
-      </c>
-      <c r="W16" s="8">
-        <f t="shared" ref="W16:X16" si="78">W14/W15</f>
-        <v>5.0113158745554602E-2</v>
-      </c>
-      <c r="X16" s="8">
+        <v>0.58842547688328473</v>
+      </c>
+      <c r="Y16" s="8">
+        <f t="shared" ref="Y16" si="76">Y14/Y15</f>
+        <v>0.4565147106369225</v>
+      </c>
+      <c r="Z16" s="8">
+        <f t="shared" ref="Z16" si="77">Z14/Z15</f>
+        <v>0.96605237633365659</v>
+      </c>
+      <c r="AA16" s="8">
+        <f t="shared" ref="AA16:AD16" si="78">AA14/AA15</f>
+        <v>0.69932104752667335</v>
+      </c>
+      <c r="AB16" s="8">
         <f t="shared" si="78"/>
-        <v>0.58842547688328473</v>
-      </c>
-      <c r="Y16" s="8">
-        <f t="shared" ref="Y16" si="79">Y14/Y15</f>
-        <v>0.4565147106369225</v>
-      </c>
-      <c r="Z16" s="8">
-        <f t="shared" ref="Z16" si="80">Z14/Z15</f>
-        <v>0.96605237633365659</v>
-      </c>
-      <c r="AA16" s="8">
-        <f t="shared" ref="AA16:AD16" si="81">AA14/AA15</f>
-        <v>0.69932104752667335</v>
-      </c>
-      <c r="AB16" s="8">
-        <f t="shared" si="81"/>
         <v>0.71117608836907042</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>0.67284552845528478</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="81"/>
+        <f t="shared" si="78"/>
         <v>1.1996086105675143</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AH16" si="82">AE14/AE15</f>
-        <v>0.7740375733855186</v>
+        <f t="shared" ref="AE16:AH16" si="79">AE14/AE15</f>
+        <v>0.84137475214805046</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="82"/>
-        <v>0.81972235812133076</v>
+        <f t="shared" si="79"/>
+        <v>1.1987971934513868</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="82"/>
-        <v>0.75115704500978453</v>
+        <f t="shared" si="79"/>
+        <v>0.91985131974607426</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="82"/>
-        <v>0.86492294846705808</v>
+        <f t="shared" si="79"/>
+        <v>1.0113520347477443</v>
       </c>
       <c r="AJ16" s="8">
         <f>AJ14/AJ15</f>
@@ -4131,52 +4121,52 @@
         <v>0.36057023643950004</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" ref="AO16:AW16" si="83">AO14/AO15</f>
+        <f t="shared" ref="AO16:AW16" si="80">AO14/AO15</f>
         <v>2.0611057225994185</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" si="83"/>
+        <f t="shared" si="80"/>
         <v>3.2938682322243946</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.2098399249836915</v>
+        <f t="shared" si="80"/>
+        <v>3.9806520681590367</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.3283406144553167</v>
+        <f t="shared" si="80"/>
+        <v>4.0236905455128626</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.3049525840180034</v>
+        <f t="shared" si="80"/>
+        <v>4.0287086986392247</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.303546907499932</v>
+        <f t="shared" si="80"/>
+        <v>4.0566642252912359</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.3365823765749321</v>
+        <f t="shared" si="80"/>
+        <v>4.1200640060910239</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.3699482003406804</v>
+        <f t="shared" si="80"/>
+        <v>4.1847827788552152</v>
       </c>
       <c r="AW16" s="8">
-        <f t="shared" si="83"/>
-        <v>3.4036476823440873</v>
+        <f t="shared" si="80"/>
+        <v>4.2508542833281471</v>
       </c>
       <c r="AX16" s="8">
-        <f t="shared" ref="AX16:AZ16" si="84">AX14/AX15</f>
-        <v>3.4376841591675276</v>
+        <f t="shared" ref="AX16:AZ16" si="81">AX14/AX15</f>
+        <v>4.3183132131463422</v>
       </c>
       <c r="AY16" s="8">
-        <f t="shared" si="84"/>
-        <v>3.472061000759203</v>
+        <f t="shared" si="81"/>
+        <v>4.3871952438722666</v>
       </c>
       <c r="AZ16" s="8">
-        <f t="shared" si="84"/>
-        <v>3.5067816107667933</v>
+        <f t="shared" si="81"/>
+        <v>4.4575370618632819</v>
       </c>
     </row>
     <row r="18" spans="2:55" x14ac:dyDescent="0.3">
@@ -4192,112 +4182,112 @@
         <v>1.0299500831946755</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ref="H18:R18" si="85">H3/D3-1</f>
+        <f t="shared" ref="H18:R18" si="82">H3/D3-1</f>
         <v>0.95704697986577192</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.84905660377358494</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.77977315689981119</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>1.6901639344262294</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>3.5507544581618653</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>3.6650660264105648</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>3.6866702071163031</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>1.913467397928093</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.53956292388847027</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.35203293875450314</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="85"/>
+        <f t="shared" si="82"/>
         <v>0.2140509915014166</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18" si="86">S3/O3-1</f>
+        <f t="shared" ref="S18" si="83">S3/O3-1</f>
         <v>0.12298682284040985</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="87">T3/P3-1</f>
+        <f t="shared" ref="T18" si="84">T3/P3-1</f>
         <v>7.6358296622613731E-2</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="88">U3/Q3-1</f>
+        <f t="shared" ref="U18" si="85">U3/Q3-1</f>
         <v>4.8629615531024184E-2</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18" si="89">V3/R3-1</f>
+        <f t="shared" ref="V18" si="86">V3/R3-1</f>
         <v>4.3307821541907598E-2</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18" si="90">W3/S3-1</f>
+        <f t="shared" ref="W18" si="87">W3/S3-1</f>
         <v>2.942819891972448E-2</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="91">X3/T3-1</f>
+        <f t="shared" ref="X18" si="88">X3/T3-1</f>
         <v>3.565256934970451E-2</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="92">Y3/U3-1</f>
+        <f t="shared" ref="Y18" si="89">Y3/U3-1</f>
         <v>3.1581813231690736E-2</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="93">Z3/V3-1</f>
+        <f t="shared" ref="Z18" si="90">Z3/V3-1</f>
         <v>2.5675433887994314E-2</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18" si="94">AA3/W3-1</f>
+        <f t="shared" ref="AA18" si="91">AA3/W3-1</f>
         <v>3.2386466437488659E-2</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18" si="95">AB3/X3-1</f>
+        <f t="shared" ref="AB18" si="92">AB3/X3-1</f>
         <v>2.0901027487485679E-2</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="96">AC3/Y3-1</f>
+        <f t="shared" ref="AC18" si="93">AC3/Y3-1</f>
         <v>3.589337556083394E-2</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="97">AD3/Z3-1</f>
+        <f t="shared" ref="AD18" si="94">AD3/Z3-1</f>
         <v>3.2795464457043177E-2</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18" si="98">AE3/AA3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AE18" si="95">AE3/AA3-1</f>
+        <v>2.9355064844023726E-2</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18" si="99">AF3/AB3-1</f>
-        <v>3.0000000000000027E-2</v>
+        <f t="shared" ref="AF18" si="96">AF3/AB3-1</f>
+        <v>4.7053763440860319E-2</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" ref="AG18" si="100">AG3/AC3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AG18" si="97">AG3/AC3-1</f>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" ref="AH18" si="101">AH3/AD3-1</f>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" ref="AH18" si="98">AH3/AD3-1</f>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9">
@@ -4305,63 +4295,63 @@
         <v>0.88411497730711064</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" ref="AL18:AW18" si="102">AL3/AK3-1</f>
+        <f t="shared" ref="AL18:AW18" si="99">AL3/AK3-1</f>
         <v>3.2579091055082703</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>0.54631515425812749</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>7.1489548525573987E-2</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>3.0571363532893248E-2</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>3.0481744085878892E-2</v>
       </c>
       <c r="AQ18" s="9">
-        <f t="shared" si="102"/>
-        <v>2.4937946112790321E-2</v>
+        <f t="shared" si="99"/>
+        <v>4.9277859944698132E-2</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" si="102"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="99"/>
+        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="99"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" ref="AX18" si="103">AX3/AW3-1</f>
+        <f t="shared" ref="AX18" si="100">AX3/AW3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" ref="AY18" si="104">AY3/AX3-1</f>
+        <f t="shared" ref="AY18" si="101">AY3/AX3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" ref="AZ18" si="105">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ18" si="102">AZ3/AY3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4370,19 +4360,19 @@
         <v>41</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:F19" si="106">C5/C3</f>
+        <f t="shared" ref="C19:F19" si="103">C5/C3</f>
         <v>0.80532445923460905</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="103"/>
         <v>0.82550335570469802</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="103"/>
         <v>0.81354051054384025</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="103"/>
         <v>0.81568998109640833</v>
       </c>
       <c r="G19" s="9">
@@ -4390,179 +4380,179 @@
         <v>0.80245901639344264</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:R19" si="107">H5/H3</f>
+        <f t="shared" ref="H19:R19" si="104">H5/H3</f>
         <v>0.8086419753086419</v>
       </c>
       <c r="I19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.81512605042016795</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.82740308019118425</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.68403412553321152</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.71017332328560656</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.66713844570252179</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.69711048158640232</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.72286132608240961</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.74419970631424381</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.74210125618576317</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" si="104"/>
+        <v>0.75984692925144681</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" ref="S19:AD19" si="105">S5/S3</f>
+        <v>0.75619295958279009</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.75115961800818554</v>
+      </c>
+      <c r="U19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.75433342408567017</v>
+      </c>
+      <c r="V19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.73662551440329216</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.76126289126108204</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.7658733643628699</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.76159056919151935</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.75900566942869607</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.76051524710830709</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.754752688172043</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.75889596602972398</v>
+      </c>
+      <c r="AD19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.75728401317456295</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" ref="AE19:AH19" si="106">AE5/AE3</f>
+        <v>0.76300331999659488</v>
+      </c>
+      <c r="AF19" s="9">
+        <f t="shared" si="106"/>
+        <v>0.77555044364114356</v>
+      </c>
+      <c r="AG19" s="9">
+        <f t="shared" si="106"/>
+        <v>0.76</v>
+      </c>
+      <c r="AH19" s="9">
+        <f t="shared" si="106"/>
+        <v>0.76</v>
+      </c>
+      <c r="AJ19" s="9">
+        <f t="shared" ref="AJ19:AW19" si="107">AJ5/AJ3</f>
+        <v>0.81543116490166412</v>
+      </c>
+      <c r="AK19" s="9">
         <f t="shared" si="107"/>
-        <v>0.81512605042016795</v>
-      </c>
-      <c r="J19" s="9">
+        <v>0.81483860607033887</v>
+      </c>
+      <c r="AL19" s="9">
         <f t="shared" si="107"/>
-        <v>0.82740308019118425</v>
-      </c>
-      <c r="K19" s="9">
+        <v>0.68997510749038249</v>
+      </c>
+      <c r="AM19" s="9">
         <f t="shared" si="107"/>
-        <v>0.68403412553321152</v>
-      </c>
-      <c r="L19" s="9">
+        <v>0.74277421400521959</v>
+      </c>
+      <c r="AN19" s="9">
         <f t="shared" si="107"/>
-        <v>0.71017332328560656</v>
-      </c>
-      <c r="M19" s="9">
+        <v>0.74948782153425908</v>
+      </c>
+      <c r="AO19" s="9">
         <f t="shared" si="107"/>
-        <v>0.66713844570252179</v>
-      </c>
-      <c r="N19" s="9">
+        <v>0.76193316104521458</v>
+      </c>
+      <c r="AP19" s="9">
         <f t="shared" si="107"/>
-        <v>0.69711048158640232</v>
-      </c>
-      <c r="O19" s="9">
+        <v>0.75785051336462816</v>
+      </c>
+      <c r="AQ19" s="9">
         <f t="shared" si="107"/>
-        <v>0.72286132608240961</v>
-      </c>
-      <c r="P19" s="9">
+        <v>0.76458735462277716</v>
+      </c>
+      <c r="AR19" s="9">
         <f t="shared" si="107"/>
-        <v>0.74419970631424381</v>
-      </c>
-      <c r="Q19" s="9">
+        <v>0.76</v>
+      </c>
+      <c r="AS19" s="9">
         <f t="shared" si="107"/>
-        <v>0.74210125618576317</v>
-      </c>
-      <c r="R19" s="9">
+        <v>0.76</v>
+      </c>
+      <c r="AT19" s="9">
         <f t="shared" si="107"/>
-        <v>0.75984692925144681</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" ref="S19:AD19" si="108">S5/S3</f>
-        <v>0.75619295958279009</v>
-      </c>
-      <c r="T19" s="9">
+        <v>0.76</v>
+      </c>
+      <c r="AU19" s="9">
+        <f t="shared" si="107"/>
+        <v>0.76</v>
+      </c>
+      <c r="AV19" s="9">
+        <f t="shared" si="107"/>
+        <v>0.76</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" si="107"/>
+        <v>0.76</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" ref="AX19:AZ19" si="108">AX5/AX3</f>
+        <v>0.76</v>
+      </c>
+      <c r="AY19" s="9">
         <f t="shared" si="108"/>
-        <v>0.75115961800818554</v>
-      </c>
-      <c r="U19" s="9">
+        <v>0.76000000000000012</v>
+      </c>
+      <c r="AZ19" s="9">
         <f t="shared" si="108"/>
-        <v>0.75433342408567017</v>
-      </c>
-      <c r="V19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.73662551440329216</v>
-      </c>
-      <c r="W19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.76126289126108204</v>
-      </c>
-      <c r="X19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.7658733643628699</v>
-      </c>
-      <c r="Y19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.76159056919151935</v>
-      </c>
-      <c r="Z19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.75900566942869607</v>
-      </c>
-      <c r="AA19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.76051524710830709</v>
-      </c>
-      <c r="AB19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.754752688172043</v>
-      </c>
-      <c r="AC19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.75889596602972398</v>
-      </c>
-      <c r="AD19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.75728401317456295</v>
-      </c>
-      <c r="AE19" s="9">
-        <f t="shared" ref="AE19:AH19" si="109">AE5/AE3</f>
-        <v>0.76</v>
-      </c>
-      <c r="AF19" s="9">
-        <f t="shared" si="109"/>
-        <v>0.76</v>
-      </c>
-      <c r="AG19" s="9">
-        <f t="shared" si="109"/>
-        <v>0.76</v>
-      </c>
-      <c r="AH19" s="9">
-        <f t="shared" si="109"/>
-        <v>0.76</v>
-      </c>
-      <c r="AJ19" s="9">
-        <f t="shared" ref="AJ19:AW19" si="110">AJ5/AJ3</f>
-        <v>0.81543116490166412</v>
-      </c>
-      <c r="AK19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.81483860607033887</v>
-      </c>
-      <c r="AL19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.68997510749038249</v>
-      </c>
-      <c r="AM19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.74277421400521959</v>
-      </c>
-      <c r="AN19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.74948782153425908</v>
-      </c>
-      <c r="AO19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76193316104521458</v>
-      </c>
-      <c r="AP19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.75785051336462816</v>
-      </c>
-      <c r="AQ19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AR19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AS19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="110"/>
-        <v>0.76</v>
-      </c>
-      <c r="AX19" s="9">
-        <f t="shared" ref="AX19:AZ19" si="111">AX5/AX3</f>
-        <v>0.76</v>
-      </c>
-      <c r="AY19" s="9">
-        <f t="shared" si="111"/>
-        <v>0.76</v>
-      </c>
-      <c r="AZ19" s="9">
-        <f t="shared" si="111"/>
         <v>0.76</v>
       </c>
     </row>
@@ -4571,19 +4561,19 @@
         <v>42</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:F20" si="112">C9/C3</f>
+        <f t="shared" ref="C20:F20" si="109">C9/C3</f>
         <v>-2.9950083194675344E-2</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v>4.6979865771812082E-2</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v>-1.2208657047724846E-2</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="109"/>
         <v>5.1984877126654047E-2</v>
       </c>
       <c r="G20" s="9">
@@ -4591,180 +4581,180 @@
         <v>1.3114754098360725E-2</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ref="H20:R20" si="113">H9/H3</f>
+        <f t="shared" ref="H20:R20" si="110">H9/H3</f>
         <v>1.5089163237311404E-2</v>
       </c>
       <c r="I20" s="9">
+        <f t="shared" si="110"/>
+        <v>-9.6038415366147181E-3</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="110"/>
+        <v>5.629314922995228E-2</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="110"/>
+        <v>7.1297989031078604E-2</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.28349660889223816</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.2474266598044261</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.29019830028328619</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.23656138883078853</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.28839941262848767</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.27683669585078036</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="110"/>
+        <v>0.23511293634496933</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" ref="S20:AD20" si="111">S9/S3</f>
+        <v>0.1742410132240641</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.11068667576170983</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="111"/>
+        <v>6.0441056357201269E-2</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="111"/>
+        <v>-0.11629987475398114</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="111"/>
+        <v>8.8655690247874432E-3</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.15596733116712036</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.14902788774522752</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.14696903619712173</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.1778829302488609</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.174021505376344</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.15524416135881108</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.19001773498859889</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="112">AE9/AE3</f>
+        <v>0.20566953264663324</v>
+      </c>
+      <c r="AF20" s="9">
+        <f t="shared" si="112"/>
+        <v>0.26429510351626689</v>
+      </c>
+      <c r="AG20" s="9">
+        <f t="shared" si="112"/>
+        <v>0.21398229379481631</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="112"/>
+        <v>0.22178462107197078</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" ref="AJ20:AW20" si="113">AJ9/AJ3</f>
+        <v>1.8456883509833568E-2</v>
+      </c>
+      <c r="AK20" s="9">
         <f t="shared" si="113"/>
-        <v>-9.6038415366147181E-3</v>
-      </c>
-      <c r="J20" s="9">
+        <v>2.0555644772763743E-2</v>
+      </c>
+      <c r="AL20" s="9">
         <f t="shared" si="113"/>
-        <v>5.629314922995228E-2</v>
-      </c>
-      <c r="K20" s="9">
+        <v>0.2488873802519424</v>
+      </c>
+      <c r="AM20" s="9">
         <f t="shared" si="113"/>
-        <v>7.1297989031078604E-2</v>
-      </c>
-      <c r="L20" s="9">
+        <v>0.2594209614868655</v>
+      </c>
+      <c r="AN20" s="9">
         <f t="shared" si="113"/>
-        <v>0.28349660889223816</v>
-      </c>
-      <c r="M20" s="9">
+        <v>5.5861597996813159E-2</v>
+      </c>
+      <c r="AO20" s="9">
         <f t="shared" si="113"/>
-        <v>0.2474266598044261</v>
-      </c>
-      <c r="N20" s="9">
+        <v>0.11602942150950898</v>
+      </c>
+      <c r="AP20" s="9">
         <f t="shared" si="113"/>
-        <v>0.29019830028328619</v>
-      </c>
-      <c r="O20" s="9">
+        <v>0.17428675540694052</v>
+      </c>
+      <c r="AQ20" s="9">
         <f t="shared" si="113"/>
-        <v>0.23656138883078853</v>
-      </c>
-      <c r="P20" s="9">
+        <v>0.22649840374113722</v>
+      </c>
+      <c r="AR20" s="9">
         <f t="shared" si="113"/>
-        <v>0.28839941262848767</v>
-      </c>
-      <c r="Q20" s="9">
+        <v>0.22432043725817427</v>
+      </c>
+      <c r="AS20" s="9">
         <f t="shared" si="113"/>
-        <v>0.27683669585078036</v>
-      </c>
-      <c r="R20" s="9">
+        <v>0.22004498798816341</v>
+      </c>
+      <c r="AT20" s="9">
         <f t="shared" si="113"/>
-        <v>0.23511293634496933</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:AD20" si="114">S9/S3</f>
-        <v>0.1742410132240641</v>
-      </c>
-      <c r="T20" s="9">
+        <v>0.21747117598804627</v>
+      </c>
+      <c r="AU20" s="9">
+        <f t="shared" si="113"/>
+        <v>0.21747117598804624</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" si="113"/>
+        <v>0.21747117598804616</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" si="113"/>
+        <v>0.21747117598804611</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" ref="AX20:AZ20" si="114">AX9/AX3</f>
+        <v>0.21747117598804619</v>
+      </c>
+      <c r="AY20" s="9">
         <f t="shared" si="114"/>
-        <v>0.11068667576170983</v>
-      </c>
-      <c r="U20" s="9">
+        <v>0.21747117598804624</v>
+      </c>
+      <c r="AZ20" s="9">
         <f t="shared" si="114"/>
-        <v>6.0441056357201269E-2</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="114"/>
-        <v>-0.11629987475398114</v>
-      </c>
-      <c r="W20" s="9">
-        <f t="shared" si="114"/>
-        <v>8.8655690247874432E-3</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.15596733116712036</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.14902788774522752</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.14696903619712173</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.1778829302488609</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.174021505376344</v>
-      </c>
-      <c r="AC20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.15524416135881108</v>
-      </c>
-      <c r="AD20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.19001773498859889</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="115">AE9/AE3</f>
-        <v>0.18412449508097423</v>
-      </c>
-      <c r="AF20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.19634826182273726</v>
-      </c>
-      <c r="AG20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.17240997460555341</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="115"/>
-        <v>0.19165852778067571</v>
-      </c>
-      <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20:AW20" si="116">AJ9/AJ3</f>
-        <v>1.8456883509833568E-2</v>
-      </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="116"/>
-        <v>2.0555644772763743E-2</v>
-      </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.2488873802519424</v>
-      </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.2594209614868655</v>
-      </c>
-      <c r="AN20" s="9">
-        <f t="shared" si="116"/>
-        <v>5.5861597996813159E-2</v>
-      </c>
-      <c r="AO20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.11602942150950898</v>
-      </c>
-      <c r="AP20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.17428675540694052</v>
-      </c>
-      <c r="AQ20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.18614601299176872</v>
-      </c>
-      <c r="AR20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.19246864461753044</v>
-      </c>
-      <c r="AS20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.18782751084680899</v>
-      </c>
-      <c r="AT20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.18503372382549027</v>
-      </c>
-      <c r="AU20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.18503372382549033</v>
-      </c>
-      <c r="AV20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.1850337238254903</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="116"/>
-        <v>0.1850337238254903</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" ref="AX20:AZ20" si="117">AX9/AX3</f>
-        <v>0.18503372382549024</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.18503372382549024</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="117"/>
-        <v>0.18503372382549016</v>
+        <v>0.21747117598804622</v>
       </c>
       <c r="BB20" t="s">
         <v>47</v>
@@ -4786,176 +4776,176 @@
         <v>1.1904761904761907</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:R21" si="118">H6/D6-1</f>
+        <f t="shared" ref="H21:R21" si="115">H6/D6-1</f>
         <v>1.1428571428571428</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0.97752808988764062</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0.91666666666666652</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0.9130434782608694</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.8466666666666667</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.4204545454545454</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.531400966183575</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.4696969696969697</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>0.92740046838407464</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.312206572769953</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="115"/>
         <v>1.2328244274809159</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21" si="119">S6/O6-1</f>
+        <f t="shared" ref="S21" si="116">S6/O6-1</f>
         <v>1.21319018404908</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21" si="120">T6/P6-1</f>
+        <f t="shared" ref="T21" si="117">T6/P6-1</f>
         <v>1.0972053462940461</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" ref="U21" si="121">U6/Q6-1</f>
+        <f t="shared" ref="U21" si="118">U6/Q6-1</f>
         <v>0.98883248730964479</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" ref="V21" si="122">V6/R6-1</f>
+        <f t="shared" ref="V21" si="119">V6/R6-1</f>
         <v>1.2333333333333334</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21" si="123">W6/S6-1</f>
+        <f t="shared" ref="W21" si="120">W6/S6-1</f>
         <v>0.45045045045045051</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" ref="X21" si="124">X6/T6-1</f>
+        <f t="shared" ref="X21" si="121">X6/T6-1</f>
         <v>0.11123986095017391</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21" si="125">Y6/U6-1</f>
+        <f t="shared" ref="Y21" si="122">Y6/U6-1</f>
         <v>4.5941807044411753E-3</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21" si="126">Z6/V6-1</f>
+        <f t="shared" ref="Z21" si="123">Z6/V6-1</f>
         <v>-0.21431305013394564</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" ref="AA21" si="127">AA6/W6-1</f>
+        <f t="shared" ref="AA21" si="124">AA6/W6-1</f>
         <v>-1.7677974199713398E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" ref="AB21" si="128">AB6/X6-1</f>
+        <f t="shared" ref="AB21" si="125">AB6/X6-1</f>
         <v>7.8206465067778952E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" ref="AC21" si="129">AC6/Y6-1</f>
+        <f t="shared" ref="AC21" si="126">AC6/Y6-1</f>
         <v>0.13313008130081294</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21" si="130">AD6/Z6-1</f>
+        <f t="shared" ref="AD21" si="127">AD6/Z6-1</f>
         <v>5.7476863127130962E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" ref="AE21" si="131">AE6/AA6-1</f>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" ref="AE21" si="128">AE6/AA6-1</f>
+        <v>-9.7276264591439343E-4</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" ref="AF21" si="132">AF6/AB6-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AF21" si="129">AF6/AB6-1</f>
+        <v>-1.9342359767892114E-3</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" ref="AG21" si="133">AG6/AC6-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AG21" si="130">AG6/AC6-1</f>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" ref="AH21" si="134">AH6/AD6-1</f>
+        <f t="shared" ref="AH21" si="131">AH6/AD6-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9">
-        <f t="shared" ref="AK21:AW21" si="135">AK6/AJ6-1</f>
+        <f t="shared" ref="AK21:AW21" si="132">AK6/AJ6-1</f>
         <v>1.0333333333333337</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.4456035767511173</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.2120658135283366</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.1325068870523411</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>3.7592042371786816E-2</v>
       </c>
       <c r="AP21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>6.1379482071713065E-2</v>
       </c>
       <c r="AQ21" s="9">
-        <f t="shared" si="135"/>
-        <v>5.1937829912023448E-2</v>
+        <f t="shared" si="132"/>
+        <v>1.7043988269793697E-3</v>
       </c>
       <c r="AR21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="132"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" ref="AX21" si="136">AX6/AW6-1</f>
+        <f t="shared" ref="AX21" si="133">AX6/AW6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" ref="AY21" si="137">AY6/AX6-1</f>
+        <f t="shared" ref="AY21" si="134">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" ref="AZ21" si="138">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ21" si="135">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" t="s">
@@ -4970,19 +4960,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="139">C7/C3</f>
+        <f t="shared" ref="C22:F22" si="136">C7/C3</f>
         <v>0.60399334442595665</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>0.55033557046979864</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>0.59378468368479476</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="139"/>
+        <f t="shared" si="136"/>
         <v>0.5207939508506616</v>
       </c>
       <c r="G22" s="9">
@@ -4990,187 +4980,187 @@
         <v>0.52459016393442626</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:R22" si="140">H7/H3</f>
+        <f t="shared" ref="H22:R22" si="137">H7/H3</f>
         <v>0.54663923182441698</v>
       </c>
       <c r="I22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.57623049219687872</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.53584705257567711</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.37050578915295551</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.23993971363978897</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.24472465259907356</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.24249291784702551</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.25695461200585651</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.26549192364170338</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.27950133231823371</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="137"/>
+        <v>0.303714765727086</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" ref="S22:AD22" si="138">S7/S3</f>
+        <v>0.33786552430620231</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.36425648021828105</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.38814774480442865</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.4523170513508678</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.38221458295639582</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.3279178010011416</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.32937450514647659</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.32368076755342351</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.3049421661409043</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.3086451612903226</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.30717622080679402</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.30309940038848071</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" ref="AE22:AH22" si="139">AE7/AE3</f>
+        <v>0.29539456882608323</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="139"/>
+        <v>0.27850805126519879</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="139"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AH22" s="9">
+        <f t="shared" si="139"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" ref="AJ22:AW22" si="140">AJ7/AJ3</f>
+        <v>0.562481089258699</v>
+      </c>
+      <c r="AK22" s="9">
         <f t="shared" si="140"/>
-        <v>0.57623049219687872</v>
-      </c>
-      <c r="J22" s="9">
+        <v>0.54697286012526092</v>
+      </c>
+      <c r="AL22" s="9">
         <f t="shared" si="140"/>
-        <v>0.53584705257567711</v>
-      </c>
-      <c r="K22" s="9">
+        <v>0.25835407709134794</v>
+      </c>
+      <c r="AM22" s="9">
         <f t="shared" si="140"/>
-        <v>0.37050578915295551</v>
-      </c>
-      <c r="L22" s="9">
+        <v>0.27707992877875071</v>
+      </c>
+      <c r="AN22" s="9">
         <f t="shared" si="140"/>
-        <v>0.23993971363978897</v>
-      </c>
-      <c r="M22" s="9">
+        <v>0.38620532665604368</v>
+      </c>
+      <c r="AO22" s="9">
         <f t="shared" si="140"/>
-        <v>0.24472465259907356</v>
-      </c>
-      <c r="N22" s="9">
+        <v>0.3404678285070572</v>
+      </c>
+      <c r="AP22" s="9">
         <f t="shared" si="140"/>
-        <v>0.24249291784702551</v>
-      </c>
-      <c r="O22" s="9">
+        <v>0.3059610314449232</v>
+      </c>
+      <c r="AQ22" s="9">
         <f t="shared" si="140"/>
-        <v>0.25695461200585651</v>
-      </c>
-      <c r="P22" s="9">
+        <v>0.28332325814941833</v>
+      </c>
+      <c r="AR22" s="9">
         <f t="shared" si="140"/>
-        <v>0.26549192364170338</v>
-      </c>
-      <c r="Q22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AS22" s="9">
         <f t="shared" si="140"/>
-        <v>0.27950133231823371</v>
-      </c>
-      <c r="R22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AT22" s="9">
         <f t="shared" si="140"/>
-        <v>0.303714765727086</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" ref="S22:AD22" si="141">S7/S3</f>
-        <v>0.33786552430620231</v>
-      </c>
-      <c r="T22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AU22" s="9">
+        <f t="shared" si="140"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" si="140"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" si="140"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AX22" s="9">
+        <f t="shared" ref="AX22:AZ22" si="141">AX7/AX3</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AY22" s="9">
         <f t="shared" si="141"/>
-        <v>0.36425648021828105</v>
-      </c>
-      <c r="U22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AZ22" s="9">
         <f t="shared" si="141"/>
-        <v>0.38814774480442865</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.4523170513508678</v>
-      </c>
-      <c r="W22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.38221458295639582</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.3279178010011416</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.32937450514647659</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.32368076755342351</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.3049421661409043</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.3086451612903226</v>
-      </c>
-      <c r="AC22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.30717622080679402</v>
-      </c>
-      <c r="AD22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.30309940038848071</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" ref="AE22:AH22" si="142">AE7/AE3</f>
-        <v>0.3</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="142"/>
-        <v>0.3</v>
-      </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="142"/>
-        <v>0.3</v>
-      </c>
-      <c r="AH22" s="9">
-        <f t="shared" si="142"/>
-        <v>0.3</v>
-      </c>
-      <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22:AW22" si="143">AJ7/AJ3</f>
-        <v>0.562481089258699</v>
-      </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.54697286012526092</v>
-      </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.25835407709134794</v>
-      </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.27707992877875071</v>
-      </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.38620532665604368</v>
-      </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.3404678285070572</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.3059610314449232</v>
-      </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.3</v>
-      </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" si="143"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AX22" s="9">
-        <f t="shared" ref="AX22:AZ22" si="144">AX7/AX3</f>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="144"/>
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="144"/>
-        <v>0.28999999999999998</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="BB22" t="s">
         <v>49</v>
       </c>
       <c r="BC22" s="3">
         <f>NPV(BC21,AQ14:FD14)</f>
-        <v>12368.960580152019</v>
+        <v>15126.360715129144</v>
       </c>
     </row>
     <row r="23" spans="2:55" x14ac:dyDescent="0.3">
@@ -5186,176 +5176,176 @@
         <v>1.4342105263157894</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:R23" si="145">H8/D8-1</f>
+        <f t="shared" ref="H23:R23" si="142">H8/D8-1</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>0.98333333333333339</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>0.58389261744966459</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>1.8702702702702703</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>2.8666666666666667</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>2.9243697478991599</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>2.9279661016949152</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>1.9020715630885121</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>0.38054187192118216</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>3.5331905781584627E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="145"/>
+        <f t="shared" si="142"/>
         <v>0.29234088457389418</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23" si="146">S8/O8-1</f>
+        <f t="shared" ref="S23" si="143">S8/O8-1</f>
         <v>-0.23556132381570405</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23" si="147">T8/P8-1</f>
+        <f t="shared" ref="T23" si="144">T8/P8-1</f>
         <v>0.16949152542372881</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" ref="U23" si="148">U8/Q8-1</f>
+        <f t="shared" ref="U23" si="145">U8/Q8-1</f>
         <v>0.45811789038262662</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23" si="149">V8/R8-1</f>
+        <f t="shared" ref="V23" si="146">V8/R8-1</f>
         <v>0.55676126878130217</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23" si="150">W8/S8-1</f>
+        <f t="shared" ref="W23" si="147">W8/S8-1</f>
         <v>0.69694397283531417</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" ref="X23" si="151">X8/T8-1</f>
+        <f t="shared" ref="X23" si="148">X8/T8-1</f>
         <v>-1.372997711670465E-2</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="152">Y8/U8-1</f>
+        <f t="shared" ref="Y23" si="149">Y8/U8-1</f>
         <v>-0.11276595744680851</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23" si="153">Z8/V8-1</f>
+        <f t="shared" ref="Z23" si="150">Z8/V8-1</f>
         <v>-0.32815013404825744</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" ref="AA23" si="154">AA8/W8-1</f>
+        <f t="shared" ref="AA23" si="151">AA8/W8-1</f>
         <v>-0.44322161080540268</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" ref="AB23" si="155">AB8/X8-1</f>
+        <f t="shared" ref="AB23" si="152">AB8/X8-1</f>
         <v>-0.15313225058004643</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" ref="AC23" si="156">AC8/Y8-1</f>
+        <f t="shared" ref="AC23" si="153">AC8/Y8-1</f>
         <v>7.9936051159072985E-3</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" ref="AD23" si="157">AD8/Z8-1</f>
+        <f t="shared" ref="AD23" si="154">AD8/Z8-1</f>
         <v>-0.23623304070231443</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" ref="AE23" si="158">AE8/AA8-1</f>
+        <f t="shared" ref="AE23" si="155">AE8/AA8-1</f>
+        <v>-8.0862533692722338E-2</v>
+      </c>
+      <c r="AF23" s="9">
+        <f t="shared" ref="AF23" si="156">AF8/AB8-1</f>
+        <v>-0.29771689497716891</v>
+      </c>
+      <c r="AG23" s="9">
+        <f t="shared" ref="AG23" si="157">AG8/AC8-1</f>
         <v>-9.9999999999999978E-2</v>
       </c>
-      <c r="AF23" s="9">
-        <f t="shared" ref="AF23" si="159">AF8/AB8-1</f>
-        <v>-9.9999999999999978E-2</v>
-      </c>
-      <c r="AG23" s="9">
-        <f t="shared" ref="AG23" si="160">AG8/AC8-1</f>
-        <v>-9.9999999999999978E-2</v>
-      </c>
       <c r="AH23" s="9">
-        <f t="shared" ref="AH23" si="161">AH8/AD8-1</f>
+        <f t="shared" ref="AH23" si="158">AH8/AD8-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ23" s="9"/>
       <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AW23" si="162">AK8/AJ8-1</f>
+        <f t="shared" ref="AK23:AW23" si="159">AK8/AJ8-1</f>
         <v>0.95280898876404496</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>2.6869965477560416</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>0.50655430711610472</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>0.19411642842345134</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>5.5517002081888478E-3</v>
       </c>
       <c r="AP23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>-0.23636991028295384</v>
       </c>
       <c r="AQ23" s="9">
-        <f t="shared" si="162"/>
-        <v>-6.7566651604157202E-2</v>
+        <f t="shared" si="159"/>
+        <v>-0.11166967916854942</v>
       </c>
       <c r="AR23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="162"/>
+        <f t="shared" si="159"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" ref="AX23" si="163">AX8/AW8-1</f>
+        <f t="shared" ref="AX23" si="160">AX8/AW8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" ref="AY23" si="164">AY8/AX8-1</f>
+        <f t="shared" ref="AY23" si="161">AY8/AX8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" ref="AZ23" si="165">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ23" si="162">AZ8/AY8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB23" t="s">
@@ -5363,7 +5353,7 @@
       </c>
       <c r="BC23" s="3">
         <f>Main!D8</f>
-        <v>8383.2000000000007</v>
+        <v>8426.6</v>
       </c>
     </row>
     <row r="24" spans="2:55" x14ac:dyDescent="0.3">
@@ -5371,19 +5361,19 @@
         <v>36</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:F24" si="166">C12/C11</f>
+        <f t="shared" ref="C24:F24" si="163">C12/C11</f>
         <v>-7.1428571428572021E-2</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="163"/>
         <v>2.4390243902439029E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="163"/>
         <v>-0.1999999999999966</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="166"/>
+        <f t="shared" si="163"/>
         <v>-6.557377049180331E-2</v>
       </c>
       <c r="G24" s="9">
@@ -5391,187 +5381,187 @@
         <v>0.115384615384615</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:R24" si="167">H12/H11</f>
+        <f t="shared" ref="H24:R24" si="164">H12/H11</f>
         <v>0.1791044776119402</v>
       </c>
       <c r="I24" s="9">
+        <f t="shared" si="164"/>
+        <v>0.1153846153846159</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="164"/>
+        <v>-5.4794520547945147E-2</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="164"/>
+        <v>7.1917808219178092E-2</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="164"/>
+        <v>2.2082018927444793E-2</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="164"/>
+        <v>-2.369912416280268E-2</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="164"/>
+        <v>1.5117157974300827E-2</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="164"/>
+        <v>6.1188811188811181E-3</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="164"/>
+        <v>2.0994133991972821E-2</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="164"/>
+        <v>0.17036314891542778</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="164"/>
+        <v>-2.5385724585436167</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" ref="S24:AD24" si="165">S12/S11</f>
+        <v>0.20876826722338201</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.49336283185840735</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.11678832116788304</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="165"/>
+        <v>-1.624685138539038</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.64203233256350978</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.27316293929712465</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.24004305705059187</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.1533012184754888</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.2592465753424657</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.25239071038251376</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.26186229040313946</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.18321119253830781</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" ref="AE24:AH24" si="166">AE12/AE11</f>
+        <v>0.19379354021532613</v>
+      </c>
+      <c r="AF24" s="9">
+        <f t="shared" si="166"/>
+        <v>0.19982158786797499</v>
+      </c>
+      <c r="AG24" s="9">
+        <f t="shared" si="166"/>
+        <v>0.25</v>
+      </c>
+      <c r="AH24" s="9">
+        <f t="shared" si="166"/>
+        <v>0.2</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" ref="AJ24:AW24" si="167">AJ12/AJ11</f>
+        <v>-1.2048192771084343E-2</v>
+      </c>
+      <c r="AK24" s="9">
         <f t="shared" si="167"/>
-        <v>0.1153846153846159</v>
-      </c>
-      <c r="J24" s="9">
+        <v>3.77358490566038E-2</v>
+      </c>
+      <c r="AL24" s="9">
         <f t="shared" si="167"/>
-        <v>-5.4794520547945147E-2</v>
-      </c>
-      <c r="K24" s="9">
+        <v>8.4058398466302902E-3</v>
+      </c>
+      <c r="AM24" s="9">
         <f t="shared" si="167"/>
-        <v>7.1917808219178092E-2</v>
-      </c>
-      <c r="L24" s="9">
+        <v>-0.2487065444313335</v>
+      </c>
+      <c r="AN24" s="9">
         <f t="shared" si="167"/>
-        <v>2.2082018927444793E-2</v>
-      </c>
-      <c r="M24" s="9">
+        <v>0.58386837881219855</v>
+      </c>
+      <c r="AO24" s="9">
         <f t="shared" si="167"/>
-        <v>-2.369912416280268E-2</v>
-      </c>
-      <c r="N24" s="9">
+        <v>0.23414223930802497</v>
+      </c>
+      <c r="AP24" s="9">
         <f t="shared" si="167"/>
-        <v>1.5117157974300827E-2</v>
-      </c>
-      <c r="O24" s="9">
+        <v>0.2322487456287062</v>
+      </c>
+      <c r="AQ24" s="9">
         <f t="shared" si="167"/>
-        <v>6.1188811188811181E-3</v>
-      </c>
-      <c r="P24" s="9">
+        <v>0.21080651535747846</v>
+      </c>
+      <c r="AR24" s="9">
         <f t="shared" si="167"/>
-        <v>2.0994133991972821E-2</v>
-      </c>
-      <c r="Q24" s="9">
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AS24" s="9">
         <f t="shared" si="167"/>
-        <v>0.17036314891542778</v>
-      </c>
-      <c r="R24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AT24" s="9">
         <f t="shared" si="167"/>
-        <v>-2.5385724585436167</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" ref="S24:AD24" si="168">S12/S11</f>
-        <v>0.20876826722338201</v>
-      </c>
-      <c r="T24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AU24" s="9">
+        <f t="shared" si="167"/>
+        <v>0.22</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="167"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="167"/>
+        <v>0.22000000000000003</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" ref="AX24:AZ24" si="168">AX12/AX11</f>
+        <v>0.22</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="168"/>
-        <v>0.49336283185840735</v>
-      </c>
-      <c r="U24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AZ24" s="9">
         <f t="shared" si="168"/>
-        <v>0.11678832116788304</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="168"/>
-        <v>-1.624685138539038</v>
-      </c>
-      <c r="W24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.64203233256350978</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.27316293929712465</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.24004305705059187</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.1533012184754888</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.2592465753424657</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.25239071038251376</v>
-      </c>
-      <c r="AC24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.26186229040313946</v>
-      </c>
-      <c r="AD24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.18321119253830781</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" ref="AE24:AH24" si="169">AE12/AE11</f>
-        <v>0.25</v>
-      </c>
-      <c r="AF24" s="9">
-        <f t="shared" si="169"/>
-        <v>0.25</v>
-      </c>
-      <c r="AG24" s="9">
-        <f t="shared" si="169"/>
-        <v>0.25</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="169"/>
-        <v>0.20000000000000004</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AW24" si="170">AJ12/AJ11</f>
-        <v>-1.2048192771084343E-2</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="170"/>
-        <v>3.77358490566038E-2</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="170"/>
-        <v>8.4058398466302902E-3</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="170"/>
-        <v>-0.2487065444313335</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.58386837881219855</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.23414223930802497</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.2322487456287062</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.23715270569481933</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.24</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.24000000000000002</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.23999999999999996</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.24</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.24</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="170"/>
-        <v>0.24000000000000002</v>
-      </c>
-      <c r="AX24" s="9">
-        <f t="shared" ref="AX24:AZ24" si="171">AX12/AX11</f>
-        <v>0.24</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="171"/>
-        <v>0.24</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="171"/>
-        <v>0.24</v>
+        <v>0.21999999999999997</v>
       </c>
       <c r="BB24" t="s">
         <v>51</v>
       </c>
       <c r="BC24" s="3">
         <f>BC22+BC23</f>
-        <v>20752.16058015202</v>
+        <v>23552.960715129142</v>
       </c>
     </row>
     <row r="25" spans="2:55" x14ac:dyDescent="0.3">
@@ -5579,19 +5569,19 @@
         <v>46</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:F25" si="172">C14/C3</f>
+        <f t="shared" ref="C25:F25" si="169">C14/C3</f>
         <v>-2.4958402662229425E-2</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>9.3959731543624119E-3</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>-6.6592674805772316E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="172"/>
+        <f t="shared" si="169"/>
         <v>1.8903591682419642E-2</v>
       </c>
       <c r="G25" s="9">
@@ -5599,187 +5589,187 @@
         <v>2.4590163934426943E-3</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:R25" si="173">H14/H3</f>
+        <f t="shared" ref="H25:R25" si="170">H14/H3</f>
         <v>3.7722908093278482E-2</v>
       </c>
       <c r="I25" s="9">
+        <f t="shared" si="170"/>
+        <v>1.3805522208883484E-2</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="170"/>
+        <v>8.1784386617100455E-2</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="170"/>
+        <v>8.2571602681291892E-2</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.28003014318010555</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.25540401441070509</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.29507082152974512</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.23781635641079271</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.31023005384238878</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.32384849638370761</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="170"/>
+        <v>0.45799887997013267</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AD25" si="171">S14/S3</f>
+        <v>0.10588563978394488</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="171"/>
+        <v>4.1655297862664802E-2</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="171"/>
+        <v>4.3924131046374514E-2</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="171"/>
+        <v>-9.3218822687421835E-2</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="171"/>
+        <v>1.4022073457571954E-2</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.15983138666900848</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.12421923110759227</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.26061927605756652</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.18953732912723453</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.18830107526881712</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.17571125265392787</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.31061565746136305</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="172">AE14/AE3</f>
+        <v>0.21673618796288421</v>
+      </c>
+      <c r="AF25" s="9">
+        <f t="shared" si="172"/>
+        <v>0.2947748931975025</v>
+      </c>
+      <c r="AG25" s="9">
+        <f t="shared" si="172"/>
+        <v>0.22057565196490805</v>
+      </c>
+      <c r="AH25" s="9">
+        <f t="shared" si="172"/>
+        <v>0.24116530188519891</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25:AW25" si="173">AJ14/AJ3</f>
+        <v>1.8154311649016442E-3</v>
+      </c>
+      <c r="AK25" s="9">
         <f t="shared" si="173"/>
-        <v>1.3805522208883484E-2</v>
-      </c>
-      <c r="J25" s="9">
+        <v>3.7738879074995957E-2</v>
+      </c>
+      <c r="AL25" s="9">
         <f t="shared" si="173"/>
-        <v>8.1784386617100455E-2</v>
-      </c>
-      <c r="K25" s="9">
+        <v>0.25337557516783588</v>
+      </c>
+      <c r="AM25" s="9">
         <f t="shared" si="173"/>
-        <v>8.2571602681291892E-2</v>
-      </c>
-      <c r="L25" s="9">
+        <v>0.33544720602941525</v>
+      </c>
+      <c r="AN25" s="9">
         <f t="shared" si="173"/>
-        <v>0.28003014318010555</v>
-      </c>
-      <c r="M25" s="9">
+        <v>2.3605736398816347E-2</v>
+      </c>
+      <c r="AO25" s="9">
         <f t="shared" si="173"/>
-        <v>0.25540401441070509</v>
-      </c>
-      <c r="N25" s="9">
+        <v>0.14081240474454976</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="173"/>
-        <v>0.29507082152974512</v>
-      </c>
-      <c r="O25" s="9">
+        <v>0.21647053780035572</v>
+      </c>
+      <c r="AQ25" s="9">
         <f t="shared" si="173"/>
-        <v>0.23781635641079271</v>
-      </c>
-      <c r="P25" s="9">
+        <v>0.24338334236259379</v>
+      </c>
+      <c r="AR25" s="9">
         <f t="shared" si="173"/>
-        <v>0.31023005384238878</v>
-      </c>
-      <c r="Q25" s="9">
+        <v>0.23884930360375423</v>
+      </c>
+      <c r="AS25" s="9">
         <f t="shared" si="173"/>
-        <v>0.32384849638370761</v>
-      </c>
-      <c r="R25" s="9">
+        <v>0.2367793910452721</v>
+      </c>
+      <c r="AT25" s="9">
         <f t="shared" si="173"/>
-        <v>0.45799887997013267</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AD25" si="174">S14/S3</f>
-        <v>0.10588563978394488</v>
-      </c>
-      <c r="T25" s="9">
+        <v>0.23606180383200254</v>
+      </c>
+      <c r="AU25" s="9">
+        <f t="shared" si="173"/>
+        <v>0.23737733425895949</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="173"/>
+        <v>0.23871891479338087</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="173"/>
+        <v>0.24008706127897894</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" ref="AX25:AZ25" si="174">AX14/AX3</f>
+        <v>0.24148229977419292</v>
+      </c>
+      <c r="AY25" s="9">
         <f t="shared" si="174"/>
-        <v>4.1655297862664802E-2</v>
-      </c>
-      <c r="U25" s="9">
+        <v>0.24290516675446064</v>
+      </c>
+      <c r="AZ25" s="9">
         <f t="shared" si="174"/>
-        <v>4.3924131046374514E-2</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="174"/>
-        <v>-9.3218822687421835E-2</v>
-      </c>
-      <c r="W25" s="9">
-        <f t="shared" si="174"/>
-        <v>1.4022073457571954E-2</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.15983138666900848</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.12421923110759227</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.26061927605756652</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.18953732912723453</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.18830107526881712</v>
-      </c>
-      <c r="AC25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.17571125265392787</v>
-      </c>
-      <c r="AD25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.31061565746136305</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="175">AE14/AE3</f>
-        <v>0.2018994824048268</v>
-      </c>
-      <c r="AF25" s="9">
-        <f t="shared" si="175"/>
-        <v>0.2098982148449734</v>
-      </c>
-      <c r="AG25" s="9">
-        <f t="shared" si="175"/>
-        <v>0.19175284126389405</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="175"/>
-        <v>0.2195639411748147</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25:AW25" si="176">AJ14/AJ3</f>
-        <v>1.8154311649016442E-3</v>
-      </c>
-      <c r="AK25" s="9">
-        <f t="shared" si="176"/>
-        <v>3.7738879074995957E-2</v>
-      </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.25337557516783588</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.33544720602941525</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="176"/>
-        <v>2.3605736398816347E-2</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.14081240474454976</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.21647053780035572</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20581564140191977</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20922934475803881</v>
-      </c>
-      <c r="AS25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20570208309229049</v>
-      </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20357880495608827</v>
-      </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20357880495608832</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20357880495608827</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="176"/>
-        <v>0.20357880495608827</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" ref="AX25:AZ25" si="177">AX14/AX3</f>
-        <v>0.20357880495608827</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="177"/>
-        <v>0.20357880495608827</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="177"/>
-        <v>0.20357880495608818</v>
+        <v>0.24435620931849594</v>
       </c>
       <c r="BB25" t="s">
         <v>53</v>
       </c>
       <c r="BC25" s="11">
         <f>BC24/AW15</f>
-        <v>67.684802935916565</v>
+        <v>78.693487187200603</v>
       </c>
     </row>
     <row r="26" spans="2:55" x14ac:dyDescent="0.3">
@@ -5788,7 +5778,7 @@
       </c>
       <c r="BC26" s="11">
         <f>Main!D3</f>
-        <v>73.25</v>
+        <v>80.599999999999994</v>
       </c>
     </row>
     <row r="27" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5800,7 +5790,7 @@
       </c>
       <c r="BC27" s="10">
         <f>BC25/BC26-1</f>
-        <v>-7.5975386540388157E-2</v>
+        <v>-2.3654005121580557E-2</v>
       </c>
     </row>
     <row r="28" spans="2:55" x14ac:dyDescent="0.3">

--- a/Financial Analysis/ZM.xlsx
+++ b/Financial Analysis/ZM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74CD4F6D-17AF-4E5D-B0D6-351CC4AB620E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F50CBC4-8D7A-4AE1-A609-5270D2CA265C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{961327DF-2131-4088-BB64-D1A8B8DD32EB}"/>
   </bookViews>
@@ -262,7 +262,7 @@
     <t>Q426</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -363,13 +363,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
+      <xdr:col>33</xdr:col>
       <xdr:colOff>15240</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
@@ -387,7 +387,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23561040" y="0"/>
+          <a:off x="24284940" y="0"/>
           <a:ext cx="0" cy="6316980"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -786,17 +786,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="11">
-        <v>80.599999999999994</v>
+        <v>84.96</v>
       </c>
       <c r="E3" s="5">
-        <v>45898</v>
+        <v>45990</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45898</v>
+        <v>45990</v>
       </c>
       <c r="G3" s="5">
-        <v>45985</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -804,11 +804,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f>265.6+30.5</f>
+        <v>296.10000000000002</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -817,7 +817,7 @@
       </c>
       <c r="D5" s="3">
         <f>D3*D4</f>
-        <v>24123.579999999998</v>
+        <v>25156.655999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -825,11 +825,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="3">
-        <f>1198.6+6580.1+647.9</f>
-        <v>8426.6</v>
+        <f>1215.9+6727.4+1052.6</f>
+        <v>8995.9</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -849,7 +849,7 @@
       </c>
       <c r="D8" s="3">
         <f>D6-D7</f>
-        <v>8426.6</v>
+        <v>8995.9</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -858,7 +858,7 @@
       </c>
       <c r="D9" s="3">
         <f>D5-D8</f>
-        <v>15696.979999999998</v>
+        <v>16160.755999999999</v>
       </c>
     </row>
   </sheetData>
@@ -876,7 +876,7 @@
     <col min="3" max="34" width="10.5546875" customWidth="1"/>
     <col min="36" max="52" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="54" max="54" width="12" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="16.88671875" customWidth="1"/>
+    <col min="55" max="55" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:160" x14ac:dyDescent="0.3">
@@ -1272,12 +1272,10 @@
         <v>1217.2</v>
       </c>
       <c r="AG3" s="7">
-        <f>AC3*1.06</f>
-        <v>1248.1500000000001</v>
+        <v>1229.8</v>
       </c>
       <c r="AH3" s="7">
-        <f>AD3*1.06</f>
-        <v>1255.146</v>
+        <v>1232.5</v>
       </c>
       <c r="AJ3" s="7">
         <f>SUM(C3:F3)</f>
@@ -1309,43 +1307,43 @@
       </c>
       <c r="AQ3" s="7">
         <f>SUM(AE3:AH3)</f>
-        <v>4895.1959999999999</v>
+        <v>4854.2</v>
       </c>
       <c r="AR3" s="7">
         <f>AQ3*1.03</f>
-        <v>5042.05188</v>
+        <v>4999.826</v>
       </c>
       <c r="AS3" s="7">
         <f>AR3*1.01</f>
-        <v>5092.4723987999996</v>
+        <v>5049.8242600000003</v>
       </c>
       <c r="AT3" s="7">
         <f t="shared" ref="AT3:AZ3" si="0">AS3*1.01</f>
-        <v>5143.3971227879993</v>
+        <v>5100.3225026</v>
       </c>
       <c r="AU3" s="7">
         <f t="shared" si="0"/>
-        <v>5194.831094015879</v>
+        <v>5151.3257276260001</v>
       </c>
       <c r="AV3" s="7">
         <f t="shared" si="0"/>
-        <v>5246.779404956038</v>
+        <v>5202.8389849022606</v>
       </c>
       <c r="AW3" s="7">
         <f t="shared" si="0"/>
-        <v>5299.2471990055983</v>
+        <v>5254.867374751283</v>
       </c>
       <c r="AX3" s="7">
         <f t="shared" si="0"/>
-        <v>5352.2396709956547</v>
+        <v>5307.416048498796</v>
       </c>
       <c r="AY3" s="7">
         <f t="shared" si="0"/>
-        <v>5405.7620677056111</v>
+        <v>5360.4902089837842</v>
       </c>
       <c r="AZ3" s="7">
         <f t="shared" si="0"/>
-        <v>5459.8196883826677</v>
+        <v>5414.0951110736223</v>
       </c>
     </row>
     <row r="4" spans="2:160" x14ac:dyDescent="0.3">
@@ -1443,12 +1441,11 @@
         <v>273.2</v>
       </c>
       <c r="AG4" s="3">
-        <f t="shared" ref="AF4:AH4" si="1">AG3-AG5</f>
-        <v>299.55600000000004</v>
+        <v>271.8</v>
       </c>
       <c r="AH4" s="3">
-        <f t="shared" si="1"/>
-        <v>301.23504000000003</v>
+        <f t="shared" ref="AH4" si="1">AH3-AH5</f>
+        <v>271.14999999999998</v>
       </c>
       <c r="AJ4" s="3">
         <f>SUM(C4:F4)</f>
@@ -1480,43 +1477,43 @@
       </c>
       <c r="AQ4" s="3">
         <f>SUM(AE4:AH4)</f>
-        <v>1152.39104</v>
+        <v>1094.5499999999997</v>
       </c>
       <c r="AR4" s="3">
         <f t="shared" ref="AR4:AW4" si="2">AR3-AR5</f>
-        <v>1210.0924512000001</v>
+        <v>1099.9617199999998</v>
       </c>
       <c r="AS4" s="3">
         <f t="shared" si="2"/>
-        <v>1222.193375712</v>
+        <v>1110.9613371999999</v>
       </c>
       <c r="AT4" s="3">
         <f t="shared" si="2"/>
-        <v>1234.4153094691196</v>
+        <v>1122.0709505719997</v>
       </c>
       <c r="AU4" s="3">
         <f t="shared" si="2"/>
-        <v>1246.7594625638108</v>
+        <v>1133.2916600777198</v>
       </c>
       <c r="AV4" s="3">
         <f t="shared" si="2"/>
-        <v>1259.2270571894492</v>
+        <v>1144.6245766784973</v>
       </c>
       <c r="AW4" s="3">
         <f t="shared" si="2"/>
-        <v>1271.8193277613436</v>
+        <v>1156.0708224452819</v>
       </c>
       <c r="AX4" s="3">
         <f t="shared" ref="AX4:AZ4" si="3">AX3-AX5</f>
-        <v>1284.537521038957</v>
+        <v>1167.6315306697352</v>
       </c>
       <c r="AY4" s="3">
         <f t="shared" si="3"/>
-        <v>1297.3828962493462</v>
+        <v>1179.307845976432</v>
       </c>
       <c r="AZ4" s="3">
         <f t="shared" si="3"/>
-        <v>1310.3567252118401</v>
+        <v>1191.1009244361967</v>
       </c>
     </row>
     <row r="5" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1620,7 +1617,7 @@
         <v>870.2</v>
       </c>
       <c r="AA5" s="7">
-        <f t="shared" ref="AA5:AF5" si="12">AA3-AA4</f>
+        <f t="shared" ref="AA5:AG5" si="12">AA3-AA4</f>
         <v>867.90000000000009</v>
       </c>
       <c r="AB5" s="7">
@@ -1644,80 +1641,80 @@
         <v>944</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" ref="AF5:AH5" si="13">AG3*0.76</f>
-        <v>948.59400000000005</v>
+        <f t="shared" si="12"/>
+        <v>958</v>
       </c>
       <c r="AH5" s="7">
+        <f>AH3*0.78</f>
+        <v>961.35</v>
+      </c>
+      <c r="AJ5" s="7">
+        <f t="shared" ref="AJ5:AQ5" si="13">AJ3-AJ4</f>
+        <v>269.5</v>
+      </c>
+      <c r="AK5" s="7">
         <f t="shared" si="13"/>
-        <v>953.91095999999993</v>
-      </c>
-      <c r="AJ5" s="7">
-        <f t="shared" ref="AJ5:AQ5" si="14">AJ3-AJ4</f>
-        <v>269.5</v>
-      </c>
-      <c r="AK5" s="7">
+        <v>507.40000000000003</v>
+      </c>
+      <c r="AL5" s="7">
+        <f t="shared" si="13"/>
+        <v>1829.4</v>
+      </c>
+      <c r="AM5" s="7">
+        <f t="shared" si="13"/>
+        <v>3045.2999999999997</v>
+      </c>
+      <c r="AN5" s="7">
+        <f t="shared" si="13"/>
+        <v>3292.5</v>
+      </c>
+      <c r="AO5" s="7">
+        <f t="shared" si="13"/>
+        <v>3449.5</v>
+      </c>
+      <c r="AP5" s="7">
+        <f t="shared" si="13"/>
+        <v>3535.5999999999995</v>
+      </c>
+      <c r="AQ5" s="7">
+        <f t="shared" si="13"/>
+        <v>3759.65</v>
+      </c>
+      <c r="AR5" s="7">
+        <f>AR3*0.78</f>
+        <v>3899.8642800000002</v>
+      </c>
+      <c r="AS5" s="7">
+        <f t="shared" ref="AS5:AZ5" si="14">AS3*0.78</f>
+        <v>3938.8629228000004</v>
+      </c>
+      <c r="AT5" s="7">
         <f t="shared" si="14"/>
-        <v>507.40000000000003</v>
-      </c>
-      <c r="AL5" s="7">
+        <v>3978.2515520280003</v>
+      </c>
+      <c r="AU5" s="7">
         <f t="shared" si="14"/>
-        <v>1829.4</v>
-      </c>
-      <c r="AM5" s="7">
+        <v>4018.0340675482803</v>
+      </c>
+      <c r="AV5" s="7">
         <f t="shared" si="14"/>
-        <v>3045.2999999999997</v>
-      </c>
-      <c r="AN5" s="7">
+        <v>4058.2144082237633</v>
+      </c>
+      <c r="AW5" s="7">
         <f t="shared" si="14"/>
-        <v>3292.5</v>
-      </c>
-      <c r="AO5" s="7">
+        <v>4098.7965523060011</v>
+      </c>
+      <c r="AX5" s="7">
         <f t="shared" si="14"/>
-        <v>3449.5</v>
-      </c>
-      <c r="AP5" s="7">
+        <v>4139.7845178290609</v>
+      </c>
+      <c r="AY5" s="7">
         <f t="shared" si="14"/>
-        <v>3535.5999999999995</v>
-      </c>
-      <c r="AQ5" s="7">
+        <v>4181.1823630073523</v>
+      </c>
+      <c r="AZ5" s="7">
         <f t="shared" si="14"/>
-        <v>3742.8049599999999</v>
-      </c>
-      <c r="AR5" s="7">
-        <f>AR3*0.76</f>
-        <v>3831.9594287999998</v>
-      </c>
-      <c r="AS5" s="7">
-        <f t="shared" ref="AS5:AZ5" si="15">AS3*0.76</f>
-        <v>3870.2790230879996</v>
-      </c>
-      <c r="AT5" s="7">
-        <f t="shared" si="15"/>
-        <v>3908.9818133188796</v>
-      </c>
-      <c r="AU5" s="7">
-        <f t="shared" si="15"/>
-        <v>3948.0716314520682</v>
-      </c>
-      <c r="AV5" s="7">
-        <f t="shared" si="15"/>
-        <v>3987.5523477665888</v>
-      </c>
-      <c r="AW5" s="7">
-        <f t="shared" si="15"/>
-        <v>4027.4278712442547</v>
-      </c>
-      <c r="AX5" s="7">
-        <f t="shared" si="15"/>
-        <v>4067.7021499566977</v>
-      </c>
-      <c r="AY5" s="7">
-        <f t="shared" si="15"/>
-        <v>4108.3791714562649</v>
-      </c>
-      <c r="AZ5" s="7">
-        <f t="shared" si="15"/>
-        <v>4149.4629631708276</v>
+        <v>4222.9941866374256</v>
       </c>
     </row>
     <row r="6" spans="2:160" x14ac:dyDescent="0.3">
@@ -1815,8 +1812,7 @@
         <v>206.4</v>
       </c>
       <c r="AG6" s="3">
-        <f>AC6*0.98</f>
-        <v>218.54</v>
+        <v>210.1</v>
       </c>
       <c r="AH6" s="3">
         <f>AD6*1.03</f>
@@ -1852,43 +1848,43 @@
       </c>
       <c r="AQ6" s="3">
         <f>SUM(AE6:AH6)</f>
-        <v>853.95299999999997</v>
+        <v>845.51299999999992</v>
       </c>
       <c r="AR6" s="3">
         <f>AQ6*1.04</f>
-        <v>888.11112000000003</v>
+        <v>879.33351999999991</v>
       </c>
       <c r="AS6" s="3">
         <f>AR6*1.03</f>
-        <v>914.75445360000003</v>
+        <v>905.71352559999991</v>
       </c>
       <c r="AT6" s="3">
         <f>AS6*1.02</f>
-        <v>933.04954267200003</v>
+        <v>923.82779611199987</v>
       </c>
       <c r="AU6" s="3">
-        <f t="shared" ref="AU6:AW8" si="16">AT6*1.01</f>
-        <v>942.38003809872009</v>
+        <f t="shared" ref="AU6:AW8" si="15">AT6*1.01</f>
+        <v>933.06607407311992</v>
       </c>
       <c r="AV6" s="3">
-        <f t="shared" si="16"/>
-        <v>951.80383847970734</v>
+        <f t="shared" si="15"/>
+        <v>942.39673481385114</v>
       </c>
       <c r="AW6" s="3">
-        <f t="shared" si="16"/>
-        <v>961.32187686450447</v>
+        <f t="shared" si="15"/>
+        <v>951.82070216198963</v>
       </c>
       <c r="AX6" s="3">
-        <f t="shared" ref="AX6" si="17">AW6*1.01</f>
-        <v>970.93509563314956</v>
+        <f t="shared" ref="AX6" si="16">AW6*1.01</f>
+        <v>961.33890918360953</v>
       </c>
       <c r="AY6" s="3">
-        <f t="shared" ref="AY6" si="18">AX6*1.01</f>
-        <v>980.64444658948105</v>
+        <f t="shared" ref="AY6" si="17">AX6*1.01</f>
+        <v>970.95229827544563</v>
       </c>
       <c r="AZ6" s="3">
-        <f t="shared" ref="AZ6" si="19">AY6*1.01</f>
-        <v>990.45089105537591</v>
+        <f t="shared" ref="AZ6" si="18">AY6*1.01</f>
+        <v>980.66182125820012</v>
       </c>
     </row>
     <row r="7" spans="2:160" x14ac:dyDescent="0.3">
@@ -1986,12 +1982,11 @@
         <v>339</v>
       </c>
       <c r="AG7" s="3">
-        <f>AG3*0.28</f>
-        <v>349.48200000000008</v>
+        <v>342.8</v>
       </c>
       <c r="AH7" s="3">
         <f>AH3*0.28</f>
-        <v>351.44088000000005</v>
+        <v>345.1</v>
       </c>
       <c r="AJ7" s="3">
         <f>SUM(C7:F7)</f>
@@ -2023,43 +2018,43 @@
       </c>
       <c r="AQ7" s="3">
         <f>SUM(AE7:AH7)</f>
-        <v>1386.9228800000001</v>
+        <v>1373.9</v>
       </c>
       <c r="AR7" s="3">
         <f>AR3*0.28</f>
-        <v>1411.7745264000002</v>
+        <v>1399.9512800000002</v>
       </c>
       <c r="AS7" s="3">
-        <f t="shared" ref="AS7:AZ7" si="20">AS3*0.28</f>
-        <v>1425.892271664</v>
+        <f t="shared" ref="AS7:AZ7" si="19">AS3*0.28</f>
+        <v>1413.9507928000003</v>
       </c>
       <c r="AT7" s="3">
-        <f t="shared" si="20"/>
-        <v>1440.1511943806399</v>
+        <f t="shared" si="19"/>
+        <v>1428.0903007280001</v>
       </c>
       <c r="AU7" s="3">
-        <f t="shared" si="20"/>
-        <v>1454.5527063244463</v>
+        <f t="shared" si="19"/>
+        <v>1442.3712037352802</v>
       </c>
       <c r="AV7" s="3">
-        <f t="shared" si="20"/>
-        <v>1469.0982333876907</v>
+        <f t="shared" si="19"/>
+        <v>1456.7949157726332</v>
       </c>
       <c r="AW7" s="3">
-        <f t="shared" si="20"/>
-        <v>1483.7892157215676</v>
+        <f t="shared" si="19"/>
+        <v>1471.3628649303594</v>
       </c>
       <c r="AX7" s="3">
-        <f t="shared" si="20"/>
-        <v>1498.6271078787834</v>
+        <f t="shared" si="19"/>
+        <v>1486.0764935796631</v>
       </c>
       <c r="AY7" s="3">
-        <f t="shared" si="20"/>
-        <v>1513.6133789575713</v>
+        <f t="shared" si="19"/>
+        <v>1500.9372585154597</v>
       </c>
       <c r="AZ7" s="3">
-        <f t="shared" si="20"/>
-        <v>1528.749512747147</v>
+        <f t="shared" si="19"/>
+        <v>1515.9466311006145</v>
       </c>
     </row>
     <row r="8" spans="2:160" x14ac:dyDescent="0.3">
@@ -2157,8 +2152,7 @@
         <v>76.900000000000006</v>
       </c>
       <c r="AG8" s="3">
-        <f t="shared" ref="AF8:AG8" si="21">AC8*0.9</f>
-        <v>113.49</v>
+        <v>94.7</v>
       </c>
       <c r="AH8" s="3">
         <f>AD8*1.05</f>
@@ -2194,43 +2188,43 @@
       </c>
       <c r="AQ8" s="3">
         <f>SUM(AE8:AH8)</f>
-        <v>393.17500000000001</v>
+        <v>374.38499999999999</v>
       </c>
       <c r="AR8" s="3">
         <f>AQ8*1.02</f>
-        <v>401.0385</v>
+        <v>381.87270000000001</v>
       </c>
       <c r="AS8" s="3">
         <f>AR8*1.02</f>
-        <v>409.05927000000003</v>
+        <v>389.510154</v>
       </c>
       <c r="AT8" s="3">
         <f>AS8*1.02</f>
-        <v>417.24045540000003</v>
+        <v>397.30035708000003</v>
       </c>
       <c r="AU8" s="3">
-        <f t="shared" si="16"/>
-        <v>421.41285995400006</v>
+        <f t="shared" si="15"/>
+        <v>401.27336065080004</v>
       </c>
       <c r="AV8" s="3">
-        <f t="shared" si="16"/>
-        <v>425.62698855354006</v>
+        <f t="shared" si="15"/>
+        <v>405.28609425730804</v>
       </c>
       <c r="AW8" s="3">
-        <f t="shared" si="16"/>
-        <v>429.88325843907546</v>
+        <f t="shared" si="15"/>
+        <v>409.33895519988113</v>
       </c>
       <c r="AX8" s="3">
-        <f t="shared" ref="AX8" si="22">AW8*1.01</f>
-        <v>434.18209102346623</v>
+        <f t="shared" ref="AX8" si="20">AW8*1.01</f>
+        <v>413.43234475187995</v>
       </c>
       <c r="AY8" s="3">
-        <f t="shared" ref="AY8" si="23">AX8*1.01</f>
-        <v>438.5239119337009</v>
+        <f t="shared" ref="AY8" si="21">AX8*1.01</f>
+        <v>417.56666819939875</v>
       </c>
       <c r="AZ8" s="3">
-        <f t="shared" ref="AZ8" si="24">AY8*1.01</f>
-        <v>442.90915105303793</v>
+        <f t="shared" ref="AZ8" si="22">AY8*1.01</f>
+        <v>421.74233488139276</v>
       </c>
     </row>
     <row r="9" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2238,132 +2232,132 @@
         <v>33</v>
       </c>
       <c r="C9" s="7">
-        <f t="shared" ref="C9:P9" si="25">C5-C6-C7-C8</f>
+        <f t="shared" ref="C9:P9" si="23">C5-C6-C7-C8</f>
         <v>-1.7999999999999883</v>
       </c>
       <c r="D9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>3.5</v>
       </c>
       <c r="E9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-1.1000000000000085</v>
       </c>
       <c r="F9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>5.4999999999999982</v>
       </c>
       <c r="G9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>1.6000000000000085</v>
       </c>
       <c r="H9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>2.2000000000000028</v>
       </c>
       <c r="I9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>-1.6000000000000121</v>
       </c>
       <c r="J9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>10.600000000000016</v>
       </c>
       <c r="K9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>23.4</v>
       </c>
       <c r="L9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>188.10000000000002</v>
       </c>
       <c r="M9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>192.29999999999998</v>
       </c>
       <c r="N9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>256.10000000000008</v>
       </c>
       <c r="O9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>226.20000000000002</v>
       </c>
       <c r="P9" s="7">
-        <f t="shared" si="25"/>
+        <f t="shared" si="23"/>
         <v>294.60000000000014</v>
       </c>
       <c r="Q9" s="7">
-        <f t="shared" ref="Q9" si="26">Q5-Q6-Q7-Q8</f>
+        <f t="shared" ref="Q9" si="24">Q5-Q6-Q7-Q8</f>
         <v>290.89999999999998</v>
       </c>
       <c r="R9" s="7">
-        <f t="shared" ref="R9" si="27">R5-R6-R7-R8</f>
+        <f t="shared" ref="R9" si="25">R5-R6-R7-R8</f>
         <v>251.90000000000015</v>
       </c>
       <c r="S9" s="7">
-        <f t="shared" ref="S9:T9" si="28">S5-S6-S7-S8</f>
+        <f t="shared" ref="S9:T9" si="26">S5-S6-S7-S8</f>
         <v>187.10000000000002</v>
       </c>
       <c r="T9" s="7">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>121.69999999999996</v>
       </c>
       <c r="U9" s="7">
-        <f t="shared" ref="U9" si="29">U5-U6-U7-U8</f>
+        <f t="shared" ref="U9" si="27">U5-U6-U7-U8</f>
         <v>66.60000000000008</v>
       </c>
       <c r="V9" s="7">
-        <f t="shared" ref="V9" si="30">V5-V6-V7-V8</f>
+        <f t="shared" ref="V9" si="28">V5-V6-V7-V8</f>
         <v>-130.00000000000011</v>
       </c>
       <c r="W9" s="7">
-        <f t="shared" ref="W9:X9" si="31">W5-W6-W7-W8</f>
+        <f t="shared" ref="W9:X9" si="29">W5-W6-W7-W8</f>
         <v>9.8000000000000398</v>
       </c>
       <c r="X9" s="7">
-        <f t="shared" si="31"/>
+        <f t="shared" si="29"/>
         <v>177.59999999999997</v>
       </c>
       <c r="Y9" s="7">
-        <f t="shared" ref="Y9" si="32">Y5-Y6-Y7-Y8</f>
+        <f t="shared" ref="Y9" si="30">Y5-Y6-Y7-Y8</f>
         <v>169.40000000000012</v>
       </c>
       <c r="Z9" s="7">
-        <f t="shared" ref="Z9" si="33">Z5-Z6-Z7-Z8</f>
+        <f t="shared" ref="Z9" si="31">Z5-Z6-Z7-Z8</f>
         <v>168.50000000000006</v>
       </c>
       <c r="AA9" s="7">
-        <f t="shared" ref="AA9:AH9" si="34">AA5-AA6-AA7-AA8</f>
+        <f t="shared" ref="AA9:AH9" si="32">AA5-AA6-AA7-AA8</f>
         <v>203.00000000000006</v>
       </c>
       <c r="AB9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>202.2999999999999</v>
       </c>
       <c r="AC9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>182.80000000000004</v>
       </c>
       <c r="AD9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>224.99999999999994</v>
       </c>
       <c r="AE9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>241.60000000000008</v>
       </c>
       <c r="AF9" s="7">
-        <f t="shared" si="34"/>
+        <f t="shared" si="32"/>
         <v>321.70000000000005</v>
       </c>
       <c r="AG9" s="7">
-        <f t="shared" si="34"/>
-        <v>267.08199999999999</v>
+        <f t="shared" si="32"/>
+        <v>310.39999999999998</v>
       </c>
       <c r="AH9" s="7">
-        <f t="shared" si="34"/>
-        <v>278.37207999999981</v>
+        <f t="shared" si="32"/>
+        <v>292.15200000000004</v>
       </c>
       <c r="AJ9" s="7">
         <f>AJ5-AJ6-AJ7-AJ8</f>
@@ -2382,56 +2376,56 @@
         <v>1063.5999999999997</v>
       </c>
       <c r="AN9" s="7">
-        <f t="shared" ref="AN9:AW9" si="35">AN5-AN6-AN7-AN8</f>
+        <f t="shared" ref="AN9:AW9" si="33">AN5-AN6-AN7-AN8</f>
         <v>245.4000000000002</v>
       </c>
       <c r="AO9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>525.30000000000007</v>
       </c>
       <c r="AP9" s="7">
-        <f t="shared" si="35"/>
+        <f t="shared" si="33"/>
         <v>813.09999999999945</v>
       </c>
       <c r="AQ9" s="7">
-        <f t="shared" si="35"/>
-        <v>1108.7540799999999</v>
+        <f t="shared" si="33"/>
+        <v>1165.8520000000001</v>
       </c>
       <c r="AR9" s="7">
-        <f t="shared" si="35"/>
-        <v>1131.0352823999997</v>
+        <f t="shared" si="33"/>
+        <v>1238.7067800000004</v>
       </c>
       <c r="AS9" s="7">
-        <f t="shared" si="35"/>
-        <v>1120.5730278239996</v>
+        <f t="shared" si="33"/>
+        <v>1229.6884504000004</v>
       </c>
       <c r="AT9" s="7">
-        <f t="shared" si="35"/>
-        <v>1118.5406208662398</v>
+        <f t="shared" si="33"/>
+        <v>1229.0330981080006</v>
       </c>
       <c r="AU9" s="7">
-        <f t="shared" si="35"/>
-        <v>1129.726027074902</v>
+        <f t="shared" si="33"/>
+        <v>1241.32342908908</v>
       </c>
       <c r="AV9" s="7">
-        <f t="shared" si="35"/>
-        <v>1141.0232873456507</v>
+        <f t="shared" si="33"/>
+        <v>1253.7366633799707</v>
       </c>
       <c r="AW9" s="7">
-        <f t="shared" si="35"/>
-        <v>1152.4335202191069</v>
+        <f t="shared" si="33"/>
+        <v>1266.2740300137709</v>
       </c>
       <c r="AX9" s="7">
-        <f t="shared" ref="AX9:AZ9" si="36">AX5-AX6-AX7-AX8</f>
-        <v>1163.9578554212985</v>
+        <f t="shared" ref="AX9:AZ9" si="34">AX5-AX6-AX7-AX8</f>
+        <v>1278.936770313908</v>
       </c>
       <c r="AY9" s="7">
-        <f t="shared" si="36"/>
-        <v>1175.5974339755116</v>
+        <f t="shared" si="34"/>
+        <v>1291.7261380170482</v>
       </c>
       <c r="AZ9" s="7">
-        <f t="shared" si="36"/>
-        <v>1187.3534083152667</v>
+        <f t="shared" si="34"/>
+        <v>1304.6433993972182</v>
       </c>
     </row>
     <row r="10" spans="2:160" x14ac:dyDescent="0.3">
@@ -2546,7 +2540,8 @@
         <v>-126.7</v>
       </c>
       <c r="AG10" s="3">
-        <v>-100</v>
+        <f>-406.1-78.2</f>
+        <v>-484.3</v>
       </c>
       <c r="AH10" s="3">
         <v>-100</v>
@@ -2581,43 +2576,43 @@
       </c>
       <c r="AQ10" s="3">
         <f>SUM(AE10:AH10)</f>
-        <v>-400.9</v>
+        <v>-785.2</v>
       </c>
       <c r="AR10" s="3">
         <f>AQ10*1.03</f>
-        <v>-412.92699999999996</v>
+        <v>-808.75600000000009</v>
       </c>
       <c r="AS10" s="3">
-        <f t="shared" ref="AS10:AZ10" si="37">AR10*1.03</f>
-        <v>-425.31480999999997</v>
+        <f t="shared" ref="AS10:AZ10" si="35">AR10*1.03</f>
+        <v>-833.01868000000013</v>
       </c>
       <c r="AT10" s="3">
-        <f t="shared" si="37"/>
-        <v>-438.07425429999995</v>
+        <f t="shared" si="35"/>
+        <v>-858.00924040000018</v>
       </c>
       <c r="AU10" s="3">
-        <f t="shared" si="37"/>
-        <v>-451.21648192899994</v>
+        <f t="shared" si="35"/>
+        <v>-883.7495176120002</v>
       </c>
       <c r="AV10" s="3">
-        <f t="shared" si="37"/>
-        <v>-464.75297638686993</v>
+        <f t="shared" si="35"/>
+        <v>-910.26200314036021</v>
       </c>
       <c r="AW10" s="3">
-        <f t="shared" si="37"/>
-        <v>-478.69556567847604</v>
+        <f t="shared" si="35"/>
+        <v>-937.56986323457102</v>
       </c>
       <c r="AX10" s="3">
-        <f t="shared" si="37"/>
-        <v>-493.05643264883031</v>
+        <f t="shared" si="35"/>
+        <v>-965.6969591316082</v>
       </c>
       <c r="AY10" s="3">
-        <f t="shared" si="37"/>
-        <v>-507.84812562829524</v>
+        <f t="shared" si="35"/>
+        <v>-994.66786790555648</v>
       </c>
       <c r="AZ10" s="3">
-        <f t="shared" si="37"/>
-        <v>-523.08356939714406</v>
+        <f t="shared" si="35"/>
+        <v>-1024.5079039427233</v>
       </c>
     </row>
     <row r="11" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2625,132 +2620,132 @@
         <v>35</v>
       </c>
       <c r="C11" s="7">
-        <f t="shared" ref="C11:P11" si="38">C9-C10</f>
+        <f t="shared" ref="C11:P11" si="36">C9-C10</f>
         <v>-1.3999999999999884</v>
       </c>
       <c r="D11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>4.0999999999999996</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>-0.50000000000000855</v>
       </c>
       <c r="F11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>6.0999999999999979</v>
       </c>
       <c r="G11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>2.6000000000000085</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>6.7000000000000028</v>
       </c>
       <c r="I11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>2.5999999999999881</v>
       </c>
       <c r="J11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>14.600000000000016</v>
       </c>
       <c r="K11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>29.2</v>
       </c>
       <c r="L11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>190.20000000000002</v>
       </c>
       <c r="M11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>194.1</v>
       </c>
       <c r="N11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>264.60000000000008</v>
       </c>
       <c r="O11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>228.8</v>
       </c>
       <c r="P11" s="7">
-        <f t="shared" si="38"/>
+        <f t="shared" si="36"/>
         <v>323.90000000000015</v>
       </c>
       <c r="Q11" s="7">
-        <f t="shared" ref="Q11" si="39">Q9-Q10</f>
+        <f t="shared" ref="Q11" si="37">Q9-Q10</f>
         <v>410.29999999999995</v>
       </c>
       <c r="R11" s="7">
-        <f t="shared" ref="R11" si="40">R9-R10</f>
+        <f t="shared" ref="R11" si="38">R9-R10</f>
         <v>138.70000000000016</v>
       </c>
       <c r="S11" s="7">
-        <f t="shared" ref="S11:T11" si="41">S9-S10</f>
+        <f t="shared" ref="S11:T11" si="39">S9-S10</f>
         <v>143.70000000000002</v>
       </c>
       <c r="T11" s="7">
-        <f t="shared" si="41"/>
+        <f t="shared" si="39"/>
         <v>90.399999999999949</v>
       </c>
       <c r="U11" s="7">
-        <f t="shared" ref="U11" si="42">U9-U10</f>
+        <f t="shared" ref="U11" si="40">U9-U10</f>
         <v>54.800000000000082</v>
       </c>
       <c r="V11" s="7">
-        <f t="shared" ref="V11" si="43">V9-V10</f>
+        <f t="shared" ref="V11" si="41">V9-V10</f>
         <v>-39.700000000000117</v>
       </c>
       <c r="W11" s="7">
-        <f t="shared" ref="W11:X11" si="44">W9-W10</f>
+        <f t="shared" ref="W11:X11" si="42">W9-W10</f>
         <v>43.30000000000004</v>
       </c>
       <c r="X11" s="7">
-        <f t="shared" si="44"/>
+        <f t="shared" si="42"/>
         <v>250.39999999999998</v>
       </c>
       <c r="Y11" s="7">
-        <f t="shared" ref="Y11" si="45">Y9-Y10</f>
+        <f t="shared" ref="Y11" si="43">Y9-Y10</f>
         <v>185.80000000000013</v>
       </c>
       <c r="Z11" s="7">
-        <f t="shared" ref="Z11" si="46">Z9-Z10</f>
+        <f t="shared" ref="Z11" si="44">Z9-Z10</f>
         <v>352.90000000000003</v>
       </c>
       <c r="AA11" s="7">
-        <f t="shared" ref="AA11:AH11" si="47">AA9-AA10</f>
+        <f t="shared" ref="AA11:AH11" si="45">AA9-AA10</f>
         <v>292.00000000000006</v>
       </c>
       <c r="AB11" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>292.7999999999999</v>
       </c>
       <c r="AC11" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>280.30000000000007</v>
       </c>
       <c r="AD11" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>450.29999999999995</v>
       </c>
       <c r="AE11" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>315.80000000000007</v>
       </c>
       <c r="AF11" s="7">
-        <f t="shared" si="47"/>
+        <f t="shared" si="45"/>
         <v>448.40000000000003</v>
       </c>
       <c r="AG11" s="7">
-        <f t="shared" si="47"/>
-        <v>367.08199999999999</v>
+        <f t="shared" si="45"/>
+        <v>794.7</v>
       </c>
       <c r="AH11" s="7">
-        <f t="shared" si="47"/>
-        <v>378.37207999999981</v>
+        <f t="shared" si="45"/>
+        <v>392.15200000000004</v>
       </c>
       <c r="AJ11" s="7">
         <f>AJ9-AJ10</f>
@@ -2769,56 +2764,56 @@
         <v>1101.6999999999996</v>
       </c>
       <c r="AN11" s="7">
-        <f t="shared" ref="AN11:AW11" si="48">AN9-AN10</f>
+        <f t="shared" ref="AN11:AW11" si="46">AN9-AN10</f>
         <v>249.20000000000022</v>
       </c>
       <c r="AO11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>832.40000000000009</v>
       </c>
       <c r="AP11" s="7">
-        <f t="shared" si="48"/>
+        <f t="shared" si="46"/>
         <v>1315.3999999999994</v>
       </c>
       <c r="AQ11" s="7">
-        <f t="shared" si="48"/>
-        <v>1509.6540799999998</v>
+        <f t="shared" si="46"/>
+        <v>1951.0520000000001</v>
       </c>
       <c r="AR11" s="7">
-        <f t="shared" si="48"/>
-        <v>1543.9622823999996</v>
+        <f t="shared" si="46"/>
+        <v>2047.4627800000005</v>
       </c>
       <c r="AS11" s="7">
-        <f t="shared" si="48"/>
-        <v>1545.8878378239997</v>
+        <f t="shared" si="46"/>
+        <v>2062.7071304000006</v>
       </c>
       <c r="AT11" s="7">
-        <f t="shared" si="48"/>
-        <v>1556.6148751662397</v>
+        <f t="shared" si="46"/>
+        <v>2087.0423385080007</v>
       </c>
       <c r="AU11" s="7">
-        <f t="shared" si="48"/>
-        <v>1580.9425090039019</v>
+        <f t="shared" si="46"/>
+        <v>2125.0729467010801</v>
       </c>
       <c r="AV11" s="7">
-        <f t="shared" si="48"/>
-        <v>1605.7762637325206</v>
+        <f t="shared" si="46"/>
+        <v>2163.998666520331</v>
       </c>
       <c r="AW11" s="7">
-        <f t="shared" si="48"/>
-        <v>1631.1290858975829</v>
+        <f t="shared" si="46"/>
+        <v>2203.8438932483418</v>
       </c>
       <c r="AX11" s="7">
-        <f t="shared" ref="AX11:AZ11" si="49">AX9-AX10</f>
-        <v>1657.0142880701287</v>
+        <f t="shared" ref="AX11:AZ11" si="47">AX9-AX10</f>
+        <v>2244.6337294455161</v>
       </c>
       <c r="AY11" s="7">
-        <f t="shared" si="49"/>
-        <v>1683.4455596038069</v>
+        <f t="shared" si="47"/>
+        <v>2286.3940059226047</v>
       </c>
       <c r="AZ11" s="7">
-        <f t="shared" si="49"/>
-        <v>1710.4369777124107</v>
+        <f t="shared" si="47"/>
+        <v>2329.1513033399415</v>
       </c>
     </row>
     <row r="12" spans="2:160" x14ac:dyDescent="0.3">
@@ -2916,12 +2911,11 @@
         <v>89.6</v>
       </c>
       <c r="AG12" s="3">
-        <f t="shared" ref="AF12:AG12" si="50">AG11*0.25</f>
-        <v>91.770499999999998</v>
+        <v>181.8</v>
       </c>
       <c r="AH12" s="3">
         <f>AH11*0.2</f>
-        <v>75.674415999999965</v>
+        <v>78.43040000000002</v>
       </c>
       <c r="AJ12" s="3">
         <f>SUM(C12:F12)</f>
@@ -2953,43 +2947,43 @@
       </c>
       <c r="AQ12" s="3">
         <f>SUM(AE12:AH12)</f>
-        <v>318.24491599999999</v>
+        <v>411.03040000000004</v>
       </c>
       <c r="AR12" s="3">
         <f>AR11*0.22</f>
-        <v>339.67170212799994</v>
+        <v>450.44181160000011</v>
       </c>
       <c r="AS12" s="3">
-        <f t="shared" ref="AS12:AZ12" si="51">AS11*0.22</f>
-        <v>340.09532432127992</v>
+        <f t="shared" ref="AS12:AZ12" si="48">AS11*0.22</f>
+        <v>453.79556868800012</v>
       </c>
       <c r="AT12" s="3">
-        <f t="shared" si="51"/>
-        <v>342.45527253657275</v>
+        <f t="shared" si="48"/>
+        <v>459.14931447176019</v>
       </c>
       <c r="AU12" s="3">
-        <f t="shared" si="51"/>
-        <v>347.80735198085841</v>
+        <f t="shared" si="48"/>
+        <v>467.51604827423762</v>
       </c>
       <c r="AV12" s="3">
-        <f t="shared" si="51"/>
-        <v>353.27077802115457</v>
+        <f t="shared" si="48"/>
+        <v>476.07970663447281</v>
       </c>
       <c r="AW12" s="3">
-        <f t="shared" si="51"/>
-        <v>358.84839889746826</v>
+        <f t="shared" si="48"/>
+        <v>484.84565651463521</v>
       </c>
       <c r="AX12" s="3">
-        <f t="shared" si="51"/>
-        <v>364.54314337542831</v>
+        <f t="shared" si="48"/>
+        <v>493.81942047801357</v>
       </c>
       <c r="AY12" s="3">
-        <f t="shared" si="51"/>
-        <v>370.35802311283754</v>
+        <f t="shared" si="48"/>
+        <v>503.00668130297305</v>
       </c>
       <c r="AZ12" s="3">
-        <f t="shared" si="51"/>
-        <v>376.29613509673032</v>
+        <f t="shared" si="48"/>
+        <v>512.41328673478711</v>
       </c>
     </row>
     <row r="13" spans="2:160" x14ac:dyDescent="0.3">
@@ -3157,132 +3151,132 @@
         <v>37</v>
       </c>
       <c r="C14" s="7">
-        <f t="shared" ref="C14:P14" si="52">C11-C12-C13</f>
+        <f t="shared" ref="C14:P14" si="49">C11-C12-C13</f>
         <v>-1.4999999999999885</v>
       </c>
       <c r="D14" s="7">
+        <f t="shared" si="49"/>
+        <v>0.69999999999999973</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="49"/>
+        <v>-0.60000000000000853</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="49"/>
+        <v>1.9999999999999982</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="49"/>
+        <v>0.3000000000000087</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="49"/>
+        <v>5.5000000000000027</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="49"/>
+        <v>2.2999999999999883</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="49"/>
+        <v>15.400000000000016</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="49"/>
+        <v>27.099999999999998</v>
+      </c>
+      <c r="L14" s="7">
+        <f t="shared" si="49"/>
+        <v>185.80000000000004</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="49"/>
+        <v>198.5</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="49"/>
+        <v>260.40000000000009</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="49"/>
+        <v>227.4</v>
+      </c>
+      <c r="P14" s="7">
+        <f t="shared" si="49"/>
+        <v>316.90000000000015</v>
+      </c>
+      <c r="Q14" s="7">
+        <f t="shared" ref="Q14" si="50">Q11-Q12-Q13</f>
+        <v>340.29999999999995</v>
+      </c>
+      <c r="R14" s="7">
+        <f t="shared" ref="R14" si="51">R11-R12-R13</f>
+        <v>490.70000000000016</v>
+      </c>
+      <c r="S14" s="7">
+        <f t="shared" ref="S14:T14" si="52">S11-S12-S13</f>
+        <v>113.70000000000002</v>
+      </c>
+      <c r="T14" s="7">
         <f t="shared" si="52"/>
-        <v>0.69999999999999973</v>
-      </c>
-      <c r="E14" s="7">
-        <f t="shared" si="52"/>
-        <v>-0.60000000000000853</v>
-      </c>
-      <c r="F14" s="7">
-        <f t="shared" si="52"/>
-        <v>1.9999999999999982</v>
-      </c>
-      <c r="G14" s="7">
-        <f t="shared" si="52"/>
-        <v>0.3000000000000087</v>
-      </c>
-      <c r="H14" s="7">
-        <f t="shared" si="52"/>
-        <v>5.5000000000000027</v>
-      </c>
-      <c r="I14" s="7">
-        <f t="shared" si="52"/>
-        <v>2.2999999999999883</v>
-      </c>
-      <c r="J14" s="7">
-        <f t="shared" si="52"/>
-        <v>15.400000000000016</v>
-      </c>
-      <c r="K14" s="7">
-        <f t="shared" si="52"/>
-        <v>27.099999999999998</v>
-      </c>
-      <c r="L14" s="7">
-        <f t="shared" si="52"/>
-        <v>185.80000000000004</v>
-      </c>
-      <c r="M14" s="7">
-        <f t="shared" si="52"/>
-        <v>198.5</v>
-      </c>
-      <c r="N14" s="7">
-        <f t="shared" si="52"/>
-        <v>260.40000000000009</v>
-      </c>
-      <c r="O14" s="7">
-        <f t="shared" si="52"/>
-        <v>227.4</v>
-      </c>
-      <c r="P14" s="7">
-        <f t="shared" si="52"/>
-        <v>316.90000000000015</v>
-      </c>
-      <c r="Q14" s="7">
-        <f t="shared" ref="Q14" si="53">Q11-Q12-Q13</f>
-        <v>340.29999999999995</v>
-      </c>
-      <c r="R14" s="7">
-        <f t="shared" ref="R14" si="54">R11-R12-R13</f>
-        <v>490.70000000000016</v>
-      </c>
-      <c r="S14" s="7">
-        <f t="shared" ref="S14:T14" si="55">S11-S12-S13</f>
-        <v>113.70000000000002</v>
-      </c>
-      <c r="T14" s="7">
+        <v>45.799999999999947</v>
+      </c>
+      <c r="U14" s="7">
+        <f t="shared" ref="U14" si="53">U11-U12-U13</f>
+        <v>48.400000000000084</v>
+      </c>
+      <c r="V14" s="7">
+        <f t="shared" ref="V14" si="54">V11-V12-V13</f>
+        <v>-104.20000000000012</v>
+      </c>
+      <c r="W14" s="7">
+        <f t="shared" ref="W14:X14" si="55">W11-W12-W13</f>
+        <v>15.500000000000039</v>
+      </c>
+      <c r="X14" s="7">
         <f t="shared" si="55"/>
-        <v>45.799999999999947</v>
-      </c>
-      <c r="U14" s="7">
-        <f t="shared" ref="U14" si="56">U11-U12-U13</f>
-        <v>48.400000000000084</v>
-      </c>
-      <c r="V14" s="7">
-        <f t="shared" ref="V14" si="57">V11-V12-V13</f>
-        <v>-104.20000000000012</v>
-      </c>
-      <c r="W14" s="7">
-        <f t="shared" ref="W14:X14" si="58">W11-W12-W13</f>
-        <v>15.500000000000039</v>
-      </c>
-      <c r="X14" s="7">
+        <v>181.99999999999997</v>
+      </c>
+      <c r="Y14" s="7">
+        <f t="shared" ref="Y14" si="56">Y11-Y12-Y13</f>
+        <v>141.20000000000013</v>
+      </c>
+      <c r="Z14" s="7">
+        <f t="shared" ref="Z14" si="57">Z11-Z12-Z13</f>
+        <v>298.8</v>
+      </c>
+      <c r="AA14" s="7">
+        <f t="shared" ref="AA14:AD14" si="58">AA11-AA12-AA13</f>
+        <v>216.30000000000007</v>
+      </c>
+      <c r="AB14" s="7">
         <f t="shared" si="58"/>
-        <v>181.99999999999997</v>
-      </c>
-      <c r="Y14" s="7">
-        <f t="shared" ref="Y14" si="59">Y11-Y12-Y13</f>
-        <v>141.20000000000013</v>
-      </c>
-      <c r="Z14" s="7">
-        <f t="shared" ref="Z14" si="60">Z11-Z12-Z13</f>
-        <v>298.8</v>
-      </c>
-      <c r="AA14" s="7">
-        <f t="shared" ref="AA14:AD14" si="61">AA11-AA12-AA13</f>
-        <v>216.30000000000007</v>
-      </c>
-      <c r="AB14" s="7">
-        <f t="shared" si="61"/>
         <v>218.89999999999989</v>
       </c>
       <c r="AC14" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>206.90000000000006</v>
       </c>
       <c r="AD14" s="7">
-        <f t="shared" si="61"/>
+        <f t="shared" si="58"/>
         <v>367.79999999999995</v>
       </c>
       <c r="AE14" s="7">
-        <f t="shared" ref="AE14:AH14" si="62">AE11-AE12-AE13</f>
+        <f t="shared" ref="AE14:AH14" si="59">AE11-AE12-AE13</f>
         <v>254.60000000000008</v>
       </c>
       <c r="AF14" s="7">
-        <f t="shared" si="62"/>
+        <f t="shared" si="59"/>
         <v>358.80000000000007</v>
       </c>
       <c r="AG14" s="7">
-        <f t="shared" si="62"/>
-        <v>275.31150000000002</v>
+        <f t="shared" si="59"/>
+        <v>612.90000000000009</v>
       </c>
       <c r="AH14" s="7">
-        <f t="shared" si="62"/>
-        <v>302.69766399999986</v>
+        <f t="shared" si="59"/>
+        <v>313.72160000000002</v>
       </c>
       <c r="AJ14" s="7">
         <f>AJ11-AJ12-AJ13</f>
@@ -3305,484 +3299,484 @@
         <v>103.70000000000022</v>
       </c>
       <c r="AO14" s="7">
-        <f t="shared" ref="AO14:AW14" si="63">AO11-AO12-AO13</f>
+        <f t="shared" ref="AO14:AW14" si="60">AO11-AO12-AO13</f>
         <v>637.50000000000011</v>
       </c>
       <c r="AP14" s="7">
-        <f t="shared" si="63"/>
+        <f t="shared" si="60"/>
         <v>1009.8999999999994</v>
       </c>
       <c r="AQ14" s="7">
-        <f t="shared" si="63"/>
-        <v>1191.4091639999997</v>
+        <f t="shared" si="60"/>
+        <v>1540.0216</v>
       </c>
       <c r="AR14" s="7">
-        <f t="shared" si="63"/>
-        <v>1204.2905802719997</v>
+        <f t="shared" si="60"/>
+        <v>1597.0209684000004</v>
       </c>
       <c r="AS14" s="7">
-        <f t="shared" si="63"/>
-        <v>1205.7925135027199</v>
+        <f t="shared" si="60"/>
+        <v>1608.9115617120005</v>
       </c>
       <c r="AT14" s="7">
-        <f t="shared" si="63"/>
-        <v>1214.159602629667</v>
+        <f t="shared" si="60"/>
+        <v>1627.8930240362406</v>
       </c>
       <c r="AU14" s="7">
-        <f t="shared" si="63"/>
-        <v>1233.1351570230436</v>
+        <f t="shared" si="60"/>
+        <v>1657.5568984268425</v>
       </c>
       <c r="AV14" s="7">
-        <f t="shared" si="63"/>
-        <v>1252.505485711366</v>
+        <f t="shared" si="60"/>
+        <v>1687.9189598858582</v>
       </c>
       <c r="AW14" s="7">
-        <f t="shared" si="63"/>
-        <v>1272.2806870001145</v>
+        <f t="shared" si="60"/>
+        <v>1718.9982367337066</v>
       </c>
       <c r="AX14" s="7">
-        <f t="shared" ref="AX14:AZ14" si="64">AX11-AX12-AX13</f>
-        <v>1292.4711446947003</v>
+        <f t="shared" ref="AX14:AZ14" si="61">AX11-AX12-AX13</f>
+        <v>1750.8143089675025</v>
       </c>
       <c r="AY14" s="7">
-        <f t="shared" si="64"/>
-        <v>1313.0875364909693</v>
+        <f t="shared" si="61"/>
+        <v>1783.3873246196317</v>
       </c>
       <c r="AZ14" s="7">
-        <f t="shared" si="64"/>
-        <v>1334.1408426156804</v>
+        <f t="shared" si="61"/>
+        <v>1816.7380166051544</v>
       </c>
       <c r="BA14" s="1">
         <f>AZ14*(1+$BC$20)</f>
-        <v>1320.7994341895237</v>
+        <v>1798.5706364391028</v>
       </c>
       <c r="BB14" s="1">
-        <f t="shared" ref="BB14:DM14" si="65">BA14*(1+$BC$20)</f>
-        <v>1307.5914398476284</v>
+        <f t="shared" ref="BB14:DM14" si="62">BA14*(1+$BC$20)</f>
+        <v>1780.5849300747118</v>
       </c>
       <c r="BC14" s="1">
-        <f t="shared" si="65"/>
-        <v>1294.5155254491522</v>
+        <f t="shared" si="62"/>
+        <v>1762.7790807739646</v>
       </c>
       <c r="BD14" s="1">
-        <f t="shared" si="65"/>
-        <v>1281.5703701946607</v>
+        <f t="shared" si="62"/>
+        <v>1745.1512899662248</v>
       </c>
       <c r="BE14" s="1">
-        <f t="shared" si="65"/>
-        <v>1268.754666492714</v>
+        <f t="shared" si="62"/>
+        <v>1727.6997770665625</v>
       </c>
       <c r="BF14" s="1">
-        <f t="shared" si="65"/>
-        <v>1256.0671198277869</v>
+        <f t="shared" si="62"/>
+        <v>1710.4227792958968</v>
       </c>
       <c r="BG14" s="1">
-        <f t="shared" si="65"/>
-        <v>1243.5064486295089</v>
+        <f t="shared" si="62"/>
+        <v>1693.3185515029379</v>
       </c>
       <c r="BH14" s="1">
-        <f t="shared" si="65"/>
-        <v>1231.0713841432139</v>
+        <f t="shared" si="62"/>
+        <v>1676.3853659879085</v>
       </c>
       <c r="BI14" s="1">
-        <f t="shared" si="65"/>
-        <v>1218.7606703017818</v>
+        <f t="shared" si="62"/>
+        <v>1659.6215123280294</v>
       </c>
       <c r="BJ14" s="1">
-        <f t="shared" si="65"/>
-        <v>1206.5730635987641</v>
+        <f t="shared" si="62"/>
+        <v>1643.0252972047492</v>
       </c>
       <c r="BK14" s="1">
-        <f t="shared" si="65"/>
-        <v>1194.5073329627764</v>
+        <f t="shared" si="62"/>
+        <v>1626.5950442327016</v>
       </c>
       <c r="BL14" s="1">
-        <f t="shared" si="65"/>
-        <v>1182.5622596331486</v>
+        <f t="shared" si="62"/>
+        <v>1610.3290937903746</v>
       </c>
       <c r="BM14" s="1">
-        <f t="shared" si="65"/>
-        <v>1170.7366370368172</v>
+        <f t="shared" si="62"/>
+        <v>1594.2258028524709</v>
       </c>
       <c r="BN14" s="1">
-        <f t="shared" si="65"/>
-        <v>1159.0292706664491</v>
+        <f t="shared" si="62"/>
+        <v>1578.2835448239462</v>
       </c>
       <c r="BO14" s="1">
-        <f t="shared" si="65"/>
-        <v>1147.4389779597846</v>
+        <f t="shared" si="62"/>
+        <v>1562.5007093757067</v>
       </c>
       <c r="BP14" s="1">
-        <f t="shared" si="65"/>
-        <v>1135.9645881801866</v>
+        <f t="shared" si="62"/>
+        <v>1546.8757022819495</v>
       </c>
       <c r="BQ14" s="1">
-        <f t="shared" si="65"/>
-        <v>1124.6049422983847</v>
+        <f t="shared" si="62"/>
+        <v>1531.40694525913</v>
       </c>
       <c r="BR14" s="1">
-        <f t="shared" si="65"/>
-        <v>1113.3588928754009</v>
+        <f t="shared" si="62"/>
+        <v>1516.0928758065386</v>
       </c>
       <c r="BS14" s="1">
-        <f t="shared" si="65"/>
-        <v>1102.2253039466468</v>
+        <f t="shared" si="62"/>
+        <v>1500.9319470484731</v>
       </c>
       <c r="BT14" s="1">
-        <f t="shared" si="65"/>
-        <v>1091.2030509071803</v>
+        <f t="shared" si="62"/>
+        <v>1485.9226275779884</v>
       </c>
       <c r="BU14" s="1">
-        <f t="shared" si="65"/>
-        <v>1080.2910203981085</v>
+        <f t="shared" si="62"/>
+        <v>1471.0634013022084</v>
       </c>
       <c r="BV14" s="1">
-        <f t="shared" si="65"/>
-        <v>1069.4881101941273</v>
+        <f t="shared" si="62"/>
+        <v>1456.3527672891862</v>
       </c>
       <c r="BW14" s="1">
-        <f t="shared" si="65"/>
-        <v>1058.793229092186</v>
+        <f t="shared" si="62"/>
+        <v>1441.7892396162943</v>
       </c>
       <c r="BX14" s="1">
-        <f t="shared" si="65"/>
-        <v>1048.2052968012642</v>
+        <f t="shared" si="62"/>
+        <v>1427.3713472201314</v>
       </c>
       <c r="BY14" s="1">
-        <f t="shared" si="65"/>
-        <v>1037.7232438332517</v>
+        <f t="shared" si="62"/>
+        <v>1413.0976337479301</v>
       </c>
       <c r="BZ14" s="1">
-        <f t="shared" si="65"/>
-        <v>1027.3460113949191</v>
+        <f t="shared" si="62"/>
+        <v>1398.9666574104508</v>
       </c>
       <c r="CA14" s="1">
-        <f t="shared" si="65"/>
-        <v>1017.0725512809698</v>
+        <f t="shared" si="62"/>
+        <v>1384.9769908363462</v>
       </c>
       <c r="CB14" s="1">
-        <f t="shared" si="65"/>
-        <v>1006.9018257681602</v>
+        <f t="shared" si="62"/>
+        <v>1371.1272209279828</v>
       </c>
       <c r="CC14" s="1">
-        <f t="shared" si="65"/>
-        <v>996.83280751047857</v>
+        <f t="shared" si="62"/>
+        <v>1357.415948718703</v>
       </c>
       <c r="CD14" s="1">
-        <f t="shared" si="65"/>
-        <v>986.86447943537382</v>
+        <f t="shared" si="62"/>
+        <v>1343.841789231516</v>
       </c>
       <c r="CE14" s="1">
-        <f t="shared" si="65"/>
-        <v>976.99583464102011</v>
+        <f t="shared" si="62"/>
+        <v>1330.4033713392009</v>
       </c>
       <c r="CF14" s="1">
-        <f t="shared" si="65"/>
-        <v>967.22587629460986</v>
+        <f t="shared" si="62"/>
+        <v>1317.0993376258089</v>
       </c>
       <c r="CG14" s="1">
-        <f t="shared" si="65"/>
-        <v>957.5536175316638</v>
+        <f t="shared" si="62"/>
+        <v>1303.9283442495507</v>
       </c>
       <c r="CH14" s="1">
-        <f t="shared" si="65"/>
-        <v>947.97808135634716</v>
+        <f t="shared" si="62"/>
+        <v>1290.8890608070551</v>
       </c>
       <c r="CI14" s="1">
-        <f t="shared" si="65"/>
-        <v>938.49830054278368</v>
+        <f t="shared" si="62"/>
+        <v>1277.9801701989845</v>
       </c>
       <c r="CJ14" s="1">
-        <f t="shared" si="65"/>
-        <v>929.11331753735578</v>
+        <f t="shared" si="62"/>
+        <v>1265.2003684969948</v>
       </c>
       <c r="CK14" s="1">
-        <f t="shared" si="65"/>
-        <v>919.82218436198218</v>
+        <f t="shared" si="62"/>
+        <v>1252.5483648120248</v>
       </c>
       <c r="CL14" s="1">
-        <f t="shared" si="65"/>
-        <v>910.6239625183623</v>
+        <f t="shared" si="62"/>
+        <v>1240.0228811639045</v>
       </c>
       <c r="CM14" s="1">
-        <f t="shared" si="65"/>
-        <v>901.51772289317864</v>
+        <f t="shared" si="62"/>
+        <v>1227.6226523522655</v>
       </c>
       <c r="CN14" s="1">
-        <f t="shared" si="65"/>
-        <v>892.5025456642469</v>
+        <f t="shared" si="62"/>
+        <v>1215.3464258287429</v>
       </c>
       <c r="CO14" s="1">
-        <f t="shared" si="65"/>
-        <v>883.57752020760438</v>
+        <f t="shared" si="62"/>
+        <v>1203.1929615704555</v>
       </c>
       <c r="CP14" s="1">
-        <f t="shared" si="65"/>
-        <v>874.74174500552829</v>
+        <f t="shared" si="62"/>
+        <v>1191.161031954751</v>
       </c>
       <c r="CQ14" s="1">
-        <f t="shared" si="65"/>
-        <v>865.99432755547298</v>
+        <f t="shared" si="62"/>
+        <v>1179.2494216352036</v>
       </c>
       <c r="CR14" s="1">
-        <f t="shared" si="65"/>
-        <v>857.33438427991825</v>
+        <f t="shared" si="62"/>
+        <v>1167.4569274188516</v>
       </c>
       <c r="CS14" s="1">
-        <f t="shared" si="65"/>
-        <v>848.76104043711905</v>
+        <f t="shared" si="62"/>
+        <v>1155.782358144663</v>
       </c>
       <c r="CT14" s="1">
-        <f t="shared" si="65"/>
-        <v>840.2734300327478</v>
+        <f t="shared" si="62"/>
+        <v>1144.2245345632164</v>
       </c>
       <c r="CU14" s="1">
-        <f t="shared" si="65"/>
-        <v>831.87069573242036</v>
+        <f t="shared" si="62"/>
+        <v>1132.7822892175841</v>
       </c>
       <c r="CV14" s="1">
-        <f t="shared" si="65"/>
-        <v>823.55198877509611</v>
+        <f t="shared" si="62"/>
+        <v>1121.4544663254082</v>
       </c>
       <c r="CW14" s="1">
-        <f t="shared" si="65"/>
-        <v>815.31646888734508</v>
+        <f t="shared" si="62"/>
+        <v>1110.2399216621541</v>
       </c>
       <c r="CX14" s="1">
-        <f t="shared" si="65"/>
-        <v>807.16330419847168</v>
+        <f t="shared" si="62"/>
+        <v>1099.1375224455326</v>
       </c>
       <c r="CY14" s="1">
-        <f t="shared" si="65"/>
-        <v>799.091671156487</v>
+        <f t="shared" si="62"/>
+        <v>1088.1461472210772</v>
       </c>
       <c r="CZ14" s="1">
-        <f t="shared" si="65"/>
-        <v>791.10075444492213</v>
+        <f t="shared" si="62"/>
+        <v>1077.2646857488664</v>
       </c>
       <c r="DA14" s="1">
-        <f t="shared" si="65"/>
-        <v>783.18974690047287</v>
+        <f t="shared" si="62"/>
+        <v>1066.4920388913777</v>
       </c>
       <c r="DB14" s="1">
-        <f t="shared" si="65"/>
-        <v>775.35784943146814</v>
+        <f t="shared" si="62"/>
+        <v>1055.8271185024639</v>
       </c>
       <c r="DC14" s="1">
-        <f t="shared" si="65"/>
-        <v>767.6042709371535</v>
+        <f t="shared" si="62"/>
+        <v>1045.2688473174392</v>
       </c>
       <c r="DD14" s="1">
-        <f t="shared" si="65"/>
-        <v>759.92822822778191</v>
+        <f t="shared" si="62"/>
+        <v>1034.8161588442647</v>
       </c>
       <c r="DE14" s="1">
-        <f t="shared" si="65"/>
-        <v>752.32894594550407</v>
+        <f t="shared" si="62"/>
+        <v>1024.467997255822</v>
       </c>
       <c r="DF14" s="1">
-        <f t="shared" si="65"/>
-        <v>744.80565648604897</v>
+        <f t="shared" si="62"/>
+        <v>1014.2233172832638</v>
       </c>
       <c r="DG14" s="1">
-        <f t="shared" si="65"/>
-        <v>737.35759992118847</v>
+        <f t="shared" si="62"/>
+        <v>1004.0810841104311</v>
       </c>
       <c r="DH14" s="1">
-        <f t="shared" si="65"/>
-        <v>729.98402392197659</v>
+        <f t="shared" si="62"/>
+        <v>994.0402732693268</v>
       </c>
       <c r="DI14" s="1">
-        <f t="shared" si="65"/>
-        <v>722.68418368275684</v>
+        <f t="shared" si="62"/>
+        <v>984.09987053663349</v>
       </c>
       <c r="DJ14" s="1">
-        <f t="shared" si="65"/>
-        <v>715.45734184592925</v>
+        <f t="shared" si="62"/>
+        <v>974.25887183126713</v>
       </c>
       <c r="DK14" s="1">
-        <f t="shared" si="65"/>
-        <v>708.30276842746991</v>
+        <f t="shared" si="62"/>
+        <v>964.5162831129544</v>
       </c>
       <c r="DL14" s="1">
-        <f t="shared" si="65"/>
-        <v>701.21974074319519</v>
+        <f t="shared" si="62"/>
+        <v>954.8711202818248</v>
       </c>
       <c r="DM14" s="1">
-        <f t="shared" si="65"/>
-        <v>694.20754333576326</v>
+        <f t="shared" si="62"/>
+        <v>945.32240907900655</v>
       </c>
       <c r="DN14" s="1">
-        <f t="shared" ref="DN14:FD14" si="66">DM14*(1+$BC$20)</f>
-        <v>687.26546790240559</v>
+        <f t="shared" ref="DN14:FD14" si="63">DM14*(1+$BC$20)</f>
+        <v>935.86918498821649</v>
       </c>
       <c r="DO14" s="1">
-        <f t="shared" si="66"/>
-        <v>680.39281322338149</v>
+        <f t="shared" si="63"/>
+        <v>926.51049313833437</v>
       </c>
       <c r="DP14" s="1">
-        <f t="shared" si="66"/>
-        <v>673.58888509114763</v>
+        <f t="shared" si="63"/>
+        <v>917.24538820695102</v>
       </c>
       <c r="DQ14" s="1">
-        <f t="shared" si="66"/>
-        <v>666.85299624023617</v>
+        <f t="shared" si="63"/>
+        <v>908.07293432488154</v>
       </c>
       <c r="DR14" s="1">
-        <f t="shared" si="66"/>
-        <v>660.18446627783385</v>
+        <f t="shared" si="63"/>
+        <v>898.99220498163277</v>
       </c>
       <c r="DS14" s="1">
-        <f t="shared" si="66"/>
-        <v>653.58262161505547</v>
+        <f t="shared" si="63"/>
+        <v>890.00228293181647</v>
       </c>
       <c r="DT14" s="1">
-        <f t="shared" si="66"/>
-        <v>647.04679539890492</v>
+        <f t="shared" si="63"/>
+        <v>881.10226010249835</v>
       </c>
       <c r="DU14" s="1">
-        <f t="shared" si="66"/>
-        <v>640.57632744491582</v>
+        <f t="shared" si="63"/>
+        <v>872.29123750147335</v>
       </c>
       <c r="DV14" s="1">
-        <f t="shared" si="66"/>
-        <v>634.1705641704666</v>
+        <f t="shared" si="63"/>
+        <v>863.5683251264586</v>
       </c>
       <c r="DW14" s="1">
-        <f t="shared" si="66"/>
-        <v>627.82885852876188</v>
+        <f t="shared" si="63"/>
+        <v>854.93264187519401</v>
       </c>
       <c r="DX14" s="1">
-        <f t="shared" si="66"/>
-        <v>621.55056994347422</v>
+        <f t="shared" si="63"/>
+        <v>846.38331545644201</v>
       </c>
       <c r="DY14" s="1">
-        <f t="shared" si="66"/>
-        <v>615.33506424403947</v>
+        <f t="shared" si="63"/>
+        <v>837.91948230187757</v>
       </c>
       <c r="DZ14" s="1">
-        <f t="shared" si="66"/>
-        <v>609.18171360159909</v>
+        <f t="shared" si="63"/>
+        <v>829.54028747885877</v>
       </c>
       <c r="EA14" s="1">
-        <f t="shared" si="66"/>
-        <v>603.08989646558314</v>
+        <f t="shared" si="63"/>
+        <v>821.24488460407019</v>
       </c>
       <c r="EB14" s="1">
-        <f t="shared" si="66"/>
-        <v>597.05899750092726</v>
+        <f t="shared" si="63"/>
+        <v>813.03243575802946</v>
       </c>
       <c r="EC14" s="1">
-        <f t="shared" si="66"/>
-        <v>591.088407525918</v>
+        <f t="shared" si="63"/>
+        <v>804.90211140044914</v>
       </c>
       <c r="ED14" s="1">
-        <f t="shared" si="66"/>
-        <v>585.17752345065878</v>
+        <f t="shared" si="63"/>
+        <v>796.85309028644463</v>
       </c>
       <c r="EE14" s="1">
-        <f t="shared" si="66"/>
-        <v>579.32574821615219</v>
+        <f t="shared" si="63"/>
+        <v>788.88455938358015</v>
       </c>
       <c r="EF14" s="1">
-        <f t="shared" si="66"/>
-        <v>573.5324907339907</v>
+        <f t="shared" si="63"/>
+        <v>780.9957137897444</v>
       </c>
       <c r="EG14" s="1">
-        <f t="shared" si="66"/>
-        <v>567.79716582665083</v>
+        <f t="shared" si="63"/>
+        <v>773.18575665184699</v>
       </c>
       <c r="EH14" s="1">
-        <f t="shared" si="66"/>
-        <v>562.1191941683843</v>
+        <f t="shared" si="63"/>
+        <v>765.45389908532854</v>
       </c>
       <c r="EI14" s="1">
-        <f t="shared" si="66"/>
-        <v>556.49800222670046</v>
+        <f t="shared" si="63"/>
+        <v>757.79936009447522</v>
       </c>
       <c r="EJ14" s="1">
-        <f t="shared" si="66"/>
-        <v>550.93302220443343</v>
+        <f t="shared" si="63"/>
+        <v>750.22136649353047</v>
       </c>
       <c r="EK14" s="1">
-        <f t="shared" si="66"/>
-        <v>545.42369198238907</v>
+        <f t="shared" si="63"/>
+        <v>742.71915282859516</v>
       </c>
       <c r="EL14" s="1">
-        <f t="shared" si="66"/>
-        <v>539.9694550625652</v>
+        <f t="shared" si="63"/>
+        <v>735.29196130030925</v>
       </c>
       <c r="EM14" s="1">
-        <f t="shared" si="66"/>
-        <v>534.56976051193953</v>
+        <f t="shared" si="63"/>
+        <v>727.93904168730614</v>
       </c>
       <c r="EN14" s="1">
-        <f t="shared" si="66"/>
-        <v>529.22406290682011</v>
+        <f t="shared" si="63"/>
+        <v>720.65965127043307</v>
       </c>
       <c r="EO14" s="1">
-        <f t="shared" si="66"/>
-        <v>523.93182227775185</v>
+        <f t="shared" si="63"/>
+        <v>713.45305475772875</v>
       </c>
       <c r="EP14" s="1">
-        <f t="shared" si="66"/>
-        <v>518.69250405497428</v>
+        <f t="shared" si="63"/>
+        <v>706.31852421015151</v>
       </c>
       <c r="EQ14" s="1">
-        <f t="shared" si="66"/>
-        <v>513.50557901442448</v>
+        <f t="shared" si="63"/>
+        <v>699.25533896804995</v>
       </c>
       <c r="ER14" s="1">
-        <f t="shared" si="66"/>
-        <v>508.37052322428025</v>
+        <f t="shared" si="63"/>
+        <v>692.2627855783694</v>
       </c>
       <c r="ES14" s="1">
-        <f t="shared" si="66"/>
-        <v>503.28681799203741</v>
+        <f t="shared" si="63"/>
+        <v>685.34015772258567</v>
       </c>
       <c r="ET14" s="1">
-        <f t="shared" si="66"/>
-        <v>498.25394981211701</v>
+        <f t="shared" si="63"/>
+        <v>678.48675614535978</v>
       </c>
       <c r="EU14" s="1">
-        <f t="shared" si="66"/>
-        <v>493.27141031399583</v>
+        <f t="shared" si="63"/>
+        <v>671.70188858390622</v>
       </c>
       <c r="EV14" s="1">
-        <f t="shared" si="66"/>
-        <v>488.33869621085586</v>
+        <f t="shared" si="63"/>
+        <v>664.9848696980672</v>
       </c>
       <c r="EW14" s="1">
-        <f t="shared" si="66"/>
-        <v>483.45530924874731</v>
+        <f t="shared" si="63"/>
+        <v>658.33502100108649</v>
       </c>
       <c r="EX14" s="1">
-        <f t="shared" si="66"/>
-        <v>478.62075615625986</v>
+        <f t="shared" si="63"/>
+        <v>651.75167079107564</v>
       </c>
       <c r="EY14" s="1">
-        <f t="shared" si="66"/>
-        <v>473.83454859469725</v>
+        <f t="shared" si="63"/>
+        <v>645.23415408316487</v>
       </c>
       <c r="EZ14" s="1">
-        <f t="shared" si="66"/>
-        <v>469.09620310875027</v>
+        <f t="shared" si="63"/>
+        <v>638.78181254233323</v>
       </c>
       <c r="FA14" s="1">
-        <f t="shared" si="66"/>
-        <v>464.40524107766277</v>
+        <f t="shared" si="63"/>
+        <v>632.39399441690989</v>
       </c>
       <c r="FB14" s="1">
-        <f t="shared" si="66"/>
-        <v>459.76118866688614</v>
+        <f t="shared" si="63"/>
+        <v>626.07005447274082</v>
       </c>
       <c r="FC14" s="1">
-        <f t="shared" si="66"/>
-        <v>455.16357678021728</v>
+        <f t="shared" si="63"/>
+        <v>619.80935392801337</v>
       </c>
       <c r="FD14" s="1">
-        <f t="shared" si="66"/>
-        <v>450.61194101241512</v>
+        <f t="shared" si="63"/>
+        <v>613.61126038873317</v>
       </c>
     </row>
     <row r="15" spans="2:160" x14ac:dyDescent="0.3">
@@ -3826,55 +3820,55 @@
         <v>287.60000000000002</v>
       </c>
       <c r="O15" s="3">
-        <f t="shared" ref="O15:AA15" si="67">263.6+45.7</f>
+        <f t="shared" ref="O15:AA15" si="64">263.6+45.7</f>
         <v>309.3</v>
       </c>
       <c r="P15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="Q15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="V15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="Z15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="AA15" s="3">
-        <f t="shared" si="67"/>
+        <f t="shared" si="64"/>
         <v>309.3</v>
       </c>
       <c r="AB15" s="3">
@@ -3897,12 +3891,12 @@
         <v>299.3</v>
       </c>
       <c r="AG15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f>265.6+30.5</f>
+        <v>296.10000000000002</v>
       </c>
       <c r="AH15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f>265.6+30.5</f>
+        <v>296.10000000000002</v>
       </c>
       <c r="AJ15" s="3">
         <v>287.60000000000002</v>
@@ -3920,7 +3914,7 @@
         <v>287.60000000000002</v>
       </c>
       <c r="AO15" s="3">
-        <f t="shared" ref="AO15" si="68">263.6+45.7</f>
+        <f t="shared" ref="AO15" si="65">263.6+45.7</f>
         <v>309.3</v>
       </c>
       <c r="AP15" s="3">
@@ -3928,44 +3922,44 @@
         <v>306.60000000000002</v>
       </c>
       <c r="AQ15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" ref="AQ15:AZ15" si="66">265.6+30.5</f>
+        <v>296.10000000000002</v>
       </c>
       <c r="AR15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AS15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AT15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AU15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AV15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AW15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AX15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AY15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
       <c r="AZ15" s="3">
-        <f>266.5+32.8</f>
-        <v>299.3</v>
+        <f t="shared" si="66"/>
+        <v>296.10000000000002</v>
       </c>
     </row>
     <row r="16" spans="2:160" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3973,132 +3967,132 @@
         <v>39</v>
       </c>
       <c r="C16" s="8">
-        <f t="shared" ref="C16:P16" si="69">C14/C15</f>
+        <f t="shared" ref="C16:P16" si="67">C14/C15</f>
         <v>-5.2155771905423795E-3</v>
       </c>
       <c r="D16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>2.4339360222531284E-3</v>
       </c>
       <c r="E16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>-2.0862308762169975E-3</v>
       </c>
       <c r="F16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>6.9541029207232201E-3</v>
       </c>
       <c r="G16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0431154381085142E-3</v>
       </c>
       <c r="H16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.9123783031988882E-2</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>7.9972183588316696E-3</v>
       </c>
       <c r="J16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>5.3546592489568896E-2</v>
       </c>
       <c r="K16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>9.4228094575799712E-2</v>
       </c>
       <c r="L16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.64603616133518782</v>
       </c>
       <c r="M16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.69019471488178019</v>
       </c>
       <c r="N16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.90542420027816439</v>
       </c>
       <c r="O16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>0.73520853540252185</v>
       </c>
       <c r="P16" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="67"/>
         <v>1.0245716133204013</v>
       </c>
       <c r="Q16" s="8">
-        <f t="shared" ref="Q16" si="70">Q14/Q15</f>
+        <f t="shared" ref="Q16" si="68">Q14/Q15</f>
         <v>1.1002263174911087</v>
       </c>
       <c r="R16" s="8">
-        <f t="shared" ref="R16" si="71">R14/R15</f>
+        <f t="shared" ref="R16" si="69">R14/R15</f>
         <v>1.5864856126737799</v>
       </c>
       <c r="S16" s="8">
-        <f t="shared" ref="S16:T16" si="72">S14/S15</f>
+        <f t="shared" ref="S16:T16" si="70">S14/S15</f>
         <v>0.36760426770126098</v>
       </c>
       <c r="T16" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="70"/>
         <v>0.1480763013255737</v>
       </c>
       <c r="U16" s="8">
-        <f t="shared" ref="U16" si="73">U14/U15</f>
+        <f t="shared" ref="U16" si="71">U14/U15</f>
         <v>0.15648237956676392</v>
       </c>
       <c r="V16" s="8">
-        <f t="shared" ref="V16" si="74">V14/V15</f>
+        <f t="shared" ref="V16" si="72">V14/V15</f>
         <v>-0.33688975105076013</v>
       </c>
       <c r="W16" s="8">
-        <f t="shared" ref="W16:X16" si="75">W14/W15</f>
+        <f t="shared" ref="W16:X16" si="73">W14/W15</f>
         <v>5.0113158745554602E-2</v>
       </c>
       <c r="X16" s="8">
-        <f t="shared" si="75"/>
+        <f t="shared" si="73"/>
         <v>0.58842547688328473</v>
       </c>
       <c r="Y16" s="8">
-        <f t="shared" ref="Y16" si="76">Y14/Y15</f>
+        <f t="shared" ref="Y16" si="74">Y14/Y15</f>
         <v>0.4565147106369225</v>
       </c>
       <c r="Z16" s="8">
-        <f t="shared" ref="Z16" si="77">Z14/Z15</f>
+        <f t="shared" ref="Z16" si="75">Z14/Z15</f>
         <v>0.96605237633365659</v>
       </c>
       <c r="AA16" s="8">
-        <f t="shared" ref="AA16:AD16" si="78">AA14/AA15</f>
+        <f t="shared" ref="AA16:AD16" si="76">AA14/AA15</f>
         <v>0.69932104752667335</v>
       </c>
       <c r="AB16" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.71117608836907042</v>
       </c>
       <c r="AC16" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>0.67284552845528478</v>
       </c>
       <c r="AD16" s="8">
-        <f t="shared" si="78"/>
+        <f t="shared" si="76"/>
         <v>1.1996086105675143</v>
       </c>
       <c r="AE16" s="8">
-        <f t="shared" ref="AE16:AH16" si="79">AE14/AE15</f>
+        <f t="shared" ref="AE16:AH16" si="77">AE14/AE15</f>
         <v>0.84137475214805046</v>
       </c>
       <c r="AF16" s="8">
-        <f t="shared" si="79"/>
+        <f t="shared" si="77"/>
         <v>1.1987971934513868</v>
       </c>
       <c r="AG16" s="8">
-        <f t="shared" si="79"/>
-        <v>0.91985131974607426</v>
+        <f t="shared" si="77"/>
+        <v>2.0699088145896658</v>
       </c>
       <c r="AH16" s="8">
-        <f t="shared" si="79"/>
-        <v>1.0113520347477443</v>
+        <f t="shared" si="77"/>
+        <v>1.0595123269165823</v>
       </c>
       <c r="AJ16" s="8">
         <f>AJ14/AJ15</f>
@@ -4121,52 +4115,52 @@
         <v>0.36057023643950004</v>
       </c>
       <c r="AO16" s="8">
-        <f t="shared" ref="AO16:AW16" si="80">AO14/AO15</f>
+        <f t="shared" ref="AO16:AW16" si="78">AO14/AO15</f>
         <v>2.0611057225994185</v>
       </c>
       <c r="AP16" s="8">
-        <f t="shared" si="80"/>
+        <f t="shared" si="78"/>
         <v>3.2938682322243946</v>
       </c>
       <c r="AQ16" s="8">
-        <f t="shared" si="80"/>
-        <v>3.9806520681590367</v>
+        <f t="shared" si="78"/>
+        <v>5.2010185748058086</v>
       </c>
       <c r="AR16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.0236905455128626</v>
+        <f t="shared" si="78"/>
+        <v>5.3935189746707204</v>
       </c>
       <c r="AS16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.0287086986392247</v>
+        <f t="shared" si="78"/>
+        <v>5.4336763313475194</v>
       </c>
       <c r="AT16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.0566642252912359</v>
+        <f t="shared" si="78"/>
+        <v>5.4977812361912886</v>
       </c>
       <c r="AU16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.1200640060910239</v>
+        <f t="shared" si="78"/>
+        <v>5.5979631827991971</v>
       </c>
       <c r="AV16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.1847827788552152</v>
+        <f t="shared" si="78"/>
+        <v>5.7005030729005677</v>
       </c>
       <c r="AW16" s="8">
-        <f t="shared" si="80"/>
-        <v>4.2508542833281471</v>
+        <f t="shared" si="78"/>
+        <v>5.8054651696511534</v>
       </c>
       <c r="AX16" s="8">
-        <f t="shared" ref="AX16:AZ16" si="81">AX14/AX15</f>
-        <v>4.3183132131463422</v>
+        <f t="shared" ref="AX16:AZ16" si="79">AX14/AX15</f>
+        <v>5.9129155993498896</v>
       </c>
       <c r="AY16" s="8">
-        <f t="shared" si="81"/>
-        <v>4.3871952438722666</v>
+        <f t="shared" si="79"/>
+        <v>6.0229224066856855</v>
       </c>
       <c r="AZ16" s="8">
-        <f t="shared" si="81"/>
-        <v>4.4575370618632819</v>
+        <f t="shared" si="79"/>
+        <v>6.1355556116351035</v>
       </c>
     </row>
     <row r="18" spans="2:55" x14ac:dyDescent="0.3">
@@ -4182,112 +4176,112 @@
         <v>1.0299500831946755</v>
       </c>
       <c r="H18" s="9">
-        <f t="shared" ref="H18:R18" si="82">H3/D3-1</f>
+        <f t="shared" ref="H18:R18" si="80">H3/D3-1</f>
         <v>0.95704697986577192</v>
       </c>
       <c r="I18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.84905660377358494</v>
       </c>
       <c r="J18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.77977315689981119</v>
       </c>
       <c r="K18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>1.6901639344262294</v>
       </c>
       <c r="L18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>3.5507544581618653</v>
       </c>
       <c r="M18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>3.6650660264105648</v>
       </c>
       <c r="N18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>3.6866702071163031</v>
       </c>
       <c r="O18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>1.913467397928093</v>
       </c>
       <c r="P18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.53956292388847027</v>
       </c>
       <c r="Q18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.35203293875450314</v>
       </c>
       <c r="R18" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="80"/>
         <v>0.2140509915014166</v>
       </c>
       <c r="S18" s="9">
-        <f t="shared" ref="S18" si="83">S3/O3-1</f>
+        <f t="shared" ref="S18" si="81">S3/O3-1</f>
         <v>0.12298682284040985</v>
       </c>
       <c r="T18" s="9">
-        <f t="shared" ref="T18" si="84">T3/P3-1</f>
+        <f t="shared" ref="T18" si="82">T3/P3-1</f>
         <v>7.6358296622613731E-2</v>
       </c>
       <c r="U18" s="9">
-        <f t="shared" ref="U18" si="85">U3/Q3-1</f>
+        <f t="shared" ref="U18" si="83">U3/Q3-1</f>
         <v>4.8629615531024184E-2</v>
       </c>
       <c r="V18" s="9">
-        <f t="shared" ref="V18" si="86">V3/R3-1</f>
+        <f t="shared" ref="V18" si="84">V3/R3-1</f>
         <v>4.3307821541907598E-2</v>
       </c>
       <c r="W18" s="9">
-        <f t="shared" ref="W18" si="87">W3/S3-1</f>
+        <f t="shared" ref="W18" si="85">W3/S3-1</f>
         <v>2.942819891972448E-2</v>
       </c>
       <c r="X18" s="9">
-        <f t="shared" ref="X18" si="88">X3/T3-1</f>
+        <f t="shared" ref="X18" si="86">X3/T3-1</f>
         <v>3.565256934970451E-2</v>
       </c>
       <c r="Y18" s="9">
-        <f t="shared" ref="Y18" si="89">Y3/U3-1</f>
+        <f t="shared" ref="Y18" si="87">Y3/U3-1</f>
         <v>3.1581813231690736E-2</v>
       </c>
       <c r="Z18" s="9">
-        <f t="shared" ref="Z18" si="90">Z3/V3-1</f>
+        <f t="shared" ref="Z18" si="88">Z3/V3-1</f>
         <v>2.5675433887994314E-2</v>
       </c>
       <c r="AA18" s="9">
-        <f t="shared" ref="AA18" si="91">AA3/W3-1</f>
+        <f t="shared" ref="AA18" si="89">AA3/W3-1</f>
         <v>3.2386466437488659E-2</v>
       </c>
       <c r="AB18" s="9">
-        <f t="shared" ref="AB18" si="92">AB3/X3-1</f>
+        <f t="shared" ref="AB18" si="90">AB3/X3-1</f>
         <v>2.0901027487485679E-2</v>
       </c>
       <c r="AC18" s="9">
-        <f t="shared" ref="AC18" si="93">AC3/Y3-1</f>
+        <f t="shared" ref="AC18" si="91">AC3/Y3-1</f>
         <v>3.589337556083394E-2</v>
       </c>
       <c r="AD18" s="9">
-        <f t="shared" ref="AD18" si="94">AD3/Z3-1</f>
+        <f t="shared" ref="AD18" si="92">AD3/Z3-1</f>
         <v>3.2795464457043177E-2</v>
       </c>
       <c r="AE18" s="9">
-        <f t="shared" ref="AE18" si="95">AE3/AA3-1</f>
+        <f t="shared" ref="AE18" si="93">AE3/AA3-1</f>
         <v>2.9355064844023726E-2</v>
       </c>
       <c r="AF18" s="9">
-        <f t="shared" ref="AF18" si="96">AF3/AB3-1</f>
+        <f t="shared" ref="AF18" si="94">AF3/AB3-1</f>
         <v>4.7053763440860319E-2</v>
       </c>
       <c r="AG18" s="9">
-        <f t="shared" ref="AG18" si="97">AG3/AC3-1</f>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" ref="AG18" si="95">AG3/AC3-1</f>
+        <v>4.4416135881103935E-2</v>
       </c>
       <c r="AH18" s="9">
-        <f t="shared" ref="AH18" si="98">AH3/AD3-1</f>
-        <v>6.0000000000000053E-2</v>
+        <f t="shared" ref="AH18" si="96">AH3/AD3-1</f>
+        <v>4.0874926104214282E-2</v>
       </c>
       <c r="AJ18" s="9"/>
       <c r="AK18" s="9">
@@ -4295,63 +4289,63 @@
         <v>0.88411497730711064</v>
       </c>
       <c r="AL18" s="9">
-        <f t="shared" ref="AL18:AW18" si="99">AL3/AK3-1</f>
+        <f t="shared" ref="AL18:AW18" si="97">AL3/AK3-1</f>
         <v>3.2579091055082703</v>
       </c>
       <c r="AM18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.54631515425812749</v>
       </c>
       <c r="AN18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>7.1489548525573987E-2</v>
       </c>
       <c r="AO18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>3.0571363532893248E-2</v>
       </c>
       <c r="AP18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>3.0481744085878892E-2</v>
       </c>
       <c r="AQ18" s="9">
-        <f t="shared" si="99"/>
-        <v>4.9277859944698132E-2</v>
+        <f t="shared" si="97"/>
+        <v>4.0490429340021228E-2</v>
       </c>
       <c r="AR18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AS18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW18" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX18" s="9">
-        <f t="shared" ref="AX18" si="100">AX3/AW3-1</f>
+        <f t="shared" ref="AX18" si="98">AX3/AW3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY18" s="9">
-        <f t="shared" ref="AY18" si="101">AY3/AX3-1</f>
+        <f t="shared" ref="AY18" si="99">AY3/AX3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ18" s="9">
-        <f t="shared" ref="AZ18" si="102">AZ3/AY3-1</f>
+        <f t="shared" ref="AZ18" si="100">AZ3/AY3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -4360,19 +4354,19 @@
         <v>41</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:F19" si="103">C5/C3</f>
+        <f t="shared" ref="C19:F19" si="101">C5/C3</f>
         <v>0.80532445923460905</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.82550335570469802</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.81354051054384025</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.81568998109640833</v>
       </c>
       <c r="G19" s="9">
@@ -4380,180 +4374,180 @@
         <v>0.80245901639344264</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" ref="H19:R19" si="104">H5/H3</f>
+        <f t="shared" ref="H19:R19" si="102">H5/H3</f>
         <v>0.8086419753086419</v>
       </c>
       <c r="I19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.81512605042016795</v>
+      </c>
+      <c r="J19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.82740308019118425</v>
+      </c>
+      <c r="K19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.68403412553321152</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.71017332328560656</v>
+      </c>
+      <c r="M19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.66713844570252179</v>
+      </c>
+      <c r="N19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.69711048158640232</v>
+      </c>
+      <c r="O19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.72286132608240961</v>
+      </c>
+      <c r="P19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.74419970631424381</v>
+      </c>
+      <c r="Q19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.74210125618576317</v>
+      </c>
+      <c r="R19" s="9">
+        <f t="shared" si="102"/>
+        <v>0.75984692925144681</v>
+      </c>
+      <c r="S19" s="9">
+        <f t="shared" ref="S19:AD19" si="103">S5/S3</f>
+        <v>0.75619295958279009</v>
+      </c>
+      <c r="T19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.75115961800818554</v>
+      </c>
+      <c r="U19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.75433342408567017</v>
+      </c>
+      <c r="V19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.73662551440329216</v>
+      </c>
+      <c r="W19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.76126289126108204</v>
+      </c>
+      <c r="X19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.7658733643628699</v>
+      </c>
+      <c r="Y19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.76159056919151935</v>
+      </c>
+      <c r="Z19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.75900566942869607</v>
+      </c>
+      <c r="AA19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.76051524710830709</v>
+      </c>
+      <c r="AB19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.754752688172043</v>
+      </c>
+      <c r="AC19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.75889596602972398</v>
+      </c>
+      <c r="AD19" s="9">
+        <f t="shared" si="103"/>
+        <v>0.75728401317456295</v>
+      </c>
+      <c r="AE19" s="9">
+        <f t="shared" ref="AE19:AH19" si="104">AE5/AE3</f>
+        <v>0.76300331999659488</v>
+      </c>
+      <c r="AF19" s="9">
         <f t="shared" si="104"/>
-        <v>0.81512605042016795</v>
-      </c>
-      <c r="J19" s="9">
+        <v>0.77555044364114356</v>
+      </c>
+      <c r="AG19" s="9">
         <f t="shared" si="104"/>
-        <v>0.82740308019118425</v>
-      </c>
-      <c r="K19" s="9">
+        <v>0.77898845340705813</v>
+      </c>
+      <c r="AH19" s="9">
         <f t="shared" si="104"/>
-        <v>0.68403412553321152</v>
-      </c>
-      <c r="L19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.71017332328560656</v>
-      </c>
-      <c r="M19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.66713844570252179</v>
-      </c>
-      <c r="N19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.69711048158640232</v>
-      </c>
-      <c r="O19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.72286132608240961</v>
-      </c>
-      <c r="P19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.74419970631424381</v>
-      </c>
-      <c r="Q19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.74210125618576317</v>
-      </c>
-      <c r="R19" s="9">
-        <f t="shared" si="104"/>
-        <v>0.75984692925144681</v>
-      </c>
-      <c r="S19" s="9">
-        <f t="shared" ref="S19:AD19" si="105">S5/S3</f>
-        <v>0.75619295958279009</v>
-      </c>
-      <c r="T19" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="AJ19" s="9">
+        <f t="shared" ref="AJ19:AW19" si="105">AJ5/AJ3</f>
+        <v>0.81543116490166412</v>
+      </c>
+      <c r="AK19" s="9">
         <f t="shared" si="105"/>
-        <v>0.75115961800818554</v>
-      </c>
-      <c r="U19" s="9">
+        <v>0.81483860607033887</v>
+      </c>
+      <c r="AL19" s="9">
         <f t="shared" si="105"/>
-        <v>0.75433342408567017</v>
-      </c>
-      <c r="V19" s="9">
+        <v>0.68997510749038249</v>
+      </c>
+      <c r="AM19" s="9">
         <f t="shared" si="105"/>
-        <v>0.73662551440329216</v>
-      </c>
-      <c r="W19" s="9">
+        <v>0.74277421400521959</v>
+      </c>
+      <c r="AN19" s="9">
         <f t="shared" si="105"/>
-        <v>0.76126289126108204</v>
-      </c>
-      <c r="X19" s="9">
+        <v>0.74948782153425908</v>
+      </c>
+      <c r="AO19" s="9">
         <f t="shared" si="105"/>
-        <v>0.7658733643628699</v>
-      </c>
-      <c r="Y19" s="9">
+        <v>0.76193316104521458</v>
+      </c>
+      <c r="AP19" s="9">
         <f t="shared" si="105"/>
-        <v>0.76159056919151935</v>
-      </c>
-      <c r="Z19" s="9">
+        <v>0.75785051336462816</v>
+      </c>
+      <c r="AQ19" s="9">
         <f t="shared" si="105"/>
-        <v>0.75900566942869607</v>
-      </c>
-      <c r="AA19" s="9">
+        <v>0.7745148531168885</v>
+      </c>
+      <c r="AR19" s="9">
         <f t="shared" si="105"/>
-        <v>0.76051524710830709</v>
-      </c>
-      <c r="AB19" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="AS19" s="9">
         <f t="shared" si="105"/>
-        <v>0.754752688172043</v>
-      </c>
-      <c r="AC19" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="AT19" s="9">
         <f t="shared" si="105"/>
-        <v>0.75889596602972398</v>
-      </c>
-      <c r="AD19" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="AU19" s="9">
         <f t="shared" si="105"/>
-        <v>0.75728401317456295</v>
-      </c>
-      <c r="AE19" s="9">
-        <f t="shared" ref="AE19:AH19" si="106">AE5/AE3</f>
-        <v>0.76300331999659488</v>
-      </c>
-      <c r="AF19" s="9">
+        <v>0.78</v>
+      </c>
+      <c r="AV19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.78</v>
+      </c>
+      <c r="AW19" s="9">
+        <f t="shared" si="105"/>
+        <v>0.78</v>
+      </c>
+      <c r="AX19" s="9">
+        <f t="shared" ref="AX19:AZ19" si="106">AX5/AX3</f>
+        <v>0.78</v>
+      </c>
+      <c r="AY19" s="9">
         <f t="shared" si="106"/>
-        <v>0.77555044364114356</v>
-      </c>
-      <c r="AG19" s="9">
+        <v>0.78000000000000014</v>
+      </c>
+      <c r="AZ19" s="9">
         <f t="shared" si="106"/>
-        <v>0.76</v>
-      </c>
-      <c r="AH19" s="9">
-        <f t="shared" si="106"/>
-        <v>0.76</v>
-      </c>
-      <c r="AJ19" s="9">
-        <f t="shared" ref="AJ19:AW19" si="107">AJ5/AJ3</f>
-        <v>0.81543116490166412</v>
-      </c>
-      <c r="AK19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.81483860607033887</v>
-      </c>
-      <c r="AL19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.68997510749038249</v>
-      </c>
-      <c r="AM19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.74277421400521959</v>
-      </c>
-      <c r="AN19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.74948782153425908</v>
-      </c>
-      <c r="AO19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76193316104521458</v>
-      </c>
-      <c r="AP19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.75785051336462816</v>
-      </c>
-      <c r="AQ19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76458735462277716</v>
-      </c>
-      <c r="AR19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AS19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AT19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AU19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AV19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AW19" s="9">
-        <f t="shared" si="107"/>
-        <v>0.76</v>
-      </c>
-      <c r="AX19" s="9">
-        <f t="shared" ref="AX19:AZ19" si="108">AX5/AX3</f>
-        <v>0.76</v>
-      </c>
-      <c r="AY19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.76000000000000012</v>
-      </c>
-      <c r="AZ19" s="9">
-        <f t="shared" si="108"/>
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="20" spans="2:55" x14ac:dyDescent="0.3">
@@ -4561,19 +4555,19 @@
         <v>42</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:F20" si="109">C9/C3</f>
+        <f t="shared" ref="C20:F20" si="107">C9/C3</f>
         <v>-2.9950083194675344E-2</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>4.6979865771812082E-2</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>-1.2208657047724846E-2</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>5.1984877126654047E-2</v>
       </c>
       <c r="G20" s="9">
@@ -4581,180 +4575,180 @@
         <v>1.3114754098360725E-2</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" ref="H20:R20" si="110">H9/H3</f>
+        <f t="shared" ref="H20:R20" si="108">H9/H3</f>
         <v>1.5089163237311404E-2</v>
       </c>
       <c r="I20" s="9">
+        <f t="shared" si="108"/>
+        <v>-9.6038415366147181E-3</v>
+      </c>
+      <c r="J20" s="9">
+        <f t="shared" si="108"/>
+        <v>5.629314922995228E-2</v>
+      </c>
+      <c r="K20" s="9">
+        <f t="shared" si="108"/>
+        <v>7.1297989031078604E-2</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.28349660889223816</v>
+      </c>
+      <c r="M20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.2474266598044261</v>
+      </c>
+      <c r="N20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.29019830028328619</v>
+      </c>
+      <c r="O20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.23656138883078853</v>
+      </c>
+      <c r="P20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.28839941262848767</v>
+      </c>
+      <c r="Q20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.27683669585078036</v>
+      </c>
+      <c r="R20" s="9">
+        <f t="shared" si="108"/>
+        <v>0.23511293634496933</v>
+      </c>
+      <c r="S20" s="9">
+        <f t="shared" ref="S20:AD20" si="109">S9/S3</f>
+        <v>0.1742410132240641</v>
+      </c>
+      <c r="T20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.11068667576170983</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="109"/>
+        <v>6.0441056357201269E-2</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="109"/>
+        <v>-0.11629987475398114</v>
+      </c>
+      <c r="W20" s="9">
+        <f t="shared" si="109"/>
+        <v>8.8655690247874432E-3</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.15596733116712036</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.14902788774522752</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.14696903619712173</v>
+      </c>
+      <c r="AA20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.1778829302488609</v>
+      </c>
+      <c r="AB20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.174021505376344</v>
+      </c>
+      <c r="AC20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.15524416135881108</v>
+      </c>
+      <c r="AD20" s="9">
+        <f t="shared" si="109"/>
+        <v>0.19001773498859889</v>
+      </c>
+      <c r="AE20" s="9">
+        <f t="shared" ref="AE20:AH20" si="110">AE9/AE3</f>
+        <v>0.20566953264663324</v>
+      </c>
+      <c r="AF20" s="9">
         <f t="shared" si="110"/>
-        <v>-9.6038415366147181E-3</v>
-      </c>
-      <c r="J20" s="9">
+        <v>0.26429510351626689</v>
+      </c>
+      <c r="AG20" s="9">
         <f t="shared" si="110"/>
-        <v>5.629314922995228E-2</v>
-      </c>
-      <c r="K20" s="9">
+        <v>0.252398764026671</v>
+      </c>
+      <c r="AH20" s="9">
         <f t="shared" si="110"/>
-        <v>7.1297989031078604E-2</v>
-      </c>
-      <c r="L20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.28349660889223816</v>
-      </c>
-      <c r="M20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.2474266598044261</v>
-      </c>
-      <c r="N20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.29019830028328619</v>
-      </c>
-      <c r="O20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.23656138883078853</v>
-      </c>
-      <c r="P20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.28839941262848767</v>
-      </c>
-      <c r="Q20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.27683669585078036</v>
-      </c>
-      <c r="R20" s="9">
-        <f t="shared" si="110"/>
-        <v>0.23511293634496933</v>
-      </c>
-      <c r="S20" s="9">
-        <f t="shared" ref="S20:AD20" si="111">S9/S3</f>
-        <v>0.1742410132240641</v>
-      </c>
-      <c r="T20" s="9">
+        <v>0.2370401622718053</v>
+      </c>
+      <c r="AJ20" s="9">
+        <f t="shared" ref="AJ20:AW20" si="111">AJ9/AJ3</f>
+        <v>1.8456883509833568E-2</v>
+      </c>
+      <c r="AK20" s="9">
         <f t="shared" si="111"/>
-        <v>0.11068667576170983</v>
-      </c>
-      <c r="U20" s="9">
+        <v>2.0555644772763743E-2</v>
+      </c>
+      <c r="AL20" s="9">
         <f t="shared" si="111"/>
-        <v>6.0441056357201269E-2</v>
-      </c>
-      <c r="V20" s="9">
+        <v>0.2488873802519424</v>
+      </c>
+      <c r="AM20" s="9">
         <f t="shared" si="111"/>
-        <v>-0.11629987475398114</v>
-      </c>
-      <c r="W20" s="9">
+        <v>0.2594209614868655</v>
+      </c>
+      <c r="AN20" s="9">
         <f t="shared" si="111"/>
-        <v>8.8655690247874432E-3</v>
-      </c>
-      <c r="X20" s="9">
+        <v>5.5861597996813159E-2</v>
+      </c>
+      <c r="AO20" s="9">
         <f t="shared" si="111"/>
-        <v>0.15596733116712036</v>
-      </c>
-      <c r="Y20" s="9">
+        <v>0.11602942150950898</v>
+      </c>
+      <c r="AP20" s="9">
         <f t="shared" si="111"/>
-        <v>0.14902788774522752</v>
-      </c>
-      <c r="Z20" s="9">
+        <v>0.17428675540694052</v>
+      </c>
+      <c r="AQ20" s="9">
         <f t="shared" si="111"/>
-        <v>0.14696903619712173</v>
-      </c>
-      <c r="AA20" s="9">
+        <v>0.24017387005067778</v>
+      </c>
+      <c r="AR20" s="9">
         <f t="shared" si="111"/>
-        <v>0.1778829302488609</v>
-      </c>
-      <c r="AB20" s="9">
+        <v>0.24774997769922402</v>
+      </c>
+      <c r="AS20" s="9">
         <f t="shared" si="111"/>
-        <v>0.174021505376344</v>
-      </c>
-      <c r="AC20" s="9">
+        <v>0.24351113763313426</v>
+      </c>
+      <c r="AT20" s="9">
         <f t="shared" si="111"/>
-        <v>0.15524416135881108</v>
-      </c>
-      <c r="AD20" s="9">
+        <v>0.24097164394633364</v>
+      </c>
+      <c r="AU20" s="9">
         <f t="shared" si="111"/>
-        <v>0.19001773498859889</v>
-      </c>
-      <c r="AE20" s="9">
-        <f t="shared" ref="AE20:AH20" si="112">AE9/AE3</f>
-        <v>0.20566953264663324</v>
-      </c>
-      <c r="AF20" s="9">
+        <v>0.24097164394633352</v>
+      </c>
+      <c r="AV20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.24097164394633347</v>
+      </c>
+      <c r="AW20" s="9">
+        <f t="shared" si="111"/>
+        <v>0.24097164394633361</v>
+      </c>
+      <c r="AX20" s="9">
+        <f t="shared" ref="AX20:AZ20" si="112">AX9/AX3</f>
+        <v>0.24097164394633347</v>
+      </c>
+      <c r="AY20" s="9">
         <f t="shared" si="112"/>
-        <v>0.26429510351626689</v>
-      </c>
-      <c r="AG20" s="9">
+        <v>0.24097164394633366</v>
+      </c>
+      <c r="AZ20" s="9">
         <f t="shared" si="112"/>
-        <v>0.21398229379481631</v>
-      </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="112"/>
-        <v>0.22178462107197078</v>
-      </c>
-      <c r="AJ20" s="9">
-        <f t="shared" ref="AJ20:AW20" si="113">AJ9/AJ3</f>
-        <v>1.8456883509833568E-2</v>
-      </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="113"/>
-        <v>2.0555644772763743E-2</v>
-      </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.2488873802519424</v>
-      </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.2594209614868655</v>
-      </c>
-      <c r="AN20" s="9">
-        <f t="shared" si="113"/>
-        <v>5.5861597996813159E-2</v>
-      </c>
-      <c r="AO20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.11602942150950898</v>
-      </c>
-      <c r="AP20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.17428675540694052</v>
-      </c>
-      <c r="AQ20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.22649840374113722</v>
-      </c>
-      <c r="AR20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.22432043725817427</v>
-      </c>
-      <c r="AS20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.22004498798816341</v>
-      </c>
-      <c r="AT20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.21747117598804627</v>
-      </c>
-      <c r="AU20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.21747117598804624</v>
-      </c>
-      <c r="AV20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.21747117598804616</v>
-      </c>
-      <c r="AW20" s="9">
-        <f t="shared" si="113"/>
-        <v>0.21747117598804611</v>
-      </c>
-      <c r="AX20" s="9">
-        <f t="shared" ref="AX20:AZ20" si="114">AX9/AX3</f>
-        <v>0.21747117598804619</v>
-      </c>
-      <c r="AY20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.21747117598804624</v>
-      </c>
-      <c r="AZ20" s="9">
-        <f t="shared" si="114"/>
-        <v>0.21747117598804622</v>
+        <v>0.24097164394633358</v>
       </c>
       <c r="BB20" t="s">
         <v>47</v>
@@ -4776,176 +4770,176 @@
         <v>1.1904761904761907</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" ref="H21:R21" si="115">H6/D6-1</f>
+        <f t="shared" ref="H21:R21" si="113">H6/D6-1</f>
         <v>1.1428571428571428</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>0.97752808988764062</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>0.91666666666666652</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>0.9130434782608694</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.8466666666666667</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.4204545454545454</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.531400966183575</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.4696969696969697</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>0.92740046838407464</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.312206572769953</v>
       </c>
       <c r="R21" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
         <v>1.2328244274809159</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21" si="116">S6/O6-1</f>
+        <f t="shared" ref="S21" si="114">S6/O6-1</f>
         <v>1.21319018404908</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" ref="T21" si="117">T6/P6-1</f>
+        <f t="shared" ref="T21" si="115">T6/P6-1</f>
         <v>1.0972053462940461</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" ref="U21" si="118">U6/Q6-1</f>
+        <f t="shared" ref="U21" si="116">U6/Q6-1</f>
         <v>0.98883248730964479</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" ref="V21" si="119">V6/R6-1</f>
+        <f t="shared" ref="V21" si="117">V6/R6-1</f>
         <v>1.2333333333333334</v>
       </c>
       <c r="W21" s="9">
-        <f t="shared" ref="W21" si="120">W6/S6-1</f>
+        <f t="shared" ref="W21" si="118">W6/S6-1</f>
         <v>0.45045045045045051</v>
       </c>
       <c r="X21" s="9">
-        <f t="shared" ref="X21" si="121">X6/T6-1</f>
+        <f t="shared" ref="X21" si="119">X6/T6-1</f>
         <v>0.11123986095017391</v>
       </c>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21" si="122">Y6/U6-1</f>
+        <f t="shared" ref="Y21" si="120">Y6/U6-1</f>
         <v>4.5941807044411753E-3</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21" si="123">Z6/V6-1</f>
+        <f t="shared" ref="Z21" si="121">Z6/V6-1</f>
         <v>-0.21431305013394564</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" ref="AA21" si="124">AA6/W6-1</f>
+        <f t="shared" ref="AA21" si="122">AA6/W6-1</f>
         <v>-1.7677974199713398E-2</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" ref="AB21" si="125">AB6/X6-1</f>
+        <f t="shared" ref="AB21" si="123">AB6/X6-1</f>
         <v>7.8206465067778952E-2</v>
       </c>
       <c r="AC21" s="9">
-        <f t="shared" ref="AC21" si="126">AC6/Y6-1</f>
+        <f t="shared" ref="AC21" si="124">AC6/Y6-1</f>
         <v>0.13313008130081294</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21" si="127">AD6/Z6-1</f>
+        <f t="shared" ref="AD21" si="125">AD6/Z6-1</f>
         <v>5.7476863127130962E-2</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" ref="AE21" si="128">AE6/AA6-1</f>
+        <f t="shared" ref="AE21" si="126">AE6/AA6-1</f>
         <v>-9.7276264591439343E-4</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" ref="AF21" si="129">AF6/AB6-1</f>
+        <f t="shared" ref="AF21" si="127">AF6/AB6-1</f>
         <v>-1.9342359767892114E-3</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" ref="AG21" si="130">AG6/AC6-1</f>
-        <v>-2.0000000000000018E-2</v>
+        <f t="shared" ref="AG21" si="128">AG6/AC6-1</f>
+        <v>-5.7847533632287007E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" ref="AH21" si="131">AH6/AD6-1</f>
+        <f t="shared" ref="AH21" si="129">AH6/AD6-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="9"/>
       <c r="AK21" s="9">
-        <f t="shared" ref="AK21:AW21" si="132">AK6/AJ6-1</f>
+        <f t="shared" ref="AK21:AW21" si="130">AK6/AJ6-1</f>
         <v>1.0333333333333337</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.4456035767511173</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.2120658135283366</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.1325068870523411</v>
       </c>
       <c r="AO21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>3.7592042371786816E-2</v>
       </c>
       <c r="AP21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>6.1379482071713065E-2</v>
       </c>
       <c r="AQ21" s="9">
-        <f t="shared" si="132"/>
-        <v>1.7043988269793697E-3</v>
+        <f t="shared" si="130"/>
+        <v>-8.1958944281526058E-3</v>
       </c>
       <c r="AR21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AS21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AT21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW21" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX21" s="9">
-        <f t="shared" ref="AX21" si="133">AX6/AW6-1</f>
+        <f t="shared" ref="AX21" si="131">AX6/AW6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY21" s="9">
-        <f t="shared" ref="AY21" si="134">AY6/AX6-1</f>
+        <f t="shared" ref="AY21" si="132">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ21" s="9">
-        <f t="shared" ref="AZ21" si="135">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ21" si="133">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB21" t="s">
@@ -4960,19 +4954,19 @@
         <v>44</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:F22" si="136">C7/C3</f>
+        <f t="shared" ref="C22:F22" si="134">C7/C3</f>
         <v>0.60399334442595665</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.55033557046979864</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.59378468368479476</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>0.5207939508506616</v>
       </c>
       <c r="G22" s="9">
@@ -4980,187 +4974,187 @@
         <v>0.52459016393442626</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" ref="H22:R22" si="137">H7/H3</f>
+        <f t="shared" ref="H22:R22" si="135">H7/H3</f>
         <v>0.54663923182441698</v>
       </c>
       <c r="I22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.57623049219687872</v>
+      </c>
+      <c r="J22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.53584705257567711</v>
+      </c>
+      <c r="K22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.37050578915295551</v>
+      </c>
+      <c r="L22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.23993971363978897</v>
+      </c>
+      <c r="M22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.24472465259907356</v>
+      </c>
+      <c r="N22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.24249291784702551</v>
+      </c>
+      <c r="O22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.25695461200585651</v>
+      </c>
+      <c r="P22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.26549192364170338</v>
+      </c>
+      <c r="Q22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.27950133231823371</v>
+      </c>
+      <c r="R22" s="9">
+        <f t="shared" si="135"/>
+        <v>0.303714765727086</v>
+      </c>
+      <c r="S22" s="9">
+        <f t="shared" ref="S22:AD22" si="136">S7/S3</f>
+        <v>0.33786552430620231</v>
+      </c>
+      <c r="T22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.36425648021828105</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.38814774480442865</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.4523170513508678</v>
+      </c>
+      <c r="W22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.38221458295639582</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.3279178010011416</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.32937450514647659</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.32368076755342351</v>
+      </c>
+      <c r="AA22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.3049421661409043</v>
+      </c>
+      <c r="AB22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.3086451612903226</v>
+      </c>
+      <c r="AC22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.30717622080679402</v>
+      </c>
+      <c r="AD22" s="9">
+        <f t="shared" si="136"/>
+        <v>0.30309940038848071</v>
+      </c>
+      <c r="AE22" s="9">
+        <f t="shared" ref="AE22:AH22" si="137">AE7/AE3</f>
+        <v>0.29539456882608323</v>
+      </c>
+      <c r="AF22" s="9">
         <f t="shared" si="137"/>
-        <v>0.57623049219687872</v>
-      </c>
-      <c r="J22" s="9">
+        <v>0.27850805126519879</v>
+      </c>
+      <c r="AG22" s="9">
         <f t="shared" si="137"/>
-        <v>0.53584705257567711</v>
-      </c>
-      <c r="K22" s="9">
+        <v>0.27874451130265088</v>
+      </c>
+      <c r="AH22" s="9">
         <f t="shared" si="137"/>
-        <v>0.37050578915295551</v>
-      </c>
-      <c r="L22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.23993971363978897</v>
-      </c>
-      <c r="M22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.24472465259907356</v>
-      </c>
-      <c r="N22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.24249291784702551</v>
-      </c>
-      <c r="O22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.25695461200585651</v>
-      </c>
-      <c r="P22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.26549192364170338</v>
-      </c>
-      <c r="Q22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.27950133231823371</v>
-      </c>
-      <c r="R22" s="9">
-        <f t="shared" si="137"/>
-        <v>0.303714765727086</v>
-      </c>
-      <c r="S22" s="9">
-        <f t="shared" ref="S22:AD22" si="138">S7/S3</f>
-        <v>0.33786552430620231</v>
-      </c>
-      <c r="T22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AJ22" s="9">
+        <f t="shared" ref="AJ22:AW22" si="138">AJ7/AJ3</f>
+        <v>0.562481089258699</v>
+      </c>
+      <c r="AK22" s="9">
         <f t="shared" si="138"/>
-        <v>0.36425648021828105</v>
-      </c>
-      <c r="U22" s="9">
+        <v>0.54697286012526092</v>
+      </c>
+      <c r="AL22" s="9">
         <f t="shared" si="138"/>
-        <v>0.38814774480442865</v>
-      </c>
-      <c r="V22" s="9">
+        <v>0.25835407709134794</v>
+      </c>
+      <c r="AM22" s="9">
         <f t="shared" si="138"/>
-        <v>0.4523170513508678</v>
-      </c>
-      <c r="W22" s="9">
+        <v>0.27707992877875071</v>
+      </c>
+      <c r="AN22" s="9">
         <f t="shared" si="138"/>
-        <v>0.38221458295639582</v>
-      </c>
-      <c r="X22" s="9">
+        <v>0.38620532665604368</v>
+      </c>
+      <c r="AO22" s="9">
         <f t="shared" si="138"/>
-        <v>0.3279178010011416</v>
-      </c>
-      <c r="Y22" s="9">
+        <v>0.3404678285070572</v>
+      </c>
+      <c r="AP22" s="9">
         <f t="shared" si="138"/>
-        <v>0.32937450514647659</v>
-      </c>
-      <c r="Z22" s="9">
+        <v>0.3059610314449232</v>
+      </c>
+      <c r="AQ22" s="9">
         <f t="shared" si="138"/>
-        <v>0.32368076755342351</v>
-      </c>
-      <c r="AA22" s="9">
+        <v>0.28303324955708464</v>
+      </c>
+      <c r="AR22" s="9">
         <f t="shared" si="138"/>
-        <v>0.3049421661409043</v>
-      </c>
-      <c r="AB22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AS22" s="9">
         <f t="shared" si="138"/>
-        <v>0.3086451612903226</v>
-      </c>
-      <c r="AC22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AT22" s="9">
         <f t="shared" si="138"/>
-        <v>0.30717622080679402</v>
-      </c>
-      <c r="AD22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AU22" s="9">
         <f t="shared" si="138"/>
-        <v>0.30309940038848071</v>
-      </c>
-      <c r="AE22" s="9">
-        <f t="shared" ref="AE22:AH22" si="139">AE7/AE3</f>
-        <v>0.29539456882608323</v>
-      </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="139"/>
-        <v>0.27850805126519879</v>
-      </c>
-      <c r="AG22" s="9">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AV22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AW22" s="9">
+        <f t="shared" si="138"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AX22" s="9">
+        <f t="shared" ref="AX22:AZ22" si="139">AX7/AX3</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="AY22" s="9">
         <f t="shared" si="139"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AH22" s="9">
+      <c r="AZ22" s="9">
         <f t="shared" si="139"/>
         <v>0.28000000000000003</v>
       </c>
-      <c r="AJ22" s="9">
-        <f t="shared" ref="AJ22:AW22" si="140">AJ7/AJ3</f>
-        <v>0.562481089258699</v>
-      </c>
-      <c r="AK22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.54697286012526092</v>
-      </c>
-      <c r="AL22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.25835407709134794</v>
-      </c>
-      <c r="AM22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.27707992877875071</v>
-      </c>
-      <c r="AN22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.38620532665604368</v>
-      </c>
-      <c r="AO22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.3404678285070572</v>
-      </c>
-      <c r="AP22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.3059610314449232</v>
-      </c>
-      <c r="AQ22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28332325814941833</v>
-      </c>
-      <c r="AR22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AS22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AT22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AU22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AV22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AW22" s="9">
-        <f t="shared" si="140"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AX22" s="9">
-        <f t="shared" ref="AX22:AZ22" si="141">AX7/AX3</f>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AY22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="AZ22" s="9">
-        <f t="shared" si="141"/>
-        <v>0.28000000000000003</v>
-      </c>
       <c r="BB22" t="s">
         <v>49</v>
       </c>
       <c r="BC22" s="3">
         <f>NPV(BC21,AQ14:FD14)</f>
-        <v>15126.360715129144</v>
+        <v>20398.984359939488</v>
       </c>
     </row>
     <row r="23" spans="2:55" x14ac:dyDescent="0.3">
@@ -5176,176 +5170,176 @@
         <v>1.4342105263157894</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" ref="H23:R23" si="142">H8/D8-1</f>
+        <f t="shared" ref="H23:R23" si="140">H8/D8-1</f>
         <v>1.1000000000000001</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0.98333333333333339</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0.58389261744966459</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.8702702702702703</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>2.8666666666666667</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>2.9243697478991599</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>2.9279661016949152</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>1.9020715630885121</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0.38054187192118216</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>3.5331905781584627E-2</v>
       </c>
       <c r="R23" s="9">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>0.29234088457389418</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23" si="143">S8/O8-1</f>
+        <f t="shared" ref="S23" si="141">S8/O8-1</f>
         <v>-0.23556132381570405</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" ref="T23" si="144">T8/P8-1</f>
+        <f t="shared" ref="T23" si="142">T8/P8-1</f>
         <v>0.16949152542372881</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" ref="U23" si="145">U8/Q8-1</f>
+        <f t="shared" ref="U23" si="143">U8/Q8-1</f>
         <v>0.45811789038262662</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" ref="V23" si="146">V8/R8-1</f>
+        <f t="shared" ref="V23" si="144">V8/R8-1</f>
         <v>0.55676126878130217</v>
       </c>
       <c r="W23" s="9">
-        <f t="shared" ref="W23" si="147">W8/S8-1</f>
+        <f t="shared" ref="W23" si="145">W8/S8-1</f>
         <v>0.69694397283531417</v>
       </c>
       <c r="X23" s="9">
-        <f t="shared" ref="X23" si="148">X8/T8-1</f>
+        <f t="shared" ref="X23" si="146">X8/T8-1</f>
         <v>-1.372997711670465E-2</v>
       </c>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="149">Y8/U8-1</f>
+        <f t="shared" ref="Y23" si="147">Y8/U8-1</f>
         <v>-0.11276595744680851</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23" si="150">Z8/V8-1</f>
+        <f t="shared" ref="Z23" si="148">Z8/V8-1</f>
         <v>-0.32815013404825744</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" ref="AA23" si="151">AA8/W8-1</f>
+        <f t="shared" ref="AA23" si="149">AA8/W8-1</f>
         <v>-0.44322161080540268</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" ref="AB23" si="152">AB8/X8-1</f>
+        <f t="shared" ref="AB23" si="150">AB8/X8-1</f>
         <v>-0.15313225058004643</v>
       </c>
       <c r="AC23" s="9">
-        <f t="shared" ref="AC23" si="153">AC8/Y8-1</f>
+        <f t="shared" ref="AC23" si="151">AC8/Y8-1</f>
         <v>7.9936051159072985E-3</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" ref="AD23" si="154">AD8/Z8-1</f>
+        <f t="shared" ref="AD23" si="152">AD8/Z8-1</f>
         <v>-0.23623304070231443</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" ref="AE23" si="155">AE8/AA8-1</f>
+        <f t="shared" ref="AE23" si="153">AE8/AA8-1</f>
         <v>-8.0862533692722338E-2</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" ref="AF23" si="156">AF8/AB8-1</f>
+        <f t="shared" ref="AF23" si="154">AF8/AB8-1</f>
         <v>-0.29771689497716891</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" ref="AG23" si="157">AG8/AC8-1</f>
-        <v>-9.9999999999999978E-2</v>
+        <f t="shared" ref="AG23" si="155">AG8/AC8-1</f>
+        <v>-0.24900872323552725</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" ref="AH23" si="158">AH8/AD8-1</f>
+        <f t="shared" ref="AH23" si="156">AH8/AD8-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AJ23" s="9"/>
       <c r="AK23" s="9">
-        <f t="shared" ref="AK23:AW23" si="159">AK8/AJ8-1</f>
+        <f t="shared" ref="AK23:AW23" si="157">AK8/AJ8-1</f>
         <v>0.95280898876404496</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>2.6869965477560416</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>0.50655430711610472</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>0.19411642842345134</v>
       </c>
       <c r="AO23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>5.5517002081888478E-3</v>
       </c>
       <c r="AP23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>-0.23636991028295384</v>
       </c>
       <c r="AQ23" s="9">
-        <f t="shared" si="159"/>
-        <v>-0.11166967916854942</v>
+        <f t="shared" si="157"/>
+        <v>-0.15412336195210119</v>
       </c>
       <c r="AR23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AS23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AT23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AU23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW23" s="9">
-        <f t="shared" si="159"/>
+        <f t="shared" si="157"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX23" s="9">
-        <f t="shared" ref="AX23" si="160">AX8/AW8-1</f>
+        <f t="shared" ref="AX23" si="158">AX8/AW8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY23" s="9">
-        <f t="shared" ref="AY23" si="161">AY8/AX8-1</f>
+        <f t="shared" ref="AY23" si="159">AY8/AX8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ23" s="9">
-        <f t="shared" ref="AZ23" si="162">AZ8/AY8-1</f>
+        <f t="shared" ref="AZ23" si="160">AZ8/AY8-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BB23" t="s">
@@ -5353,7 +5347,7 @@
       </c>
       <c r="BC23" s="3">
         <f>Main!D8</f>
-        <v>8426.6</v>
+        <v>8995.9</v>
       </c>
     </row>
     <row r="24" spans="2:55" x14ac:dyDescent="0.3">
@@ -5361,19 +5355,19 @@
         <v>36</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:F24" si="163">C12/C11</f>
+        <f t="shared" ref="C24:F24" si="161">C12/C11</f>
         <v>-7.1428571428572021E-2</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="161"/>
         <v>2.4390243902439029E-2</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="161"/>
         <v>-0.1999999999999966</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="163"/>
+        <f t="shared" si="161"/>
         <v>-6.557377049180331E-2</v>
       </c>
       <c r="G24" s="9">
@@ -5381,187 +5375,187 @@
         <v>0.115384615384615</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" ref="H24:R24" si="164">H12/H11</f>
+        <f t="shared" ref="H24:R24" si="162">H12/H11</f>
         <v>0.1791044776119402</v>
       </c>
       <c r="I24" s="9">
+        <f t="shared" si="162"/>
+        <v>0.1153846153846159</v>
+      </c>
+      <c r="J24" s="9">
+        <f t="shared" si="162"/>
+        <v>-5.4794520547945147E-2</v>
+      </c>
+      <c r="K24" s="9">
+        <f t="shared" si="162"/>
+        <v>7.1917808219178092E-2</v>
+      </c>
+      <c r="L24" s="9">
+        <f t="shared" si="162"/>
+        <v>2.2082018927444793E-2</v>
+      </c>
+      <c r="M24" s="9">
+        <f t="shared" si="162"/>
+        <v>-2.369912416280268E-2</v>
+      </c>
+      <c r="N24" s="9">
+        <f t="shared" si="162"/>
+        <v>1.5117157974300827E-2</v>
+      </c>
+      <c r="O24" s="9">
+        <f t="shared" si="162"/>
+        <v>6.1188811188811181E-3</v>
+      </c>
+      <c r="P24" s="9">
+        <f t="shared" si="162"/>
+        <v>2.0994133991972821E-2</v>
+      </c>
+      <c r="Q24" s="9">
+        <f t="shared" si="162"/>
+        <v>0.17036314891542778</v>
+      </c>
+      <c r="R24" s="9">
+        <f t="shared" si="162"/>
+        <v>-2.5385724585436167</v>
+      </c>
+      <c r="S24" s="9">
+        <f t="shared" ref="S24:AD24" si="163">S12/S11</f>
+        <v>0.20876826722338201</v>
+      </c>
+      <c r="T24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.49336283185840735</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.11678832116788304</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="163"/>
+        <v>-1.624685138539038</v>
+      </c>
+      <c r="W24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.64203233256350978</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.27316293929712465</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.24004305705059187</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.1533012184754888</v>
+      </c>
+      <c r="AA24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.2592465753424657</v>
+      </c>
+      <c r="AB24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.25239071038251376</v>
+      </c>
+      <c r="AC24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.26186229040313946</v>
+      </c>
+      <c r="AD24" s="9">
+        <f t="shared" si="163"/>
+        <v>0.18321119253830781</v>
+      </c>
+      <c r="AE24" s="9">
+        <f t="shared" ref="AE24:AH24" si="164">AE12/AE11</f>
+        <v>0.19379354021532613</v>
+      </c>
+      <c r="AF24" s="9">
         <f t="shared" si="164"/>
-        <v>0.1153846153846159</v>
-      </c>
-      <c r="J24" s="9">
+        <v>0.19982158786797499</v>
+      </c>
+      <c r="AG24" s="9">
         <f t="shared" si="164"/>
-        <v>-5.4794520547945147E-2</v>
-      </c>
-      <c r="K24" s="9">
+        <v>0.22876557191392979</v>
+      </c>
+      <c r="AH24" s="9">
         <f t="shared" si="164"/>
-        <v>7.1917808219178092E-2</v>
-      </c>
-      <c r="L24" s="9">
-        <f t="shared" si="164"/>
-        <v>2.2082018927444793E-2</v>
-      </c>
-      <c r="M24" s="9">
-        <f t="shared" si="164"/>
-        <v>-2.369912416280268E-2</v>
-      </c>
-      <c r="N24" s="9">
-        <f t="shared" si="164"/>
-        <v>1.5117157974300827E-2</v>
-      </c>
-      <c r="O24" s="9">
-        <f t="shared" si="164"/>
-        <v>6.1188811188811181E-3</v>
-      </c>
-      <c r="P24" s="9">
-        <f t="shared" si="164"/>
-        <v>2.0994133991972821E-2</v>
-      </c>
-      <c r="Q24" s="9">
-        <f t="shared" si="164"/>
-        <v>0.17036314891542778</v>
-      </c>
-      <c r="R24" s="9">
-        <f t="shared" si="164"/>
-        <v>-2.5385724585436167</v>
-      </c>
-      <c r="S24" s="9">
-        <f t="shared" ref="S24:AD24" si="165">S12/S11</f>
-        <v>0.20876826722338201</v>
-      </c>
-      <c r="T24" s="9">
+        <v>0.20000000000000004</v>
+      </c>
+      <c r="AJ24" s="9">
+        <f t="shared" ref="AJ24:AW24" si="165">AJ12/AJ11</f>
+        <v>-1.2048192771084343E-2</v>
+      </c>
+      <c r="AK24" s="9">
         <f t="shared" si="165"/>
-        <v>0.49336283185840735</v>
-      </c>
-      <c r="U24" s="9">
+        <v>3.77358490566038E-2</v>
+      </c>
+      <c r="AL24" s="9">
         <f t="shared" si="165"/>
-        <v>0.11678832116788304</v>
-      </c>
-      <c r="V24" s="9">
+        <v>8.4058398466302902E-3</v>
+      </c>
+      <c r="AM24" s="9">
         <f t="shared" si="165"/>
-        <v>-1.624685138539038</v>
-      </c>
-      <c r="W24" s="9">
+        <v>-0.2487065444313335</v>
+      </c>
+      <c r="AN24" s="9">
         <f t="shared" si="165"/>
-        <v>0.64203233256350978</v>
-      </c>
-      <c r="X24" s="9">
+        <v>0.58386837881219855</v>
+      </c>
+      <c r="AO24" s="9">
         <f t="shared" si="165"/>
-        <v>0.27316293929712465</v>
-      </c>
-      <c r="Y24" s="9">
+        <v>0.23414223930802497</v>
+      </c>
+      <c r="AP24" s="9">
         <f t="shared" si="165"/>
-        <v>0.24004305705059187</v>
-      </c>
-      <c r="Z24" s="9">
+        <v>0.2322487456287062</v>
+      </c>
+      <c r="AQ24" s="9">
         <f t="shared" si="165"/>
-        <v>0.1533012184754888</v>
-      </c>
-      <c r="AA24" s="9">
+        <v>0.21067116611961137</v>
+      </c>
+      <c r="AR24" s="9">
         <f t="shared" si="165"/>
-        <v>0.2592465753424657</v>
-      </c>
-      <c r="AB24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AS24" s="9">
         <f t="shared" si="165"/>
-        <v>0.25239071038251376</v>
-      </c>
-      <c r="AC24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AT24" s="9">
         <f t="shared" si="165"/>
-        <v>0.26186229040313946</v>
-      </c>
-      <c r="AD24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AU24" s="9">
         <f t="shared" si="165"/>
-        <v>0.18321119253830781</v>
-      </c>
-      <c r="AE24" s="9">
-        <f t="shared" ref="AE24:AH24" si="166">AE12/AE11</f>
-        <v>0.19379354021532613</v>
-      </c>
-      <c r="AF24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AV24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.22</v>
+      </c>
+      <c r="AW24" s="9">
+        <f t="shared" si="165"/>
+        <v>0.22</v>
+      </c>
+      <c r="AX24" s="9">
+        <f t="shared" ref="AX24:AZ24" si="166">AX12/AX11</f>
+        <v>0.22</v>
+      </c>
+      <c r="AY24" s="9">
         <f t="shared" si="166"/>
-        <v>0.19982158786797499</v>
-      </c>
-      <c r="AG24" s="9">
+        <v>0.22</v>
+      </c>
+      <c r="AZ24" s="9">
         <f t="shared" si="166"/>
-        <v>0.25</v>
-      </c>
-      <c r="AH24" s="9">
-        <f t="shared" si="166"/>
-        <v>0.2</v>
-      </c>
-      <c r="AJ24" s="9">
-        <f t="shared" ref="AJ24:AW24" si="167">AJ12/AJ11</f>
-        <v>-1.2048192771084343E-2</v>
-      </c>
-      <c r="AK24" s="9">
-        <f t="shared" si="167"/>
-        <v>3.77358490566038E-2</v>
-      </c>
-      <c r="AL24" s="9">
-        <f t="shared" si="167"/>
-        <v>8.4058398466302902E-3</v>
-      </c>
-      <c r="AM24" s="9">
-        <f t="shared" si="167"/>
-        <v>-0.2487065444313335</v>
-      </c>
-      <c r="AN24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.58386837881219855</v>
-      </c>
-      <c r="AO24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.23414223930802497</v>
-      </c>
-      <c r="AP24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.2322487456287062</v>
-      </c>
-      <c r="AQ24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.21080651535747846</v>
-      </c>
-      <c r="AR24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.22000000000000003</v>
-      </c>
-      <c r="AS24" s="9">
-        <f t="shared" si="167"/>
         <v>0.22</v>
-      </c>
-      <c r="AT24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.22</v>
-      </c>
-      <c r="AU24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.22</v>
-      </c>
-      <c r="AV24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.22000000000000003</v>
-      </c>
-      <c r="AW24" s="9">
-        <f t="shared" si="167"/>
-        <v>0.22000000000000003</v>
-      </c>
-      <c r="AX24" s="9">
-        <f t="shared" ref="AX24:AZ24" si="168">AX12/AX11</f>
-        <v>0.22</v>
-      </c>
-      <c r="AY24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.22</v>
-      </c>
-      <c r="AZ24" s="9">
-        <f t="shared" si="168"/>
-        <v>0.21999999999999997</v>
       </c>
       <c r="BB24" t="s">
         <v>51</v>
       </c>
       <c r="BC24" s="3">
         <f>BC22+BC23</f>
-        <v>23552.960715129142</v>
+        <v>29394.88435993949</v>
       </c>
     </row>
     <row r="25" spans="2:55" x14ac:dyDescent="0.3">
@@ -5569,19 +5563,19 @@
         <v>46</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:F25" si="169">C14/C3</f>
+        <f t="shared" ref="C25:F25" si="167">C14/C3</f>
         <v>-2.4958402662229425E-2</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>9.3959731543624119E-3</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>-6.6592674805772316E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="169"/>
+        <f t="shared" si="167"/>
         <v>1.8903591682419642E-2</v>
       </c>
       <c r="G25" s="9">
@@ -5589,187 +5583,187 @@
         <v>2.4590163934426943E-3</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" ref="H25:R25" si="170">H14/H3</f>
+        <f t="shared" ref="H25:R25" si="168">H14/H3</f>
         <v>3.7722908093278482E-2</v>
       </c>
       <c r="I25" s="9">
+        <f t="shared" si="168"/>
+        <v>1.3805522208883484E-2</v>
+      </c>
+      <c r="J25" s="9">
+        <f t="shared" si="168"/>
+        <v>8.1784386617100455E-2</v>
+      </c>
+      <c r="K25" s="9">
+        <f t="shared" si="168"/>
+        <v>8.2571602681291892E-2</v>
+      </c>
+      <c r="L25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.28003014318010555</v>
+      </c>
+      <c r="M25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.25540401441070509</v>
+      </c>
+      <c r="N25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.29507082152974512</v>
+      </c>
+      <c r="O25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.23781635641079271</v>
+      </c>
+      <c r="P25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.31023005384238878</v>
+      </c>
+      <c r="Q25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.32384849638370761</v>
+      </c>
+      <c r="R25" s="9">
+        <f t="shared" si="168"/>
+        <v>0.45799887997013267</v>
+      </c>
+      <c r="S25" s="9">
+        <f t="shared" ref="S25:AD25" si="169">S14/S3</f>
+        <v>0.10588563978394488</v>
+      </c>
+      <c r="T25" s="9">
+        <f t="shared" si="169"/>
+        <v>4.1655297862664802E-2</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="169"/>
+        <v>4.3924131046374514E-2</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="169"/>
+        <v>-9.3218822687421835E-2</v>
+      </c>
+      <c r="W25" s="9">
+        <f t="shared" si="169"/>
+        <v>1.4022073457571954E-2</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.15983138666900848</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.12421923110759227</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.26061927605756652</v>
+      </c>
+      <c r="AA25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.18953732912723453</v>
+      </c>
+      <c r="AB25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.18830107526881712</v>
+      </c>
+      <c r="AC25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.17571125265392787</v>
+      </c>
+      <c r="AD25" s="9">
+        <f t="shared" si="169"/>
+        <v>0.31061565746136305</v>
+      </c>
+      <c r="AE25" s="9">
+        <f t="shared" ref="AE25:AH25" si="170">AE14/AE3</f>
+        <v>0.21673618796288421</v>
+      </c>
+      <c r="AF25" s="9">
         <f t="shared" si="170"/>
-        <v>1.3805522208883484E-2</v>
-      </c>
-      <c r="J25" s="9">
+        <v>0.2947748931975025</v>
+      </c>
+      <c r="AG25" s="9">
         <f t="shared" si="170"/>
-        <v>8.1784386617100455E-2</v>
-      </c>
-      <c r="K25" s="9">
+        <v>0.49837371930395197</v>
+      </c>
+      <c r="AH25" s="9">
         <f t="shared" si="170"/>
-        <v>8.2571602681291892E-2</v>
-      </c>
-      <c r="L25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.28003014318010555</v>
-      </c>
-      <c r="M25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.25540401441070509</v>
-      </c>
-      <c r="N25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.29507082152974512</v>
-      </c>
-      <c r="O25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.23781635641079271</v>
-      </c>
-      <c r="P25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.31023005384238878</v>
-      </c>
-      <c r="Q25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.32384849638370761</v>
-      </c>
-      <c r="R25" s="9">
-        <f t="shared" si="170"/>
-        <v>0.45799887997013267</v>
-      </c>
-      <c r="S25" s="9">
-        <f t="shared" ref="S25:AD25" si="171">S14/S3</f>
-        <v>0.10588563978394488</v>
-      </c>
-      <c r="T25" s="9">
+        <v>0.25454085192697773</v>
+      </c>
+      <c r="AJ25" s="9">
+        <f t="shared" ref="AJ25:AW25" si="171">AJ14/AJ3</f>
+        <v>1.8154311649016442E-3</v>
+      </c>
+      <c r="AK25" s="9">
         <f t="shared" si="171"/>
-        <v>4.1655297862664802E-2</v>
-      </c>
-      <c r="U25" s="9">
+        <v>3.7738879074995957E-2</v>
+      </c>
+      <c r="AL25" s="9">
         <f t="shared" si="171"/>
-        <v>4.3924131046374514E-2</v>
-      </c>
-      <c r="V25" s="9">
+        <v>0.25337557516783588</v>
+      </c>
+      <c r="AM25" s="9">
         <f t="shared" si="171"/>
-        <v>-9.3218822687421835E-2</v>
-      </c>
-      <c r="W25" s="9">
+        <v>0.33544720602941525</v>
+      </c>
+      <c r="AN25" s="9">
         <f t="shared" si="171"/>
-        <v>1.4022073457571954E-2</v>
-      </c>
-      <c r="X25" s="9">
+        <v>2.3605736398816347E-2</v>
+      </c>
+      <c r="AO25" s="9">
         <f t="shared" si="171"/>
-        <v>0.15983138666900848</v>
-      </c>
-      <c r="Y25" s="9">
+        <v>0.14081240474454976</v>
+      </c>
+      <c r="AP25" s="9">
         <f t="shared" si="171"/>
-        <v>0.12421923110759227</v>
-      </c>
-      <c r="Z25" s="9">
+        <v>0.21647053780035572</v>
+      </c>
+      <c r="AQ25" s="9">
         <f t="shared" si="171"/>
-        <v>0.26061927605756652</v>
-      </c>
-      <c r="AA25" s="9">
+        <v>0.31725549009105519</v>
+      </c>
+      <c r="AR25" s="9">
         <f t="shared" si="171"/>
-        <v>0.18953732912723453</v>
-      </c>
-      <c r="AB25" s="9">
+        <v>0.31941530933276485</v>
+      </c>
+      <c r="AS25" s="9">
         <f t="shared" si="171"/>
-        <v>0.18830107526881712</v>
-      </c>
-      <c r="AC25" s="9">
+        <v>0.31860743639264794</v>
+      </c>
+      <c r="AT25" s="9">
         <f t="shared" si="171"/>
-        <v>0.17571125265392787</v>
-      </c>
-      <c r="AD25" s="9">
+        <v>0.31917452733751384</v>
+      </c>
+      <c r="AU25" s="9">
         <f t="shared" si="171"/>
-        <v>0.31061565746136305</v>
-      </c>
-      <c r="AE25" s="9">
-        <f t="shared" ref="AE25:AH25" si="172">AE14/AE3</f>
-        <v>0.21673618796288421</v>
-      </c>
-      <c r="AF25" s="9">
+        <v>0.32177287674463001</v>
+      </c>
+      <c r="AV25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.32442267861525353</v>
+      </c>
+      <c r="AW25" s="9">
+        <f t="shared" si="171"/>
+        <v>0.32712495181004791</v>
+      </c>
+      <c r="AX25" s="9">
+        <f t="shared" ref="AX25:AZ25" si="172">AX14/AX3</f>
+        <v>0.32988073536513512</v>
+      </c>
+      <c r="AY25" s="9">
         <f t="shared" si="172"/>
-        <v>0.2947748931975025</v>
-      </c>
-      <c r="AG25" s="9">
+        <v>0.33269108889161048</v>
+      </c>
+      <c r="AZ25" s="9">
         <f t="shared" si="172"/>
-        <v>0.22057565196490805</v>
-      </c>
-      <c r="AH25" s="9">
-        <f t="shared" si="172"/>
-        <v>0.24116530188519891</v>
-      </c>
-      <c r="AJ25" s="9">
-        <f t="shared" ref="AJ25:AW25" si="173">AJ14/AJ3</f>
-        <v>1.8154311649016442E-3</v>
-      </c>
-      <c r="AK25" s="9">
-        <f t="shared" si="173"/>
-        <v>3.7738879074995957E-2</v>
-      </c>
-      <c r="AL25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.25337557516783588</v>
-      </c>
-      <c r="AM25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.33544720602941525</v>
-      </c>
-      <c r="AN25" s="9">
-        <f t="shared" si="173"/>
-        <v>2.3605736398816347E-2</v>
-      </c>
-      <c r="AO25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.14081240474454976</v>
-      </c>
-      <c r="AP25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.21647053780035572</v>
-      </c>
-      <c r="AQ25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.24338334236259379</v>
-      </c>
-      <c r="AR25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.23884930360375423</v>
-      </c>
-      <c r="AS25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.2367793910452721</v>
-      </c>
-      <c r="AT25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.23606180383200254</v>
-      </c>
-      <c r="AU25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.23737733425895949</v>
-      </c>
-      <c r="AV25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.23871891479338087</v>
-      </c>
-      <c r="AW25" s="9">
-        <f t="shared" si="173"/>
-        <v>0.24008706127897894</v>
-      </c>
-      <c r="AX25" s="9">
-        <f t="shared" ref="AX25:AZ25" si="174">AX14/AX3</f>
-        <v>0.24148229977419292</v>
-      </c>
-      <c r="AY25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.24290516675446064</v>
-      </c>
-      <c r="AZ25" s="9">
-        <f t="shared" si="174"/>
-        <v>0.24435620931849594</v>
+        <v>0.33555709298296621</v>
       </c>
       <c r="BB25" t="s">
         <v>53</v>
       </c>
       <c r="BC25" s="11">
         <f>BC24/AW15</f>
-        <v>78.693487187200603</v>
+        <v>99.273503410805432</v>
       </c>
     </row>
     <row r="26" spans="2:55" x14ac:dyDescent="0.3">
@@ -5778,7 +5772,7 @@
       </c>
       <c r="BC26" s="11">
         <f>Main!D3</f>
-        <v>80.599999999999994</v>
+        <v>84.96</v>
       </c>
     </row>
     <row r="27" spans="2:55" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5790,7 +5784,7 @@
       </c>
       <c r="BC27" s="10">
         <f>BC25/BC26-1</f>
-        <v>-2.3654005121580557E-2</v>
+        <v>0.16847343939271942</v>
       </c>
     </row>
     <row r="28" spans="2:55" x14ac:dyDescent="0.3">
